--- a/report/Team1.xlsx
+++ b/report/Team1.xlsx
@@ -1,431 +1,405 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28480" windowHeight="14100"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28480" windowHeight="14100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet" sheetId="5" r:id="rId1"/>
+    <sheet name="sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="计划总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="周计划明细" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
-  <si>
-    <t>角色</t>
-  </si>
-  <si>
-    <t>角色名称(不含PM/PMO)</t>
-  </si>
-  <si>
-    <t>核心职责</t>
-  </si>
-  <si>
-    <t>技能要求</t>
-  </si>
-  <si>
-    <t>工作量占比</t>
-  </si>
-  <si>
-    <t>人天（12 周）</t>
-  </si>
-  <si>
-    <t>单价</t>
-  </si>
-  <si>
-    <t>人力费用</t>
-  </si>
-  <si>
-    <t>关键产出物</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>负责人</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>需求分析师（专职，50% 投入）</t>
-  </si>
-  <si>
-    <t>① 需求访谈与引导（业务方 / 源系统方 / 合规法务）
-② BRD：数据流图（源系统 → 抽取 → 湖仓四层 → 查询/附件/销毁） + 归档范围与保留期矩阵（系统 × 表 × 保留年限）+ 非功能需求（RPO / 查询性能 / 安全合规）
-③ 用户故事地图与验收标准（每个故事带“谁用 / 查什么 / 怎么算完成”）
-④ UAT 场景设计与组织（归档查询、附件调阅、到期销毁举证等核心场景）
-⑤ 需求变更管理与优先级排序</t>
-  </si>
-  <si>
-    <t>需求分析 / 业务流程建模 / 用户故事</t>
-  </si>
-  <si>
-    <t>BRD、用户故事地图、验收标准、UAT 场景脚本、需求变更记录</t>
-  </si>
-  <si>
-    <t>W1~W2 密集；之后 Sprint 级澄清与验收</t>
-  </si>
-  <si>
-    <t>Mandy</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>架构师（兼职功能开发）</t>
-  </si>
-  <si>
-    <t>① 架构定稿（W1~W2）：湖仓分层架构与数据流设计定稿、资源申请单对接平台团队、交付资源逐项验收
-② 专项一 · 权限与数据安全：Unity Catalog 三级授权模型（Catalog→Schema→Table GRANT 继承）、Entra ID 安全组 ↔ UC 组映射、服务主体（SP-query / SP-audit）最小权限设计、行级隔离（Row Filter）、列级动态脱敏（aes_encrypt + COLUMN MASK + is_account_group_member）、PII 标签（ABAC）策略
-③ 专项二 · 冷热数据管理：ADLS Hot/Cool/Cold 分层与生命周期规则（Auto-Tiering，30 天降 Cool / 90 天降 Cold）、Iceberg 分区策略（生命周期分区 + Partition Evolution + hidden partitioning）、Z-Order 排序与 SERVE 物化视图、表维护机制（OPTIMIZE 合并 / expire_snapshots / VACUUM 物理清除）
-④ 前端功能开发：附件预览（SAS 直连）、多表 JOIN 渲染、Retention 配置与销毁审批界面
-⑤ 代码评审与技术决策（ADR 记录）</t>
-  </si>
-  <si>
-    <t>Databricks / Azure 网络 / .NET 或 React / 系统设计</t>
-  </si>
-  <si>
-    <t>架构文档、Azure 部署脚本、RBAC 权限矩阵与 API、UC 授权/掩码/行级隔离、冷热分层与生命周期策略、SERVE 物化与 Compaction、附件预览/JOIN 渲染/Retention 界面</t>
-  </si>
-  <si>
-    <t>W1~W3 架构为主；W4 起开发为主</t>
-  </si>
-  <si>
-    <t>Wade</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>数据工程师（ETL / 湖仓开发）</t>
-  </si>
-  <si>
-    <t>① SeaTunnel 同步链路：源库 JDBC 批量抽取（分片并行 / 限速保护源库 / 断点续传）+ 元数据驱动的配置生成器（勾选表 → 自动生成 .conf 任务）
-② Iceberg 湖仓建模：RAW→CURATED→LAKE→SERVE 四层转换（Spark SQL）、分区与文件设计（target-file-size、Parquet + ZSTD）、Schema Evolution 与源-目标类型映射
-③ Databricks Jobs 编排：多 Task 依赖 DAG（抽取→转换→物化→维护→销毁）、失败重试、告警联动
-④ 数据对账：行数 / 校验和双向比对 + SHA-256 完整性台账（迁移举证）
-⑤ 凭据治理：连接串全走 Key Vault 引用，零硬编码、日志零明文
-⑥ 性能调优：小文件合并、分区裁剪、查询计划分析（EXPLAIN）、Compaction 频率与成本平衡</t>
-  </si>
-  <si>
-    <t>Python / SeaTunnel / Iceberg / Databricks SDK</t>
-  </si>
-  <si>
-    <t>ETL 生成器、四层 SQL、销毁作业、对账脚本、性能报告</t>
-  </si>
-  <si>
-    <t>核心开发，代码量最大</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>全栈开发 + DevOps</t>
-  </si>
-  <si>
-    <t>① .NET 10 后端：元数据服务、查询代理（SQL 白名单校验 + 参数化拼装）、附件服务（SAS 签发）、销毁调度服务
-② React 前端：配置化查询平台（JSON Schema 元数据驱动动态渲染）
-③ CI/CD：GitHub Actions → ACR → Helm 部署到平台提供的 AKS 命名空间（Dev/Staging/Prod 多环境 values）
-④ 代码安全四道 CI 门禁：SAST 静态扫描（CodeQL/Semgrep）、依赖漏洞扫描（Dependabot / dotnet audit）、密钥泄漏扫描（gitleaks）、镜像 CVE 扫描（Trivy）——全部设为合并卡点 + 高中危漏洞清零闭环
-⑤ SSO 集成：Entra ID OIDC 登录 + JWT 角色 Claims 透传</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.NET 10 / React / Docker / AKS </t>
-  </si>
-  <si>
-    <t>后端 API、React 前端、CI/CD、SSO 集成</t>
-  </si>
-  <si>
-    <t>W4 后 B 加入分担，压力缓解</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>QA 测试 + SLC 全生命周期文档</t>
-  </si>
-  <si>
-    <t>① 测试策略与计划（功能 / 集成 / 性能 / 安全 / UAT 五类）
-② 测试执行：功能与回归、数据一致性对账验证（迁移前后行数/校验和）、性能基准（首屏 P95、导出吞吐、20GB 级查询）、安全测试（注入 / 越权 / 掩码旁路）+ UAT 协调
-③ 缺陷全生命周期管理与回归验证
-④ SLC 文档：架构图（C4 四层：上下文/容器/组件/部署）+ 数据流图、详细设计（应用/数据/安全三模块）、接口文档（OpenAPI）、数据字典（35 张元数据表 + 湖仓四层表结构）、用户手册、运维手册、审批材料包</t>
-  </si>
-  <si>
-    <t>测试设计 / 自动化 / 技术写作</t>
-  </si>
-  <si>
-    <t>测试计划/用例(80+)/自动化/报告、架构图×4、详细设计×3、接口文档、数据字典、用户/运维手册、审批包、培训材料</t>
-  </si>
-  <si>
-    <t>W4 起文档测试并重，W9~10 冲刺</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="5" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="32">
-    <font>
-      <sz val="10"/>
+  <fonts count="58">
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF2563EB"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FF2563EB"/>
       <sz val="10"/>
-      <color rgb="FF0F172A"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FF0F172A"/>
       <sz val="10"/>
-      <color rgb="FF475569"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF475569"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="10"/>
-      <color rgb="FF64748B"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF64748B"/>
       <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFC2410C"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
-      <color rgb="FF047857"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FF047857"/>
       <sz val="10"/>
-      <color rgb="FF7C3AED"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FF7C3AED"/>
       <sz val="10"/>
-      <color rgb="FFB45309"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b val="1"/>
+      <color rgb="FFB45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001d4ed8"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="001E3A8A"/>
+      <sz val="8.300000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000284c7"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00d97706"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001d4ed8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="001E3A8A"/>
+      <sz val="8.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="000F172A"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00c2410c"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00b45309"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="39">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="47">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -652,8 +626,48 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -844,209 +858,311 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="5" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="42" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="43" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="44" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="40" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="40" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="46" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="46" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="44" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="44" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="43" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1294,7 +1410,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1303,7 +1419,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1316,11 +1432,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1560,236 +1739,2804 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelRow="5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="17.7083333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="140.708333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="9.70833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.7083333333333" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" customWidth="1"/>
-    <col min="8" max="8" width="15.7083333333333" customWidth="1"/>
-    <col min="9" max="9" width="24.7083333333333" customWidth="1"/>
-    <col min="10" max="10" width="19.7083333333333" customWidth="1"/>
-    <col min="11" max="11" width="28.7083333333333" customWidth="1"/>
+    <col width="17.7083333333333" customWidth="1" style="18" min="1" max="1"/>
+    <col width="22.7083333333333" customWidth="1" style="18" min="2" max="2"/>
+    <col width="140.708333333333" customWidth="1" style="18" min="3" max="3"/>
+    <col width="19.7083333333333" customWidth="1" style="18" min="4" max="4"/>
+    <col width="9.70833333333333" customWidth="1" style="18" min="5" max="5"/>
+    <col width="11.7083333333333" customWidth="1" style="18" min="6" max="6"/>
+    <col width="9.70833333333333" customWidth="1" style="18" min="7" max="7"/>
+    <col width="15.7083333333333" customWidth="1" style="18" min="8" max="8"/>
+    <col width="24.7083333333333" customWidth="1" style="18" min="9" max="9"/>
+    <col width="19.7083333333333" customWidth="1" style="18" min="10" max="10"/>
+    <col width="28.7083333333333" customWidth="1" style="18" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" ht="95.25" customHeight="1" spans="1:11">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="7">
+    <row r="1" ht="26.25" customHeight="1" s="18">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>角色名称(不含PM/PMO)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>核心职责</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>技能要求</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>工作量占比</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>人天（12 周）</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>人力费用</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>关键产出物</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="95.25" customHeight="1" s="18">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>需求分析师（专职，50% 投入）</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>① 需求访谈与引导（业务方 / 源系统方 / 合规法务）
+② BRD：数据流图（源系统 → 抽取 → 湖仓四层 → 查询/附件/销毁） + 归档范围与保留期矩阵（系统 × 表 × 保留年限）+ 非功能需求（RPO / 查询性能 / 安全合规）
+③ 用户故事地图与验收标准（每个故事带“谁用 / 查什么 / 怎么算完成”）
+④ UAT 场景设计与组织（归档查询、附件调阅、到期销毁举证等核心场景）
+⑤ 需求变更管理与优先级排序</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>需求分析 / 业务流程建模 / 用户故事</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
         <v>0.1333</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="9" t="n">
         <v>6600</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="19" t="n">
         <v>132000</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="140.25" customHeight="1" spans="1:11">
-      <c r="A3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>BRD、用户故事地图、验收标准、UAT 场景脚本、需求变更记录</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>W1~W2 密集；之后 Sprint 级澄清与验收</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>Mandy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="140.25" customHeight="1" s="18">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>架构师（兼职功能开发）</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>① 架构定稿（W1~W2）：湖仓分层架构与数据流设计定稿、资源申请单对接平台团队、交付资源逐项验收
+② 专项一 · 权限与数据安全：Unity Catalog 三级授权模型（Catalog→Schema→Table GRANT 继承）、Entra ID 安全组 ↔ UC 组映射、服务主体（SP-query / SP-audit）最小权限设计、行级隔离（Row Filter）、列级动态脱敏（aes_encrypt + COLUMN MASK + is_account_group_member）、PII 标签（ABAC）策略
+③ 专项二 · 冷热数据管理：ADLS Hot/Cool/Cold 分层与生命周期规则（Auto-Tiering，30 天降 Cool / 90 天降 Cold）、Iceberg 分区策略（生命周期分区 + Partition Evolution + hidden partitioning）、Z-Order 排序与 SERVE 物化视图、表维护机制（OPTIMIZE 合并 / expire_snapshots / VACUUM 物理清除）
+④ 前端功能开发：附件预览（SAS 直连）、多表 JOIN 渲染、Retention 配置与销毁审批界面
+⑤ 代码评审与技术决策（ADR 记录）</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Databricks / Azure 网络 / .NET 或 React / 系统设计</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>117000</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>架构文档、Azure 部署脚本、RBAC 权限矩阵与 API、UC 授权/掩码/行级隔离、冷热分层与生命周期策略、SERVE 物化与 Compaction、附件预览/JOIN 渲染/Retention 界面</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>W1~W3 架构为主；W4 起开发为主</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>Wade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="107.25" customHeight="1" s="18">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>数据工程师（ETL / 湖仓开发）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>① SeaTunnel 同步链路：源库 JDBC 批量抽取（分片并行 / 限速保护源库 / 断点续传）+ 元数据驱动的配置生成器（勾选表 → 自动生成 .conf 任务）
+② Iceberg 湖仓建模：RAW→CURATED→LAKE→SERVE 四层转换（Spark SQL）、分区与文件设计（target-file-size、Parquet + ZSTD）、Schema Evolution 与源-目标类型映射
+③ Databricks Jobs 编排：多 Task 依赖 DAG（抽取→转换→物化→维护→销毁）、失败重试、告警联动
+④ 数据对账：行数 / 校验和双向比对 + SHA-256 完整性台账（迁移举证）
+⑤ 凭据治理：连接串全走 Key Vault 引用，零硬编码、日志零明文
+⑥ 性能调优：小文件合并、分区裁剪、查询计划分析（EXPLAIN）、Compaction 频率与成本平衡</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Python / SeaTunnel / Iceberg / Databricks SDK</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="G4" s="9" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>78000</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>ETL 生成器、四层 SQL、销毁作业、对账脚本、性能报告</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>核心开发，代码量最大</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>Wade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="102.75" customHeight="1" s="18">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>全栈开发 + DevOps</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>① .NET 10 后端：元数据服务、查询代理（SQL 白名单校验 + 参数化拼装）、附件服务（SAS 签发）、销毁调度服务
+② React 前端：配置化查询平台（JSON Schema 元数据驱动动态渲染）
+③ CI/CD：GitHub Actions → ACR → Helm 部署到平台提供的 AKS 命名空间（Dev/Staging/Prod 多环境 values）
+④ 代码安全四道 CI 门禁：SAST 静态扫描（CodeQL/Semgrep）、依赖漏洞扫描（Dependabot / dotnet audit）、密钥泄漏扫描（gitleaks）、镜像 CVE 扫描（Trivy）——全部设为合并卡点 + 高中危漏洞清零闭环
+⑤ SSO 集成：Entra ID OIDC 登录 + JWT 角色 Claims 透传</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.NET 10 / React / Docker / AKS </t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>195000</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>后端 API、React 前端、CI/CD、SSO 集成</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>W4 后 B 加入分担，压力缓解</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>Wade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110.25" customHeight="1" s="18">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>QA 测试 + SLC 全生命周期文档</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>① 测试策略与计划（功能 / 集成 / 性能 / 安全 / UAT 五类）
+② 测试执行：功能与回归、数据一致性对账验证（迁移前后行数/校验和）、性能基准（首屏 P95、导出吞吐、20GB 级查询）、安全测试（注入 / 越权 / 掩码旁路）+ UAT 协调
+③ 缺陷全生命周期管理与回归验证
+④ SLC 文档：架构图（C4 四层：上下文/容器/组件/部署）+ 数据流图、详细设计（应用/数据/安全三模块）、接口文档（OpenAPI）、数据字典（35 张元数据表 + 湖仓四层表结构）、用户手册、运维手册、审批材料包</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>测试设计 / 自动化 / 技术写作</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F6" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G3" s="9">
-        <v>3900</v>
-      </c>
-      <c r="H3" s="10">
-        <v>117000</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="107.25" customHeight="1" spans="1:11">
-      <c r="A4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0.1333</v>
-      </c>
-      <c r="F4" s="8">
-        <v>20</v>
-      </c>
-      <c r="G4" s="9">
-        <v>3900</v>
-      </c>
-      <c r="H4" s="10">
-        <v>78000</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" ht="102.75" customHeight="1" spans="1:11">
-      <c r="A5" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.3333</v>
-      </c>
-      <c r="F5" s="8">
-        <v>50</v>
-      </c>
-      <c r="G5" s="9">
-        <v>3900</v>
-      </c>
-      <c r="H5" s="10">
-        <v>195000</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" ht="110.25" customHeight="1" spans="1:11">
-      <c r="A6" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="F6" s="8">
-        <v>30</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="G6" s="9" t="n">
         <v>2500</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>43</v>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>测试计划/用例(80+)/自动化/报告、架构图×4、详细设计×3、接口文档、数据字典、用户/运维手册、审批包、培训材料</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>W4 起文档测试并重，W9~10 冲刺</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" style="18" min="1" max="1"/>
+    <col width="13" customWidth="1" style="18" min="2" max="2"/>
+    <col width="8" customWidth="1" style="18" min="3" max="3"/>
+    <col width="19" customWidth="1" style="18" min="4" max="4"/>
+    <col width="66" customWidth="1" style="18" min="5" max="5"/>
+    <col width="30" customWidth="1" style="18" min="6" max="6"/>
+    <col width="30" customWidth="1" style="18" min="7" max="7"/>
+    <col width="30" customWidth="1" style="18" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>B2 湖仓归档平台 · 3 人团队执行计划（BA + Dev + QA · 双 Release 对半 · AI Vibe Coding）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="18">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>R1 归档检索平台（W1~W6）：存量迁移 + 检索/权限/审计 → W6 Go-Live #1 · R2 治理合规完整版（W7~W12）：治理/生命周期/安全/合规报表 + 全量迁移 + 文档 → W12 Go-Live #2 + 项目结束 · CC（Caring Center）单系统贯穿验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="18">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>主题 / 目标</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>核心交付物（按功能域编号）</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>演示 / 里程碑</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>主要风险</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>需确认/决策项</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="132" customHeight="1" s="18">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Release 1
+归档检索平台</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Sprint 1
+打底+MVP</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>W1~W2</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>需求定稿 + 环境就绪 + CC 连接 + MVP 数据链路</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>【BA】① BRD 定稿（数据流图+保留期矩阵+PII 分级+检索权限矩阵）② CC 垃圾表剔除标准与首批 50 表清单确认 【DEV-Wade】③ 架构定稿 + 资源申请（区域=境内）+ 资源验收 + UC 初始化（arch_cc）④ 前后端骨架 + Azure DevOps Pipelines CI ⑤ SeaTunnel PoC（CC 抽样 10 表端到端）+ 1253 表扫描分类 ⑥【01】首批 50 表批量导入（分片/限速/断点）+ 配置生成器 v1 【QA】⑦ 测试计划（8 域）+ 架构图×2（上下文/容器）+ 文档模板 ⑧ 迁移对账测试设计</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>★ W2：CC PoC 端到端 + BRD 签字 + 50 表入 RAW + 登录页可访问</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>CC 账号/白名单周期；Wade 一人扛三角色串行风险；1253 表审表量</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>① CC 只读账号（W1）② 垃圾表标准 ③ 50 表清单（W2 末）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="132" customHeight="1" s="18">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Release 1
+归档检索平台</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2
+检索增强+就绪</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>W3~W5</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>检索/权限/审计端到端 + R1 上线就绪</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>【DEV-Wade】【05】① 配置化检索页 + 预览（SAS）+ 导出【08】② RBAC 五角色 + UC GRANT + 掩码函数（权限三态）③ SSO JWT Claims ④【06】审计埋点【07】⑤ 连接器模板 v1 ⑥ SERVE 热表物化【安全】⑦ 四道 CI 门禁 【BA】⑧ PII 字段标记 + 预览范围确认 ⑨ R1 验收 + UAT #1 脚本【QA】⑩ 功能/安全测试执行 ⑪ R1 文档 50%（用户手册检索章节）【就绪 W5】⑫ 发布包+回退演练+UAT 预演+迁移预跑+就绪检查</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>★ W5 末：R1 上线就绪检查 100%（发布包/预演/回退/预跑全绿）</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>Wade 任务密度最高的一段；权限三态联调复杂</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>① PII 标记（W3）② 性能标准 P95&lt;5s ③ UAT 预演排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="132" customHeight="1" s="18">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Release 1
+归档检索平台</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2
+检索增强+就绪</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>R1 上线周：发布 → UAT → Go-Live #1</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>【DEV】① 生产发布（就绪包一键发布+Environments 审批）② CC 50 表生产迁移+对账 ③ P1 当日清 【BA】④ UAT #1 正式主持（检索/预览/导出/权限/SSO/审计 → 签字）⑤ Go/No-Go 需求侧 【QA】⑥ 上线记录 + R1 审批材料提交 ⑦ 48h 值守三角色轮值</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>★ W6：Go-Live #1 —— CC 可查、有权限、有审计（Release 1 交付）</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>三人全上线值守（轮值缓解）；审批受理时长</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>① Go-Live #1 窗口 ② UAT #1 签字人</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="132" customHeight="1" s="18">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Release 2
+治理合规完整版</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Sprint 3
+治理+安全</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>W7~W9</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>治理 + 生命周期 + 安全管控（R2 功能主体）</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>【DEV-Wade】【02】① 增量接入（watermark）+ 冷数据自动转冷 ② 元数据标准界面 【03】③ 处置引擎（DROP PARTITION+VACUUM）+ Legal Hold + 归档模型 ④ 处置/Hold 界面 【04】⑤ 加密（CMK+字段级+轮转）+ 脱敏 + 境内驻留核查 ⑥ ADLS 分层+生命周期+Compaction 【07】⑦ 连接器模板库（MySQL+文件源）+ 连接管理界面【08】⑧ 行级隔离验证 【BA】⑨ Legal Hold 触发条件定稿（法务）⑩ 增量频率/冷数据标准 【QA】⑪ 处置全链路 E2E（1 天保留期→到期→Hold→处置→审计）⑫ 掩码旁路/越权测试 ⑬ 文档 60%</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>★ W8：处置全链路通过+脱敏三态+驻留核查；★ W9：越权全拦截+新源 30 分钟接入</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>处置不可逆需沙箱验证；加密/驻留须人工复核（Wade 自查=风险）</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>① Legal Hold 审批人 ② 保留期底线 ③ 实时指标验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="132" customHeight="1" s="18">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Release 2
+治理合规完整版</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 4
+全量+合规+就绪</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>W10~W11</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>CC 全量迁移 + 合规报表 + R2 上线就绪</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>【DEV-Wade】【01】① CC 全量 1253 表分批迁移（600~800 有效表）+ 逐批对账 【06】② 合规报表（等保/个保法对照+导出）③ 全量回归（R1+R2）④ R2 发布包+回退演练 ⑤ 安全终检（四门禁+渗透配合）⑥ 迁移预跑+窗口预约 【BA】⑦ 全量范围最终确认（签字）⑧ 合规报表口径对齐（法务）⑨ UAT #2 脚本 【QA】⑩ 文档冲刺（7 套 80%→终稿）+ 审批材料 ⑪ 连接器兼容矩阵 + 口径验证 ⑫ W11 末就绪检查</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>★ W10：CC 全量对账 100%；★ W11 末：R2 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>全量迁移时长不可控；文档冲刺与就绪并行（QA 压力最大）</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>① CC 数据量实测 ② 迁移窗口 ③ 报表口径签字人</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="132" customHeight="1" s="18">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Release 2
+治理合规完整版</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 4
+全量+合规+就绪</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>R2 上线周 + 收尾：Go-Live #2 → 项目结束</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>【DEV】① R2 生产发布（治理/安全/合规，增量发布不中断 R1）② CC 生产全量迁移收尾+终版对账 ③ P1 当日清 【BA】④ UAT #2 正式主持（处置/Hold/脱敏/报表 → 签字）⑤ Go/No-Go 【QA】⑥ 审批材料提交（完整版）⑦ 文档终版归档（7 套）⑧ 上线验证与稳定性报告 → 项目结束</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>★ W12：Go-Live #2（完整版）+ 交付物归档 → 项目结束</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>上线+文档+收尾三线并行在 W12；全量迁移收尾跨窗口</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>① Go-Live #2 窗口 ② UAT #2 签字人 ③ 文档确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1" s="18">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>团队：3 人 —— BA（Mandy，50% 投入）/ DEV（Wade，全职，承担架构+数据工程+全栈 DevOps 三角色）/ QA（全职，测试+SLC 文档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" s="18">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>结构：双 Release 对半（R1 W1~W6 / R2 W7~W12），各自"功能→就绪→上线"闭环，上线各占最后一周（W6/W12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1" s="18">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>人天：BA 20 + DEV 100 + QA 30 = 150 人天（12 周）；人力费用 = 132,000 + 390,000 + 75,000 = ¥597,000（按 Team1 表单价）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1" s="18">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>与 5 人版差异：DEV 集中 Wade 一人（风险↑），用 AI Vibe Coding 提效；BA 兼测试协调；无独立架构评审——建议 W1/W5 两个节点请平台团队做外部 sanity check</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1" s="18">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>W7~W11 期间 R1 已在生产运行，R2 上线为增量发布不中断服务</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="8" customWidth="1" style="18" min="2" max="2"/>
+    <col width="6" customWidth="1" style="18" min="3" max="3"/>
+    <col width="13" customWidth="1" style="18" min="4" max="4"/>
+    <col width="66" customWidth="1" style="18" min="5" max="5"/>
+    <col width="26" customWidth="1" style="18" min="6" max="6"/>
+    <col width="20" customWidth="1" style="18" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>周计划明细 · 3 人 × 12 周（BA·Mandy / DEV·Wade / QA · 双 Release · 上线仅 W6/W12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>🤖 = AI Vibe Coding 提效标注（主要落在 DEV-Wade 任务）· 外部依赖为不可压缩物理时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="18">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>产出物 / 验收标准</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>外部依赖</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="18">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D5" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>• 【8 域需求访谈】业务方×2 场 + 合规法务×1 场（保留期/PII/Legal Hold）</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>BRD 初稿；CC 剔除规则</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>业务方访谈排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="18">
+      <c r="A6" s="43" t="n"/>
+      <c r="B6" s="43" t="n"/>
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 BRD 起稿：数据流图 + 归档范围矩阵 + PII 分级 + 检索权限矩阵</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="43" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="18">
+      <c r="A7" s="43" t="n"/>
+      <c r="B7" s="43" t="n"/>
+      <c r="C7" s="43" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>• CC 接入范围初定：1253 表垃圾表剔除标准与业务方对齐</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="43" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="18">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>• 架构文档定稿（湖仓分层+UC 授权+存储分层）+ 资源申请单（区域=境内）</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>架构 V1；申请单；骨架+CI</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>平台受理；CC 账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="18">
+      <c r="A9" s="43" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>• CC 只读账号 + NAT 白名单申请（D1 启动）</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="43" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="18">
+      <c r="A10" s="43" t="n"/>
+      <c r="B10" s="43" t="n"/>
+      <c r="C10" s="43" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 CC 1253 表扫描分类脚本 + 前后端骨架 + Azure DevOps Pipelines CI</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="43" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="18">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 测试计划初稿（按 8 域组织：迁移/治理/生命周期/安全/检索/合规/连接器/权限）</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>测试计划；架构图×2</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>BA 的 BRD 范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="18">
+      <c r="A12" s="43" t="n"/>
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="43" t="n"/>
+      <c r="D12" s="48" t="n"/>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>• 架构图初稿：上下文图 + 容器图</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="43" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="18">
+      <c r="A13" s="43" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="48" t="n"/>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>• 文档模板 4 套定稿</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="43" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="18">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>• BRD 评审 → 定稿签字</t>
+        </is>
+      </c>
+      <c r="F14" s="42" t="inlineStr">
+        <is>
+          <t>BRD 签字；50 表清单</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="inlineStr">
+        <is>
+          <t>业务方到场</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="18">
+      <c r="A15" s="43" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>• CC 首批 50 张热表清单确认（业务方勾选）</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="43" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="18">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>• 平台交付资源验收 + UC 初始化（arch_cc + GRANT 模板 + SP）</t>
+        </is>
+      </c>
+      <c r="F16" s="42" t="inlineStr">
+        <is>
+          <t>★ PoC 端到端；50 表入 RAW</t>
+        </is>
+      </c>
+      <c r="G16" s="29" t="inlineStr">
+        <is>
+          <t>资源交付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="18">
+      <c r="A17" s="43" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="43" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 SeaTunnel PoC：抽样 10 表 → RAW → SQL Warehouse 可查</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="43" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="18">
+      <c r="A18" s="43" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>• 【01】50 表批量导入（分片/限速/断点）+ 配置生成器 v1</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="43" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="18">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="inlineStr">
+        <is>
+          <t>• 架构图完善：组件图 + 部署图</t>
+        </is>
+      </c>
+      <c r="F19" s="42" t="inlineStr">
+        <is>
+          <t>架构图×4 初稿</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="18">
+      <c r="A20" s="43" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="43" t="n"/>
+      <c r="D20" s="48" t="n"/>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>• 【01】迁移对账测试设计（行数/校验和）</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="43" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="18">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E21" s="41" t="inlineStr">
+        <is>
+          <t>• 【05】检索场景字段级确认（PII 列标记）</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>PII 标记清单</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="18">
+      <c r="A22" s="43" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="41" t="inlineStr">
+        <is>
+          <t>• 预览格式范围确认（图片/音频/视频）</t>
+        </is>
+      </c>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="43" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="18">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="D23" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>• 【08】RBAC CRUD + OIDC/JWT 鉴权 + 前端权限渲染（🤖 AI 生成）</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="inlineStr">
+        <is>
+          <t>RBAC+检索页提测</t>
+        </is>
+      </c>
+      <c r="G23" s="29" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="18">
+      <c r="A24" s="43" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="43" t="n"/>
+      <c r="D24" s="46" t="n"/>
+      <c r="E24" s="41" t="inlineStr">
+        <is>
+          <t>• 【05】配置化检索页（动态筛选/表格/分页）</t>
+        </is>
+      </c>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="43" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="18">
+      <c r="A25" s="43" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="43" t="n"/>
+      <c r="D25" s="46" t="n"/>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>• 【06】审计埋点 v1 + 安全门禁①②进 CI</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="43" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="18">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>• 单测框架 + 覆盖率门禁 &gt;70% 进 CI</t>
+        </is>
+      </c>
+      <c r="F26" s="42" t="inlineStr">
+        <is>
+          <t>CI 门禁生效</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t>DEV API 稳定</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="18">
+      <c r="A27" s="43" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="48" t="n"/>
+      <c r="E27" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 API 集成测试 10 场景（AI 生成用例）</t>
+        </is>
+      </c>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="43" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" s="18">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>• R1 核心场景验收（检索/预览/导出/权限三态对照用户故事）</t>
+        </is>
+      </c>
+      <c r="F28" s="42" t="inlineStr">
+        <is>
+          <t>R1 验收记录</t>
+        </is>
+      </c>
+      <c r="G28" s="29" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" s="18">
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="43" t="n"/>
+      <c r="C29" s="43" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #1 场景脚本初稿</t>
+        </is>
+      </c>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="43" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1" s="18">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="D30" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>• 【08】UC GRANT 落地 + 掩码函数（aes_encrypt+COLUMN MASK）+ 权限三态联调</t>
+        </is>
+      </c>
+      <c r="F30" s="42" t="inlineStr">
+        <is>
+          <t>权限三态通过；预览/导出可用</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="18">
+      <c r="A31" s="43" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="46" t="n"/>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>• 【05】SERVE 热表物化 + 预览（SAS）+ 导出</t>
+        </is>
+      </c>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="43" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="18">
+      <c r="A32" s="43" t="n"/>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="46" t="n"/>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>• 安全修复 High 清零</t>
+        </is>
+      </c>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="43" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1" s="18">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="D33" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>• 功能测试执行 + Bug 跟踪</t>
+        </is>
+      </c>
+      <c r="F33" s="42" t="inlineStr">
+        <is>
+          <t>测试报告</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1" s="18">
+      <c r="A34" s="43" t="n"/>
+      <c r="B34" s="43" t="n"/>
+      <c r="C34" s="43" t="n"/>
+      <c r="D34" s="48" t="n"/>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 安全测试①：注入/XSS/越权用例</t>
+        </is>
+      </c>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="43" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1" s="18">
+      <c r="A35" s="43" t="n"/>
+      <c r="B35" s="43" t="n"/>
+      <c r="C35" s="43" t="n"/>
+      <c r="D35" s="48" t="n"/>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>• 性能测试准备</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="43" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1" s="18">
+      <c r="A36" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="D36" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #1 预演主持（Staging：检索/权限/审计场景）</t>
+        </is>
+      </c>
+      <c r="F36" s="42" t="inlineStr">
+        <is>
+          <t>预演完成</t>
+        </is>
+      </c>
+      <c r="G36" s="29" t="inlineStr">
+        <is>
+          <t>业务方预演排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" s="18">
+      <c r="A37" s="43" t="n"/>
+      <c r="B37" s="43" t="n"/>
+      <c r="C37" s="43" t="n"/>
+      <c r="D37" s="44" t="n"/>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>• 预演反馈分类与裁决</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="n"/>
+      <c r="G37" s="43" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="18">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="D38" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 R1 发布包（Helm 生产 values + UC 生产脚本）+ 回退演练</t>
+        </is>
+      </c>
+      <c r="F38" s="42" t="inlineStr">
+        <is>
+          <t>发布包就绪；预跑完成</t>
+        </is>
+      </c>
+      <c r="G38" s="29" t="inlineStr">
+        <is>
+          <t>生产窗口审批</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" s="18">
+      <c r="A39" s="43" t="n"/>
+      <c r="B39" s="43" t="n"/>
+      <c r="C39" s="43" t="n"/>
+      <c r="D39" s="46" t="n"/>
+      <c r="E39" s="41" t="inlineStr">
+        <is>
+          <t>• CC 生产迁移预跑（50 表→Staging）+ Runbook</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="n"/>
+      <c r="G39" s="43" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1" s="18">
+      <c r="A40" s="43" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="46" t="n"/>
+      <c r="E40" s="41" t="inlineStr">
+        <is>
+          <t>• 功能收口：性能优化（P95&lt;5s）+ 遗留清零 + 监控告警就绪</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="n"/>
+      <c r="G40" s="43" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1" s="18">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="D41" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="inlineStr">
+        <is>
+          <t>• R1 文档冲刺：用户手册 50% + 运维手册 40%</t>
+        </is>
+      </c>
+      <c r="F41" s="42" t="inlineStr">
+        <is>
+          <t>★ 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="inlineStr">
+        <is>
+          <t>各角色材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" s="18">
+      <c r="A42" s="43" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="48" t="n"/>
+      <c r="E42" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 上线 Checklist v1 + UAT #1 脚本定稿</t>
+        </is>
+      </c>
+      <c r="F42" s="43" t="n"/>
+      <c r="G42" s="43" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1" s="18">
+      <c r="A43" s="43" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="48" t="n"/>
+      <c r="E43" s="41" t="inlineStr">
+        <is>
+          <t>• W5 末就绪检查组织（发布包/预演/回退/预跑）</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1" s="18">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="inlineStr">
+        <is>
+          <t>• Go/No-Go #1 决策参与</t>
+        </is>
+      </c>
+      <c r="F44" s="42" t="inlineStr">
+        <is>
+          <t>★ UAT #1 签字</t>
+        </is>
+      </c>
+      <c r="G44" s="29" t="inlineStr">
+        <is>
+          <t>UAT 业务方时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" s="18">
+      <c r="A45" s="43" t="n"/>
+      <c r="B45" s="43" t="n"/>
+      <c r="C45" s="43" t="n"/>
+      <c r="D45" s="44" t="n"/>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #1 正式主持（签字）</t>
+        </is>
+      </c>
+      <c r="F45" s="43" t="n"/>
+      <c r="G45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1" s="18">
+      <c r="A46" s="43" t="n"/>
+      <c r="B46" s="43" t="n"/>
+      <c r="C46" s="43" t="n"/>
+      <c r="D46" s="44" t="n"/>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>• 上线后用户反馈分诊</t>
+        </is>
+      </c>
+      <c r="F46" s="43" t="n"/>
+      <c r="G46" s="43" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1" s="18">
+      <c r="A47" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>• 生产发布执行（就绪包一键发布+审批）</t>
+        </is>
+      </c>
+      <c r="F47" s="42" t="inlineStr">
+        <is>
+          <t>★ Go-Live #1</t>
+        </is>
+      </c>
+      <c r="G47" s="29" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1" s="18">
+      <c r="A48" s="43" t="n"/>
+      <c r="B48" s="43" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="46" t="n"/>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>• CC 50 表生产迁移+对账</t>
+        </is>
+      </c>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="43" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1" s="18">
+      <c r="A49" s="43" t="n"/>
+      <c r="B49" s="43" t="n"/>
+      <c r="C49" s="43" t="n"/>
+      <c r="D49" s="46" t="n"/>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>• P1 当日清 + 48h 值守</t>
+        </is>
+      </c>
+      <c r="F49" s="43" t="n"/>
+      <c r="G49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1" s="18">
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>• 上线执行记录（Checklist 勾选）</t>
+        </is>
+      </c>
+      <c r="F50" s="42" t="inlineStr">
+        <is>
+          <t>★ Release 1 交付</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>审批受理</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1" s="18">
+      <c r="A51" s="43" t="n"/>
+      <c r="B51" s="43" t="n"/>
+      <c r="C51" s="43" t="n"/>
+      <c r="D51" s="48" t="n"/>
+      <c r="E51" s="41" t="inlineStr">
+        <is>
+          <t>• R1 审批材料提交</t>
+        </is>
+      </c>
+      <c r="F51" s="43" t="n"/>
+      <c r="G51" s="43" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1" s="18">
+      <c r="A52" s="43" t="n"/>
+      <c r="B52" s="43" t="n"/>
+      <c r="C52" s="43" t="n"/>
+      <c r="D52" s="48" t="n"/>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>• 48h 值守轮值</t>
+        </is>
+      </c>
+      <c r="F52" s="43" t="n"/>
+      <c r="G52" s="43" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1" s="18">
+      <c r="A53" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="D53" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E53" s="41" t="inlineStr">
+        <is>
+          <t>• 【02】增量频率与冷数据标准确认</t>
+        </is>
+      </c>
+      <c r="F53" s="42" t="inlineStr">
+        <is>
+          <t>R2 需求就绪</t>
+        </is>
+      </c>
+      <c r="G53" s="29" t="inlineStr">
+        <is>
+          <t>法务配合</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1" s="18">
+      <c r="A54" s="43" t="n"/>
+      <c r="B54" s="43" t="n"/>
+      <c r="C54" s="43" t="n"/>
+      <c r="D54" s="44" t="n"/>
+      <c r="E54" s="41" t="inlineStr">
+        <is>
+          <t>• 【03】Legal Hold 触发条件定稿（法务）</t>
+        </is>
+      </c>
+      <c r="F54" s="43" t="n"/>
+      <c r="G54" s="43" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1" s="18">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>• 【03】处置引擎（扫描→DROP PARTITION→VACUUM）</t>
+        </is>
+      </c>
+      <c r="F55" s="42" t="inlineStr">
+        <is>
+          <t>处置引擎可跑；加密生效</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1" s="18">
+      <c r="A56" s="43" t="n"/>
+      <c r="B56" s="43" t="n"/>
+      <c r="C56" s="43" t="n"/>
+      <c r="D56" s="46" t="n"/>
+      <c r="E56" s="41" t="inlineStr">
+        <is>
+          <t>• 【04】加密体系（CMK+字段级+密钥轮转）</t>
+        </is>
+      </c>
+      <c r="F56" s="43" t="n"/>
+      <c r="G56" s="43" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1" s="18">
+      <c r="A57" s="43" t="n"/>
+      <c r="B57" s="43" t="n"/>
+      <c r="C57" s="43" t="n"/>
+      <c r="D57" s="46" t="n"/>
+      <c r="E57" s="41" t="inlineStr">
+        <is>
+          <t>• 【02】增量接入（watermark）+ 冷数据自动转冷</t>
+        </is>
+      </c>
+      <c r="F57" s="43" t="n"/>
+      <c r="G57" s="43" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1" s="18">
+      <c r="A58" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B58" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="D58" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E58" s="41" t="inlineStr">
+        <is>
+          <t>• 功能用例扩充（处置/Hold/增量/脱敏）</t>
+        </is>
+      </c>
+      <c r="F58" s="42" t="inlineStr">
+        <is>
+          <t>用例扩充</t>
+        </is>
+      </c>
+      <c r="G58" s="29" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1" s="18">
+      <c r="A59" s="43" t="n"/>
+      <c r="B59" s="43" t="n"/>
+      <c r="C59" s="43" t="n"/>
+      <c r="D59" s="48" t="n"/>
+      <c r="E59" s="41" t="inlineStr">
+        <is>
+          <t>• R1 上线后回归监控 + 文档推进（手册 60%）</t>
+        </is>
+      </c>
+      <c r="F59" s="43" t="n"/>
+      <c r="G59" s="43" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1" s="18">
+      <c r="A60" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B60" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="D60" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E60" s="41" t="inlineStr">
+        <is>
+          <t>• 验收处置全链路（对照合规要求）</t>
+        </is>
+      </c>
+      <c r="F60" s="42" t="inlineStr">
+        <is>
+          <t>处置验收</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr"/>
+    </row>
+    <row r="61" ht="22" customHeight="1" s="18">
+      <c r="A61" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B61" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E61" s="41" t="inlineStr">
+        <is>
+          <t>• 【03】Legal Hold（Hold/Release+豁免+留痕）+ 归档模型管理</t>
+        </is>
+      </c>
+      <c r="F61" s="42" t="inlineStr">
+        <is>
+          <t>Hold 可用；分层生效</t>
+        </is>
+      </c>
+      <c r="G61" s="29" t="inlineStr"/>
+    </row>
+    <row r="62" ht="22" customHeight="1" s="18">
+      <c r="A62" s="43" t="n"/>
+      <c r="B62" s="43" t="n"/>
+      <c r="C62" s="43" t="n"/>
+      <c r="D62" s="46" t="n"/>
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>• 【04】境内驻留核查（区域+出口流量）</t>
+        </is>
+      </c>
+      <c r="F62" s="43" t="n"/>
+      <c r="G62" s="43" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1" s="18">
+      <c r="A63" s="43" t="n"/>
+      <c r="B63" s="43" t="n"/>
+      <c r="C63" s="43" t="n"/>
+      <c r="D63" s="46" t="n"/>
+      <c r="E63" s="41" t="inlineStr">
+        <is>
+          <t>• 【04】ADLS 分层+生命周期+Compaction</t>
+        </is>
+      </c>
+      <c r="F63" s="43" t="n"/>
+      <c r="G63" s="43" t="n"/>
+    </row>
+    <row r="64" ht="22" customHeight="1" s="18">
+      <c r="A64" s="43" t="n"/>
+      <c r="B64" s="43" t="n"/>
+      <c r="C64" s="43" t="n"/>
+      <c r="D64" s="46" t="n"/>
+      <c r="E64" s="41" t="inlineStr">
+        <is>
+          <t>• 【07】连接器模板库（MySQL+文件源）</t>
+        </is>
+      </c>
+      <c r="F64" s="43" t="n"/>
+      <c r="G64" s="43" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1" s="18">
+      <c r="A65" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B65" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="D65" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E65" s="41" t="inlineStr">
+        <is>
+          <t>• 【03】处置全链路 E2E：1 天保留期→到期→Hold→处置→审计</t>
+        </is>
+      </c>
+      <c r="F65" s="42" t="inlineStr">
+        <is>
+          <t>处置 E2E 通过</t>
+        </is>
+      </c>
+      <c r="G65" s="29" t="inlineStr"/>
+    </row>
+    <row r="66" ht="22" customHeight="1" s="18">
+      <c r="A66" s="43" t="n"/>
+      <c r="B66" s="43" t="n"/>
+      <c r="C66" s="43" t="n"/>
+      <c r="D66" s="48" t="n"/>
+      <c r="E66" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 安全测试②：掩码旁路/越权用例</t>
+        </is>
+      </c>
+      <c r="F66" s="43" t="n"/>
+      <c r="G66" s="43" t="n"/>
+    </row>
+    <row r="67" ht="22" customHeight="1" s="18">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B67" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="D67" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E67" s="41" t="inlineStr">
+        <is>
+          <t>• 合规报表口径与法务对齐</t>
+        </is>
+      </c>
+      <c r="F67" s="42" t="inlineStr">
+        <is>
+          <t>口径确认；范围签字</t>
+        </is>
+      </c>
+      <c r="G67" s="29" t="inlineStr"/>
+    </row>
+    <row r="68" ht="22" customHeight="1" s="18">
+      <c r="A68" s="43" t="n"/>
+      <c r="B68" s="43" t="n"/>
+      <c r="C68" s="43" t="n"/>
+      <c r="D68" s="44" t="n"/>
+      <c r="E68" s="41" t="inlineStr">
+        <is>
+          <t>• CC 全量迁移范围最终确认（签字）</t>
+        </is>
+      </c>
+      <c r="F68" s="43" t="n"/>
+      <c r="G68" s="43" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1" s="18">
+      <c r="A69" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B69" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="D69" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E69" s="41" t="inlineStr">
+        <is>
+          <t>• 【08】行级隔离验证（越权全拦）</t>
+        </is>
+      </c>
+      <c r="F69" s="42" t="inlineStr">
+        <is>
+          <t>全量启动；越权拦截</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>CC 数据量实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" s="18">
+      <c r="A70" s="43" t="n"/>
+      <c r="B70" s="43" t="n"/>
+      <c r="C70" s="43" t="n"/>
+      <c r="D70" s="46" t="n"/>
+      <c r="E70" s="41" t="inlineStr">
+        <is>
+          <t>• 【01】CC 全量 1253 表分批迁移启动（600~800 有效表）</t>
+        </is>
+      </c>
+      <c r="F70" s="43" t="n"/>
+      <c r="G70" s="43" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1" s="18">
+      <c r="A71" s="43" t="n"/>
+      <c r="B71" s="43" t="n"/>
+      <c r="C71" s="43" t="n"/>
+      <c r="D71" s="46" t="n"/>
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>• 【07】连接器运行监控与审计</t>
+        </is>
+      </c>
+      <c r="F71" s="43" t="n"/>
+      <c r="G71" s="43" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1" s="18">
+      <c r="A72" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B72" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="D72" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E72" s="41" t="inlineStr">
+        <is>
+          <t>• 【07】连接器兼容性测试（SQL Server/MySQL 矩阵）</t>
+        </is>
+      </c>
+      <c r="F72" s="42" t="inlineStr">
+        <is>
+          <t>兼容矩阵</t>
+        </is>
+      </c>
+      <c r="G72" s="29" t="inlineStr"/>
+    </row>
+    <row r="73" ht="22" customHeight="1" s="18">
+      <c r="A73" s="43" t="n"/>
+      <c r="B73" s="43" t="n"/>
+      <c r="C73" s="43" t="n"/>
+      <c r="D73" s="48" t="n"/>
+      <c r="E73" s="41" t="inlineStr">
+        <is>
+          <t>• 【06】合规报表口径验证</t>
+        </is>
+      </c>
+      <c r="F73" s="43" t="n"/>
+      <c r="G73" s="43" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1" s="18">
+      <c r="A74" s="43" t="n"/>
+      <c r="B74" s="43" t="n"/>
+      <c r="C74" s="43" t="n"/>
+      <c r="D74" s="48" t="n"/>
+      <c r="E74" s="41" t="inlineStr">
+        <is>
+          <t>• 用户手册 70% + 数据字典初稿</t>
+        </is>
+      </c>
+      <c r="F74" s="43" t="n"/>
+      <c r="G74" s="43" t="n"/>
+    </row>
+    <row r="75" ht="22" customHeight="1" s="18">
+      <c r="A75" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B75" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D75" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E75" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 场景脚本定稿（处置/Hold/脱敏/报表）</t>
+        </is>
+      </c>
+      <c r="F75" s="42" t="inlineStr">
+        <is>
+          <t>UAT #2 脚本</t>
+        </is>
+      </c>
+      <c r="G75" s="29" t="inlineStr"/>
+    </row>
+    <row r="76" ht="22" customHeight="1" s="18">
+      <c r="A76" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B76" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D76" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E76" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 R2 发布包（增量/处置/加密/分层生产版）+ 回退演练</t>
+        </is>
+      </c>
+      <c r="F76" s="42" t="inlineStr">
+        <is>
+          <t>R2 发布包就绪</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1" s="18">
+      <c r="A77" s="43" t="n"/>
+      <c r="B77" s="43" t="n"/>
+      <c r="C77" s="43" t="n"/>
+      <c r="D77" s="46" t="n"/>
+      <c r="E77" s="41" t="inlineStr">
+        <is>
+          <t>• 安全评审材料（技术说明）</t>
+        </is>
+      </c>
+      <c r="F77" s="43" t="n"/>
+      <c r="G77" s="43" t="n"/>
+    </row>
+    <row r="78" ht="22" customHeight="1" s="18">
+      <c r="A78" s="43" t="n"/>
+      <c r="B78" s="43" t="n"/>
+      <c r="C78" s="43" t="n"/>
+      <c r="D78" s="46" t="n"/>
+      <c r="E78" s="41" t="inlineStr">
+        <is>
+          <t>• 【01】全量迁移继续 + 逐批对账 + 生产预跑</t>
+        </is>
+      </c>
+      <c r="F78" s="43" t="n"/>
+      <c r="G78" s="43" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1" s="18">
+      <c r="A79" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B79" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D79" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E79" s="41" t="inlineStr">
+        <is>
+          <t>• 文档冲刺：用户手册 85% + 运维手册 70% + 架构图更新</t>
+        </is>
+      </c>
+      <c r="F79" s="42" t="inlineStr">
+        <is>
+          <t>文档 80%+</t>
+        </is>
+      </c>
+      <c r="G79" s="29" t="inlineStr"/>
+    </row>
+    <row r="80" ht="22" customHeight="1" s="18">
+      <c r="A80" s="43" t="n"/>
+      <c r="B80" s="43" t="n"/>
+      <c r="C80" s="43" t="n"/>
+      <c r="D80" s="48" t="n"/>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 审批材料起稿</t>
+        </is>
+      </c>
+      <c r="F80" s="43" t="n"/>
+      <c r="G80" s="43" t="n"/>
+    </row>
+    <row r="81" ht="22" customHeight="1" s="18">
+      <c r="A81" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D81" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E81" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 预演主持（处置/Hold/脱敏/报表）</t>
+        </is>
+      </c>
+      <c r="F81" s="42" t="inlineStr">
+        <is>
+          <t>预演完成</t>
+        </is>
+      </c>
+      <c r="G81" s="29" t="inlineStr">
+        <is>
+          <t>业务方排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1" s="18">
+      <c r="A82" s="43" t="n"/>
+      <c r="B82" s="43" t="n"/>
+      <c r="C82" s="43" t="n"/>
+      <c r="D82" s="44" t="n"/>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>• 预演反馈裁决</t>
+        </is>
+      </c>
+      <c r="F82" s="43" t="n"/>
+      <c r="G82" s="43" t="n"/>
+    </row>
+    <row r="83" ht="22" customHeight="1" s="18">
+      <c r="A83" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D83" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E83" s="41" t="inlineStr">
+        <is>
+          <t>• 全量回归（R1+R2）+ 安全终检（四门禁+渗透）</t>
+        </is>
+      </c>
+      <c r="F83" s="42" t="inlineStr">
+        <is>
+          <t>★ 全量对账 100%</t>
+        </is>
+      </c>
+      <c r="G83" s="29" t="inlineStr">
+        <is>
+          <t>渗透排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1" s="18">
+      <c r="A84" s="43" t="n"/>
+      <c r="B84" s="43" t="n"/>
+      <c r="C84" s="43" t="n"/>
+      <c r="D84" s="46" t="n"/>
+      <c r="E84" s="41" t="inlineStr">
+        <is>
+          <t>• 【01】全量迁移收尾 + 对账报告</t>
+        </is>
+      </c>
+      <c r="F84" s="43" t="n"/>
+      <c r="G84" s="43" t="n"/>
+    </row>
+    <row r="85" ht="22" customHeight="1" s="18">
+      <c r="A85" s="43" t="n"/>
+      <c r="B85" s="43" t="n"/>
+      <c r="C85" s="43" t="n"/>
+      <c r="D85" s="46" t="n"/>
+      <c r="E85" s="41" t="inlineStr">
+        <is>
+          <t>• R2 发布包冻结 + 上线 Checklist v2</t>
+        </is>
+      </c>
+      <c r="F85" s="43" t="n"/>
+      <c r="G85" s="43" t="n"/>
+    </row>
+    <row r="86" ht="22" customHeight="1" s="18">
+      <c r="A86" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B86" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C86" s="26" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D86" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E86" s="41" t="inlineStr">
+        <is>
+          <t>• 文档终审推进（7 套终稿）</t>
+        </is>
+      </c>
+      <c r="F86" s="42" t="inlineStr">
+        <is>
+          <t>★ R2 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G86" s="29" t="inlineStr"/>
+    </row>
+    <row r="87" ht="22" customHeight="1" s="18">
+      <c r="A87" s="43" t="n"/>
+      <c r="B87" s="43" t="n"/>
+      <c r="C87" s="43" t="n"/>
+      <c r="D87" s="48" t="n"/>
+      <c r="E87" s="41" t="inlineStr">
+        <is>
+          <t>• W11 末就绪检查组织（发布包/预演/文档/回退）</t>
+        </is>
+      </c>
+      <c r="F87" s="43" t="n"/>
+      <c r="G87" s="43" t="n"/>
+    </row>
+    <row r="88" ht="22" customHeight="1" s="18">
+      <c r="A88" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B88" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D88" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E88" s="41" t="inlineStr">
+        <is>
+          <t>• Go/No-Go #2 决策参与</t>
+        </is>
+      </c>
+      <c r="F88" s="42" t="inlineStr">
+        <is>
+          <t>★ UAT #2 签字</t>
+        </is>
+      </c>
+      <c r="G88" s="29" t="inlineStr">
+        <is>
+          <t>UAT 时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1" s="18">
+      <c r="A89" s="43" t="n"/>
+      <c r="B89" s="43" t="n"/>
+      <c r="C89" s="43" t="n"/>
+      <c r="D89" s="44" t="n"/>
+      <c r="E89" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 正式主持（签字）</t>
+        </is>
+      </c>
+      <c r="F89" s="43" t="n"/>
+      <c r="G89" s="43" t="n"/>
+    </row>
+    <row r="90" ht="22" customHeight="1" s="18">
+      <c r="A90" s="43" t="n"/>
+      <c r="B90" s="43" t="n"/>
+      <c r="C90" s="43" t="n"/>
+      <c r="D90" s="44" t="n"/>
+      <c r="E90" s="41" t="inlineStr">
+        <is>
+          <t>• 上线后反馈分诊</t>
+        </is>
+      </c>
+      <c r="F90" s="43" t="n"/>
+      <c r="G90" s="43" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1" s="18">
+      <c r="A91" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B91" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D91" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E91" s="41" t="inlineStr">
+        <is>
+          <t>• R2 生产发布（增量发布不中断 R1）</t>
+        </is>
+      </c>
+      <c r="F91" s="42" t="inlineStr">
+        <is>
+          <t>★ Go-Live #2</t>
+        </is>
+      </c>
+      <c r="G91" s="29" t="inlineStr"/>
+    </row>
+    <row r="92" ht="22" customHeight="1" s="18">
+      <c r="A92" s="43" t="n"/>
+      <c r="B92" s="43" t="n"/>
+      <c r="C92" s="43" t="n"/>
+      <c r="D92" s="46" t="n"/>
+      <c r="E92" s="41" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移收尾+终版对账</t>
+        </is>
+      </c>
+      <c r="F92" s="43" t="n"/>
+      <c r="G92" s="43" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1" s="18">
+      <c r="A93" s="43" t="n"/>
+      <c r="B93" s="43" t="n"/>
+      <c r="C93" s="43" t="n"/>
+      <c r="D93" s="46" t="n"/>
+      <c r="E93" s="41" t="inlineStr">
+        <is>
+          <t>• P1 当日清 + 48h 值守 + 交付物 tag</t>
+        </is>
+      </c>
+      <c r="F93" s="43" t="n"/>
+      <c r="G93" s="43" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1" s="18">
+      <c r="A94" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B94" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D94" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E94" s="41" t="inlineStr">
+        <is>
+          <t>• 审批材料提交（完整版）</t>
+        </is>
+      </c>
+      <c r="F94" s="42" t="inlineStr">
+        <is>
+          <t>★ Release 2 交付完成</t>
+        </is>
+      </c>
+      <c r="G94" s="29" t="inlineStr">
+        <is>
+          <t>审批受理</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1" s="18">
+      <c r="A95" s="43" t="n"/>
+      <c r="B95" s="43" t="n"/>
+      <c r="C95" s="43" t="n"/>
+      <c r="D95" s="48" t="n"/>
+      <c r="E95" s="41" t="inlineStr">
+        <is>
+          <t>• 文档终版归档（7 套）</t>
+        </is>
+      </c>
+      <c r="F95" s="43" t="n"/>
+      <c r="G95" s="43" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1" s="18">
+      <c r="A96" s="43" t="n"/>
+      <c r="B96" s="43" t="n"/>
+      <c r="C96" s="43" t="n"/>
+      <c r="D96" s="48" t="n"/>
+      <c r="E96" s="41" t="inlineStr">
+        <is>
+          <t>• 上线验证与稳定性报告 → 项目结束</t>
+        </is>
+      </c>
+      <c r="F96" s="43" t="n"/>
+      <c r="G96" s="43" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/report/Team1.xlsx
+++ b/report/Team1.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
@@ -396,8 +396,14 @@
       <color rgb="007c3aed"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00ca8a04"/>
+      <sz val="9.199999999999999"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="48">
     <fill>
       <patternFill/>
     </fill>
@@ -666,6 +672,11 @@
         <fgColor rgb="00FFEDD5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -1022,7 +1033,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1163,6 +1174,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="43" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="47" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2093,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" style="18" min="1" max="1"/>
@@ -2109,14 +2123,14 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>B2 湖仓归档平台 · 3 人团队执行计划（BA + Dev + QA · 双 Release 对半 · AI Vibe Coding）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="18">
+          <t>B2 湖仓归档平台 · 3 人团队执行计划 V2（14 周 · 双 Release · AI Vibe Coding）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1" s="18">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>R1 归档检索平台（W1~W6）：存量迁移 + 检索/权限/审计 → W6 Go-Live #1 · R2 治理合规完整版（W7~W12）：治理/生命周期/安全/合规报表 + 全量迁移 + 文档 → W12 Go-Live #2 + 项目结束 · CC（Caring Center）单系统贯穿验证</t>
+          <t>V2 调整：原 W3~W5 工作过载，拆为「功能开发（W3~W4）+ DevOps与就绪（W5~W6）」两个 Sprint，R1 上线移至 W7；R2 同理多拆一周，上线 W14。R1 = W1~W7 / R2 = W8~W14（各 +1 周，共 14 周）· CC 单系统贯穿</t>
         </is>
       </c>
     </row>
@@ -2187,22 +2201,22 @@
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>【BA】① BRD 定稿（数据流图+保留期矩阵+PII 分级+检索权限矩阵）② CC 垃圾表剔除标准与首批 50 表清单确认 【DEV-Wade】③ 架构定稿 + 资源申请（区域=境内）+ 资源验收 + UC 初始化（arch_cc）④ 前后端骨架 + Azure DevOps Pipelines CI ⑤ SeaTunnel PoC（CC 抽样 10 表端到端）+ 1253 表扫描分类 ⑥【01】首批 50 表批量导入（分片/限速/断点）+ 配置生成器 v1 【QA】⑦ 测试计划（8 域）+ 架构图×2（上下文/容器）+ 文档模板 ⑧ 迁移对账测试设计</t>
+          <t>【BA】① BRD 定稿（数据流图+保留期矩阵+PII 分级+检索权限矩阵）② CC 垃圾表标准与首批 50 表清单 【DEV】③ 架构定稿+资源申请+验收+UC 初始化 ④ 前后端骨架+CI 骨架 ⑤ SeaTunnel PoC（10 表端到端）+ 1253 表分类 ⑥【01】50 表批量导入+生成器 v1 【QA】⑦ 测试计划（8 域）+ 架构图×2 + 文档模板</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>★ W2：CC PoC 端到端 + BRD 签字 + 50 表入 RAW + 登录页可访问</t>
+          <t>★ W2：PoC 端到端 + BRD 签字 + 50 表入 RAW</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
-          <t>CC 账号/白名单周期；Wade 一人扛三角色串行风险；1253 表审表量</t>
+          <t>CC 账号周期；Wade 串行压力</t>
         </is>
       </c>
       <c r="H5" s="30" t="inlineStr">
         <is>
-          <t>① CC 只读账号（W1）② 垃圾表标准 ③ 50 表清单（W2 末）</t>
+          <t>① CC 账号 ② 垃圾表标准 ③ 50 表清单</t>
         </is>
       </c>
     </row>
@@ -2216,37 +2230,37 @@
       <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Sprint 2
-检索增强+就绪</t>
+检索与权限</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>W3~W5</t>
+          <t>W3~W4</t>
         </is>
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>检索/权限/审计端到端 + R1 上线就绪</t>
+          <t>检索/权限/审计 功能开发（纯功能，不做上线准备）</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>【DEV-Wade】【05】① 配置化检索页 + 预览（SAS）+ 导出【08】② RBAC 五角色 + UC GRANT + 掩码函数（权限三态）③ SSO JWT Claims ④【06】审计埋点【07】⑤ 连接器模板 v1 ⑥ SERVE 热表物化【安全】⑦ 四道 CI 门禁 【BA】⑧ PII 字段标记 + 预览范围确认 ⑨ R1 验收 + UAT #1 脚本【QA】⑩ 功能/安全测试执行 ⑪ R1 文档 50%（用户手册检索章节）【就绪 W5】⑫ 发布包+回退演练+UAT 预演+迁移预跑+就绪检查</t>
+          <t>【DEV】【05】① 配置化检索页 ② 预览（SAS）③ 导出【08】④ RBAC 五角色 CRUD+鉴权 ⑤ UC GRANT+掩码函数（权限三态）⑥ SERVE 物化 【06】⑦ 审计埋点【07】⑧ 连接器模板 v1【安全】⑨ 依赖扫描+SAST 门禁 【BA】⑩ PII 字段标记+预览范围 ⑪ R1 功能验收 【QA】⑫ 功能/安全测试 ⑬ 文档 50%</t>
         </is>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>★ W5 末：R1 上线就绪检查 100%（发布包/预演/回退/预跑全绿）</t>
+          <t>★ W4：R1 功能全部 Done（登录→检索→预览→导出+权限三态）</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
         <is>
-          <t>Wade 任务密度最高的一段；权限三态联调复杂</t>
+          <t>功能密度仍高但不再混上线准备；掩码/三态是硬骨头</t>
         </is>
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>① PII 标记（W3）② 性能标准 P95&lt;5s ③ UAT 预演排期</t>
+          <t>① PII 标记（W3）② 性能标准</t>
         </is>
       </c>
     </row>
@@ -2257,219 +2271,263 @@
 归档检索平台</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Sprint 2
-检索增强+就绪</t>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>Sprint 3
+DevOps+R1就绪</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5~W6</t>
         </is>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
-          <t>R1 上线周：发布 → UAT → Go-Live #1</t>
+          <t>DevOps + R1 上线就绪（独立 Sprint，不再挤占功能期）</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>【DEV】① 生产发布（就绪包一键发布+Environments 审批）② CC 50 表生产迁移+对账 ③ P1 当日清 【BA】④ UAT #1 正式主持（检索/预览/导出/权限/SSO/审计 → 签字）⑤ Go/No-Go 需求侧 【QA】⑥ 上线记录 + R1 审批材料提交 ⑦ 48h 值守三角色轮值</t>
+          <t>【DEV·DevOps】① CD 流水线完善（Helm 多环境 Dev/Staging/Prod + Environments 审批流）② 四道安全门禁全量上线（gitleaks/Trivy）③ 生产发布包（一键发布就绪）④ 回退预案与演练 ⑤ 监控告警就绪（App Insights+Dashboard）⑥ CC 迁移预跑+Runbook 【BA】⑦ UAT #1 脚本+预演主持 【QA】⑧ R1 文档冲刺（用户手册/运维手册 70%）⑨ 上线 Checklist ⑩ W6 末就绪检查</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>★ W6：Go-Live #1 —— CC 可查、有权限、有审计（Release 1 交付）</t>
+          <t>★ W6 末：R1 就绪检查 100%（DevOps 就绪/预演/回退/预跑全绿）</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>三人全上线值守（轮值缓解）；审批受理时长</t>
+          <t>DevOps 环境问题（AKS 权限/ACR 网络）；预演排期</t>
         </is>
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>① Go-Live #1 窗口 ② UAT #1 签字人</t>
+          <t>① 生产环境权限 ② 预演排期 ③ 迁移窗口</t>
         </is>
       </c>
     </row>
     <row r="8" ht="132" customHeight="1" s="18">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Release 1
+归档检索平台</t>
+        </is>
+      </c>
+      <c r="B8" s="50" t="inlineStr">
+        <is>
+          <t>Sprint 3
+DevOps+R1就绪</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>R1 上线周：发布 → UAT → Go-Live #1（仅执行）</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>【DEV】① 生产发布（就绪包+审批）② CC 50 表生产迁移+对账 ③ P1 当日清 【BA】④ UAT #1 正式主持（签字）⑤ Go/No-Go 【QA】⑥ 上线记录+R1 审批材料提交 ⑦ 48h 值守三角色轮值</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>★ W7：Go-Live #1 —— CC 可查、有权限、有审计（Release 1 交付）</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>依赖 W6 就绪检查通过</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>① Go 窗口 ② UAT 签字人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="132" customHeight="1" s="18">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Release 2
 治理合规完整版</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>Sprint 3
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Sprint 4
 治理+安全</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>W7~W9</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>治理 + 生命周期 + 安全管控（R2 功能主体）</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>【DEV-Wade】【02】① 增量接入（watermark）+ 冷数据自动转冷 ② 元数据标准界面 【03】③ 处置引擎（DROP PARTITION+VACUUM）+ Legal Hold + 归档模型 ④ 处置/Hold 界面 【04】⑤ 加密（CMK+字段级+轮转）+ 脱敏 + 境内驻留核查 ⑥ ADLS 分层+生命周期+Compaction 【07】⑦ 连接器模板库（MySQL+文件源）+ 连接管理界面【08】⑧ 行级隔离验证 【BA】⑨ Legal Hold 触发条件定稿（法务）⑩ 增量频率/冷数据标准 【QA】⑪ 处置全链路 E2E（1 天保留期→到期→Hold→处置→审计）⑫ 掩码旁路/越权测试 ⑬ 文档 60%</t>
-        </is>
-      </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>★ W8：处置全链路通过+脱敏三态+驻留核查；★ W9：越权全拦截+新源 30 分钟接入</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>处置不可逆需沙箱验证；加密/驻留须人工复核（Wade 自查=风险）</t>
-        </is>
-      </c>
-      <c r="H8" s="30" t="inlineStr">
-        <is>
-          <t>① Legal Hold 审批人 ② 保留期底线 ③ 实时指标验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="132" customHeight="1" s="18">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>W8~W9</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>治理 + 生命周期 + 安全管控（R2 功能主体一）</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>【DEV】【02】① 增量接入+冷数据转冷 ② 元数据标准界面【03】③ 处置引擎+Legal Hold+归档模型 ④ 处置/Hold 界面 【04】⑤ 加密+脱敏+驻留核查 ⑥ ADLS 分层+Compaction【07】⑦ 连接器模板库 【BA】⑧ Hold 条件定稿（法务）【QA】⑨ 处置 E2E+安全测试 ⑩ 文档 60%</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>★ W9：处置全链路+脱敏三态+驻留核查通过</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>处置不可逆；加密需人工复核</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>① Hold 审批人 ② 保留期底线 ③ 实时指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="132" customHeight="1" s="18">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Release 2
 治理合规完整版</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>Sprint 4
-全量+合规+就绪</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>W10~W11</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>CC 全量迁移 + 合规报表 + R2 上线就绪</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>【DEV-Wade】【01】① CC 全量 1253 表分批迁移（600~800 有效表）+ 逐批对账 【06】② 合规报表（等保/个保法对照+导出）③ 全量回归（R1+R2）④ R2 发布包+回退演练 ⑤ 安全终检（四门禁+渗透配合）⑥ 迁移预跑+窗口预约 【BA】⑦ 全量范围最终确认（签字）⑧ 合规报表口径对齐（法务）⑨ UAT #2 脚本 【QA】⑩ 文档冲刺（7 套 80%→终稿）+ 审批材料 ⑪ 连接器兼容矩阵 + 口径验证 ⑫ W11 末就绪检查</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>★ W10：CC 全量对账 100%；★ W11 末：R2 就绪检查 100%</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t>全量迁移时长不可控；文档冲刺与就绪并行（QA 压力最大）</t>
-        </is>
-      </c>
-      <c r="H9" s="30" t="inlineStr">
-        <is>
-          <t>① CC 数据量实测 ② 迁移窗口 ③ 报表口径签字人</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="132" customHeight="1" s="18">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 5
+全量+合规+R2就绪</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>W10~W13</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>CC 全量 + 合规报表 + 连接器完善 + R2 就绪（多一周，不再挤）</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>【DEV】【01】① CC 全量 1253 表分批迁移+逐批对账【06】② 合规报表【07】③ 连接器运行监控+连接管理界面【08】④ 行级隔离验证 【就绪 W12~13】⑤ 全量回归（R1+R2）⑥ R2 发布包+回退演练 ⑦ 安全终检（四门禁+渗透）⑧ 迁移预跑+窗口预约 【BA】⑨ 全量范围签字 ⑩ 报表口径对齐 ⑪ UAT #2 脚本+预演 【QA】⑫ 文档冲刺（7 套终稿）+审批材料 ⑬ 兼容矩阵 ⑭ W13 末就绪检查</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>★ W11：全量对账 100%；★ W13 末：R2 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>全量迁移时长；文档冲刺与就绪并行</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>① 数据量实测 ② 迁移窗口 ③ 报表口径签字</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="132" customHeight="1" s="18">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Release 2
 治理合规完整版</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>Sprint 4
-全量+合规+就绪</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 5
+全量+合规+R2就绪</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>R2 上线周 + 收尾：Go-Live #2 → 项目结束</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>【DEV】① R2 生产发布（治理/安全/合规，增量发布不中断 R1）② CC 生产全量迁移收尾+终版对账 ③ P1 当日清 【BA】④ UAT #2 正式主持（处置/Hold/脱敏/报表 → 签字）⑤ Go/No-Go 【QA】⑥ 审批材料提交（完整版）⑦ 文档终版归档（7 套）⑧ 上线验证与稳定性报告 → 项目结束</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>★ W12：Go-Live #2（完整版）+ 交付物归档 → 项目结束</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="inlineStr">
-        <is>
-          <t>上线+文档+收尾三线并行在 W12；全量迁移收尾跨窗口</t>
-        </is>
-      </c>
-      <c r="H10" s="30" t="inlineStr">
-        <is>
-          <t>① Go-Live #2 窗口 ② UAT #2 签字人 ③ 文档确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1" s="18">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>团队：3 人 —— BA（Mandy，50% 投入）/ DEV（Wade，全职，承担架构+数据工程+全栈 DevOps 三角色）/ QA（全职，测试+SLC 文档）</t>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>【DEV】① R2 生产发布（增量不中断 R1）② CC 生产全量迁移收尾+终版对账 ③ P1 当日清 【BA】④ UAT #2 正式主持（签字）⑤ Go/No-Go 【QA】⑥ 审批材料提交 ⑦ 文档终版归档（7 套）⑧ 稳定性报告 → 项目结束</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>★ W14：Go-Live #2（完整版）+ 交付物归档 → 项目结束</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>上线+文档+收尾并行；迁移收尾跨窗口</t>
+        </is>
+      </c>
+      <c r="H11" s="30" t="inlineStr">
+        <is>
+          <t>① Go 窗口 ② UAT 签字人 ③ 文档确认</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" s="18">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>结构：双 Release 对半（R1 W1~W6 / R2 W7~W12），各自"功能→就绪→上线"闭环，上线各占最后一周（W6/W12）</t>
+          <t>V2 变更：原「W3~W5 检索增强+就绪」一个 Sprint 拆为两个 —— S2 功能开发（W3~W4，纯功能）+ S3 DevOps与就绪（W5~W6），R1 上线 W7</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1" s="18">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>人天：BA 20 + DEV 100 + QA 30 = 150 人天（12 周）；人力费用 = 132,000 + 390,000 + 75,000 = ¥597,000（按 Team1 表单价）</t>
+          <t>R2 同理：原「W10~W11 全量+就绪」扩为 W10~W13（多一周），R2 上线 W14。总工期 12 → 14 周（+2 周）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1" s="18">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>与 5 人版差异：DEV 集中 Wade 一人（风险↑），用 AI Vibe Coding 提效；BA 兼测试协调；无独立架构评审——建议 W1/W5 两个节点请平台团队做外部 sanity check</t>
+          <t>人天口径：仍按 Team1 表（BA 20 + DEV 100 + QA 30 = 150 人天）；+2 周主要为 DevOps/就绪/缓冲的节奏舒展，不增功能范围</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1" s="18">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>W7~W11 期间 R1 已在生产运行，R2 上线为增量发布不中断服务</t>
+          <t>团队与风险不变：Mandy·BA（50%）/ Wade·DEV（全开发，🤖 AI 提效）/ QA；无独立架构评审——W1/W5/W12 三个节点请平台团队外部 sanity check</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1" s="18">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>上线只占 W7 / W14 最后一周；W8~W13 期间 R1 已在生产运行，R2 增量发布不中断服务</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2481,14 +2539,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="18" min="1" max="1"/>
     <col width="8" customWidth="1" style="18" min="2" max="2"/>
     <col width="6" customWidth="1" style="18" min="3" max="3"/>
     <col width="13" customWidth="1" style="18" min="4" max="4"/>
-    <col width="66" customWidth="1" style="18" min="5" max="5"/>
+    <col width="64" customWidth="1" style="18" min="5" max="5"/>
     <col width="26" customWidth="1" style="18" min="6" max="6"/>
     <col width="20" customWidth="1" style="18" min="7" max="7"/>
   </cols>
@@ -2496,14 +2554,14 @@
     <row r="1">
       <c r="A1" s="36" t="inlineStr">
         <is>
-          <t>周计划明细 · 3 人 × 12 周（BA·Mandy / DEV·Wade / QA · 双 Release · 上线仅 W6/W12）</t>
+          <t>周计划明细 · 3 人 × 14 周（W3~W4 纯功能 / W5~W6 DevOps就绪 / W7 上线 · R2 同理 / W14 上线收尾）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>🤖 = AI Vibe Coding 提效标注（主要落在 DEV-Wade 任务）· 外部依赖为不可压缩物理时间</t>
+          <t>🤖 = AI 提效标注 · BA·Mandy / DEV·Wade / QA · 外部依赖为不可压缩时间</t>
         </is>
       </c>
     </row>
@@ -2567,12 +2625,12 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>• 【8 域需求访谈】业务方×2 场 + 合规法务×1 场（保留期/PII/Legal Hold）</t>
+          <t>• 【8 域需求访谈】业务方×2 + 合规法务×1（保留期/PII/Legal Hold）</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>BRD 初稿；CC 剔除规则</t>
+          <t>BRD 初稿；剔除规则</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -2588,7 +2646,7 @@
       <c r="D6" s="44" t="n"/>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 BRD 起稿：数据流图 + 归档范围矩阵 + PII 分级 + 检索权限矩阵</t>
+          <t>• 🤖 BRD 起稿：数据流图+归档范围矩阵+PII 分级+检索权限矩阵</t>
         </is>
       </c>
       <c r="F6" s="43" t="n"/>
@@ -2601,7 +2659,7 @@
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>• CC 接入范围初定：1253 表垃圾表剔除标准与业务方对齐</t>
+          <t>• CC 垃圾表剔除标准与业务方对齐</t>
         </is>
       </c>
       <c r="F7" s="43" t="n"/>
@@ -2630,12 +2688,12 @@
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>• 架构文档定稿（湖仓分层+UC 授权+存储分层）+ 资源申请单（区域=境内）</t>
+          <t>• 架构文档定稿 + 资源申请单（区域=境内）+ CC 账号/白名单申请（D1）</t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t>架构 V1；申请单；骨架+CI</t>
+          <t>架构 V1；骨架+CI</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
@@ -2651,20 +2709,20 @@
       <c r="D9" s="46" t="n"/>
       <c r="E9" s="41" t="inlineStr">
         <is>
-          <t>• CC 只读账号 + NAT 白名单申请（D1 启动）</t>
+          <t>• 🤖 CC 1253 表扫描分类脚本</t>
         </is>
       </c>
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="18">
+    <row r="10" ht="22" customHeight="1" s="18">
       <c r="A10" s="43" t="n"/>
       <c r="B10" s="43" t="n"/>
       <c r="C10" s="43" t="n"/>
       <c r="D10" s="46" t="n"/>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 CC 1253 表扫描分类脚本 + 前后端骨架 + Azure DevOps Pipelines CI</t>
+          <t>• 🤖 前后端骨架 + CI 骨架（build+单测+推镜像）</t>
         </is>
       </c>
       <c r="F10" s="43" t="n"/>
@@ -2693,7 +2751,7 @@
       </c>
       <c r="E11" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 测试计划初稿（按 8 域组织：迁移/治理/生命周期/安全/检索/合规/连接器/权限）</t>
+          <t>• 🤖 测试计划初稿（8 域）</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
@@ -2701,11 +2759,7 @@
           <t>测试计划；架构图×2</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
-        <is>
-          <t>BA 的 BRD 范围</t>
-        </is>
-      </c>
+      <c r="G11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1" s="18">
       <c r="A12" s="43" t="n"/>
@@ -2714,7 +2768,7 @@
       <c r="D12" s="48" t="n"/>
       <c r="E12" s="41" t="inlineStr">
         <is>
-          <t>• 架构图初稿：上下文图 + 容器图</t>
+          <t>• 架构图初稿：上下文+容器图</t>
         </is>
       </c>
       <c r="F12" s="43" t="n"/>
@@ -2727,7 +2781,7 @@
       <c r="D13" s="48" t="n"/>
       <c r="E13" s="41" t="inlineStr">
         <is>
-          <t>• 文档模板 4 套定稿</t>
+          <t>• 文档模板 4 套</t>
         </is>
       </c>
       <c r="F13" s="43" t="n"/>
@@ -2756,7 +2810,7 @@
       </c>
       <c r="E14" s="41" t="inlineStr">
         <is>
-          <t>• BRD 评审 → 定稿签字</t>
+          <t>• BRD 评审→定稿签字</t>
         </is>
       </c>
       <c r="F14" s="42" t="inlineStr">
@@ -2777,7 +2831,7 @@
       <c r="D15" s="44" t="n"/>
       <c r="E15" s="41" t="inlineStr">
         <is>
-          <t>• CC 首批 50 张热表清单确认（业务方勾选）</t>
+          <t>• CC 首批 50 张热表清单确认</t>
         </is>
       </c>
       <c r="F15" s="43" t="n"/>
@@ -2806,7 +2860,7 @@
       </c>
       <c r="E16" s="41" t="inlineStr">
         <is>
-          <t>• 平台交付资源验收 + UC 初始化（arch_cc + GRANT 模板 + SP）</t>
+          <t>• 平台资源验收 + UC 初始化（arch_cc+GRANT+SP）</t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
@@ -2820,14 +2874,14 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="18">
+    <row r="17" ht="22" customHeight="1" s="18">
       <c r="A17" s="43" t="n"/>
       <c r="B17" s="43" t="n"/>
       <c r="C17" s="43" t="n"/>
       <c r="D17" s="46" t="n"/>
       <c r="E17" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 SeaTunnel PoC：抽样 10 表 → RAW → SQL Warehouse 可查</t>
+          <t>• 🤖 SeaTunnel PoC：抽样 10 表端到端</t>
         </is>
       </c>
       <c r="F17" s="43" t="n"/>
@@ -2840,7 +2894,7 @@
       <c r="D18" s="46" t="n"/>
       <c r="E18" s="41" t="inlineStr">
         <is>
-          <t>• 【01】50 表批量导入（分片/限速/断点）+ 配置生成器 v1</t>
+          <t>• 【01】50 表批量导入 + 配置生成器 v1</t>
         </is>
       </c>
       <c r="F18" s="43" t="n"/>
@@ -2869,7 +2923,7 @@
       </c>
       <c r="E19" s="41" t="inlineStr">
         <is>
-          <t>• 架构图完善：组件图 + 部署图</t>
+          <t>• 架构图完善：组件+部署图</t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
@@ -2886,7 +2940,7 @@
       <c r="D20" s="48" t="n"/>
       <c r="E20" s="41" t="inlineStr">
         <is>
-          <t>• 【01】迁移对账测试设计（行数/校验和）</t>
+          <t>• 【01】对账测试设计</t>
         </is>
       </c>
       <c r="F20" s="43" t="n"/>
@@ -2932,7 +2986,7 @@
       <c r="D22" s="44" t="n"/>
       <c r="E22" s="41" t="inlineStr">
         <is>
-          <t>• 预览格式范围确认（图片/音频/视频）</t>
+          <t>• 预览格式范围确认</t>
         </is>
       </c>
       <c r="F22" s="43" t="n"/>
@@ -2961,7 +3015,7 @@
       </c>
       <c r="E23" s="41" t="inlineStr">
         <is>
-          <t>• 【08】RBAC CRUD + OIDC/JWT 鉴权 + 前端权限渲染（🤖 AI 生成）</t>
+          <t>• 🤖【08】RBAC CRUD + OIDC/JWT 鉴权 + 前端权限渲染</t>
         </is>
       </c>
       <c r="F23" s="42" t="inlineStr">
@@ -2978,7 +3032,7 @@
       <c r="D24" s="46" t="n"/>
       <c r="E24" s="41" t="inlineStr">
         <is>
-          <t>• 【05】配置化检索页（动态筛选/表格/分页）</t>
+          <t>• 🤖【05】配置化检索页（动态筛选/表格/分页）</t>
         </is>
       </c>
       <c r="F24" s="43" t="n"/>
@@ -2991,7 +3045,7 @@
       <c r="D25" s="46" t="n"/>
       <c r="E25" s="41" t="inlineStr">
         <is>
-          <t>• 【06】审计埋点 v1 + 安全门禁①②进 CI</t>
+          <t>• 【06】审计埋点 v1</t>
         </is>
       </c>
       <c r="F25" s="43" t="n"/>
@@ -3020,7 +3074,7 @@
       </c>
       <c r="E26" s="41" t="inlineStr">
         <is>
-          <t>• 单测框架 + 覆盖率门禁 &gt;70% 进 CI</t>
+          <t>• 单测框架+覆盖率门禁 &gt;70%</t>
         </is>
       </c>
       <c r="F26" s="42" t="inlineStr">
@@ -3041,7 +3095,7 @@
       <c r="D27" s="48" t="n"/>
       <c r="E27" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 API 集成测试 10 场景（AI 生成用例）</t>
+          <t>• 🤖 API 集成测试 10 场景</t>
         </is>
       </c>
       <c r="F27" s="43" t="n"/>
@@ -3070,12 +3124,12 @@
       </c>
       <c r="E28" s="41" t="inlineStr">
         <is>
-          <t>• R1 核心场景验收（检索/预览/导出/权限三态对照用户故事）</t>
+          <t>• R1 功能验收（检索/预览/导出/权限三态）</t>
         </is>
       </c>
       <c r="F28" s="42" t="inlineStr">
         <is>
-          <t>R1 验收记录</t>
+          <t>R1 功能验收记录</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr"/>
@@ -3093,7 +3147,7 @@
       <c r="F29" s="43" t="n"/>
       <c r="G29" s="43" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1" s="18">
+    <row r="30" ht="22" customHeight="1" s="18">
       <c r="A30" s="38" t="inlineStr">
         <is>
           <t>R1</t>
@@ -3116,12 +3170,12 @@
       </c>
       <c r="E30" s="41" t="inlineStr">
         <is>
-          <t>• 【08】UC GRANT 落地 + 掩码函数（aes_encrypt+COLUMN MASK）+ 权限三态联调</t>
+          <t>• 【08】UC GRANT+掩码函数+权限三态联调</t>
         </is>
       </c>
       <c r="F30" s="42" t="inlineStr">
         <is>
-          <t>权限三态通过；预览/导出可用</t>
+          <t>★ R1 功能全部 Done</t>
         </is>
       </c>
       <c r="G30" s="29" t="inlineStr"/>
@@ -3133,7 +3187,7 @@
       <c r="D31" s="46" t="n"/>
       <c r="E31" s="41" t="inlineStr">
         <is>
-          <t>• 【05】SERVE 热表物化 + 预览（SAS）+ 导出</t>
+          <t>• 【05】SERVE 物化+预览（SAS）+导出</t>
         </is>
       </c>
       <c r="F31" s="43" t="n"/>
@@ -3146,7 +3200,7 @@
       <c r="D32" s="46" t="n"/>
       <c r="E32" s="41" t="inlineStr">
         <is>
-          <t>• 安全修复 High 清零</t>
+          <t>• 安全门禁①②上线 + High 清零</t>
         </is>
       </c>
       <c r="F32" s="43" t="n"/>
@@ -3175,7 +3229,7 @@
       </c>
       <c r="E33" s="41" t="inlineStr">
         <is>
-          <t>• 功能测试执行 + Bug 跟踪</t>
+          <t>• 功能测试执行+Bug 跟踪</t>
         </is>
       </c>
       <c r="F33" s="42" t="inlineStr">
@@ -3192,7 +3246,7 @@
       <c r="D34" s="48" t="n"/>
       <c r="E34" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 安全测试①：注入/XSS/越权用例</t>
+          <t>• 🤖 安全测试①：注入/XSS/越权</t>
         </is>
       </c>
       <c r="F34" s="43" t="n"/>
@@ -3219,7 +3273,7 @@
       </c>
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
@@ -3234,17 +3288,17 @@
       </c>
       <c r="E36" s="41" t="inlineStr">
         <is>
-          <t>• UAT #1 预演主持（Staging：检索/权限/审计场景）</t>
+          <t>• UAT #1 脚本定稿</t>
         </is>
       </c>
       <c r="F36" s="42" t="inlineStr">
         <is>
-          <t>预演完成</t>
+          <t>UAT #1 脚本</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>业务方预演排期</t>
+          <t>业务方排期</t>
         </is>
       </c>
     </row>
@@ -3255,13 +3309,13 @@
       <c r="D37" s="44" t="n"/>
       <c r="E37" s="41" t="inlineStr">
         <is>
-          <t>• 预演反馈分类与裁决</t>
+          <t>• 预演协调（业务方排期）</t>
         </is>
       </c>
       <c r="F37" s="43" t="n"/>
       <c r="G37" s="43" t="n"/>
     </row>
-    <row r="38" ht="22" customHeight="1" s="18">
+    <row r="38" ht="30" customHeight="1" s="18">
       <c r="A38" s="38" t="inlineStr">
         <is>
           <t>R1</t>
@@ -3269,7 +3323,7 @@
       </c>
       <c r="B38" s="39" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
@@ -3284,17 +3338,17 @@
       </c>
       <c r="E38" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 R1 发布包（Helm 生产 values + UC 生产脚本）+ 回退演练</t>
+          <t>• 【DevOps】CD 流水线完善：Helm 多环境（Dev/Staging/Prod）+ Environments 审批流</t>
         </is>
       </c>
       <c r="F38" s="42" t="inlineStr">
         <is>
-          <t>发布包就绪；预跑完成</t>
+          <t>CD 就绪；发布包 v1</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>生产窗口审批</t>
+          <t>生产环境权限</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3359,7 @@
       <c r="D39" s="46" t="n"/>
       <c r="E39" s="41" t="inlineStr">
         <is>
-          <t>• CC 生产迁移预跑（50 表→Staging）+ Runbook</t>
+          <t>• 【DevOps】安全门禁③④上线（gitleaks+Trivy，四道全开）</t>
         </is>
       </c>
       <c r="F39" s="43" t="n"/>
@@ -3318,7 +3372,7 @@
       <c r="D40" s="46" t="n"/>
       <c r="E40" s="41" t="inlineStr">
         <is>
-          <t>• 功能收口：性能优化（P95&lt;5s）+ 遗留清零 + 监控告警就绪</t>
+          <t>• 🤖 生产发布包（Helm 生产 values+UC 生产脚本）</t>
         </is>
       </c>
       <c r="F40" s="43" t="n"/>
@@ -3332,7 +3386,7 @@
       </c>
       <c r="B41" s="39" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
@@ -3347,19 +3401,15 @@
       </c>
       <c r="E41" s="41" t="inlineStr">
         <is>
-          <t>• R1 文档冲刺：用户手册 50% + 运维手册 40%</t>
+          <t>• R1 文档冲刺：用户手册 60%</t>
         </is>
       </c>
       <c r="F41" s="42" t="inlineStr">
         <is>
-          <t>★ 就绪检查 100%</t>
-        </is>
-      </c>
-      <c r="G41" s="29" t="inlineStr">
-        <is>
-          <t>各角色材料</t>
-        </is>
-      </c>
+          <t>文档 60%</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1" s="18">
       <c r="A42" s="43" t="n"/>
@@ -3368,142 +3418,166 @@
       <c r="D42" s="48" t="n"/>
       <c r="E42" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 上线 Checklist v1 + UAT #1 脚本定稿</t>
+          <t>• 运维手册初稿（部署/监控部分）</t>
         </is>
       </c>
       <c r="F42" s="43" t="n"/>
       <c r="G42" s="43" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1" s="18">
-      <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="48" t="n"/>
+      <c r="A43" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E43" s="41" t="inlineStr">
         <is>
-          <t>• W5 末就绪检查组织（发布包/预演/回退/预跑）</t>
-        </is>
-      </c>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
+          <t>• UAT #1 预演主持（Staging：检索/权限/审计）</t>
+        </is>
+      </c>
+      <c r="F43" s="42" t="inlineStr">
+        <is>
+          <t>预演完成</t>
+        </is>
+      </c>
+      <c r="G43" s="29" t="inlineStr"/>
     </row>
     <row r="44" ht="22" customHeight="1" s="18">
-      <c r="A44" s="38" t="inlineStr">
+      <c r="A44" s="43" t="n"/>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="44" t="n"/>
+      <c r="E44" s="41" t="inlineStr">
+        <is>
+          <t>• 预演反馈裁决</t>
+        </is>
+      </c>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1" s="18">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="D44" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E44" s="41" t="inlineStr">
-        <is>
-          <t>• Go/No-Go #1 决策参与</t>
-        </is>
-      </c>
-      <c r="F44" s="42" t="inlineStr">
-        <is>
-          <t>★ UAT #1 签字</t>
-        </is>
-      </c>
-      <c r="G44" s="29" t="inlineStr">
-        <is>
-          <t>UAT 业务方时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1" s="18">
-      <c r="A45" s="43" t="n"/>
-      <c r="B45" s="43" t="n"/>
-      <c r="C45" s="43" t="n"/>
-      <c r="D45" s="44" t="n"/>
+      <c r="D45" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E45" s="41" t="inlineStr">
         <is>
-          <t>• UAT #1 正式主持（签字）</t>
-        </is>
-      </c>
-      <c r="F45" s="43" t="n"/>
-      <c r="G45" s="43" t="n"/>
+          <t>• 回退预案演练（发布回滚+UC 配置回滚）</t>
+        </is>
+      </c>
+      <c r="F45" s="42" t="inlineStr">
+        <is>
+          <t>回退演练过；预跑完成</t>
+        </is>
+      </c>
+      <c r="G45" s="29" t="inlineStr">
+        <is>
+          <t>生产窗口审批</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1" s="18">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="43" t="n"/>
       <c r="C46" s="43" t="n"/>
-      <c r="D46" s="44" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="41" t="inlineStr">
         <is>
-          <t>• 上线后用户反馈分诊</t>
+          <t>• 监控告警就绪（App Insights+Dashboard）</t>
         </is>
       </c>
       <c r="F46" s="43" t="n"/>
       <c r="G46" s="43" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1" s="18">
-      <c r="A47" s="38" t="inlineStr">
+      <c r="A47" s="43" t="n"/>
+      <c r="B47" s="43" t="n"/>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="46" t="n"/>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>• CC 迁移预跑（50 表→Staging）+ Runbook</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="43" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1" s="18">
+      <c r="A48" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B47" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="E47" s="41" t="inlineStr">
-        <is>
-          <t>• 生产发布执行（就绪包一键发布+审批）</t>
-        </is>
-      </c>
-      <c r="F47" s="42" t="inlineStr">
-        <is>
-          <t>★ Go-Live #1</t>
-        </is>
-      </c>
-      <c r="G47" s="29" t="inlineStr"/>
-    </row>
-    <row r="48" ht="22" customHeight="1" s="18">
-      <c r="A48" s="43" t="n"/>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E48" s="41" t="inlineStr">
         <is>
-          <t>• CC 50 表生产迁移+对账</t>
-        </is>
-      </c>
-      <c r="F48" s="43" t="n"/>
-      <c r="G48" s="43" t="n"/>
+          <t>• 上线 Checklist v1</t>
+        </is>
+      </c>
+      <c r="F48" s="42" t="inlineStr">
+        <is>
+          <t>★ R1 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>各角色材料</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1" s="18">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="43" t="n"/>
       <c r="C49" s="43" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="D49" s="48" t="n"/>
       <c r="E49" s="41" t="inlineStr">
         <is>
-          <t>• P1 当日清 + 48h 值守</t>
+          <t>• W6 末就绪检查组织（CD/发布包/预演/回退/预跑）</t>
         </is>
       </c>
       <c r="F49" s="43" t="n"/>
@@ -3517,32 +3591,32 @@
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="D50" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
         </is>
       </c>
       <c r="E50" s="41" t="inlineStr">
         <is>
-          <t>• 上线执行记录（Checklist 勾选）</t>
+          <t>• Go/No-Go #1 决策参与</t>
         </is>
       </c>
       <c r="F50" s="42" t="inlineStr">
         <is>
-          <t>★ Release 1 交付</t>
+          <t>★ UAT #1 签字</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>审批受理</t>
+          <t>UAT 业务方时间</t>
         </is>
       </c>
     </row>
@@ -3550,10 +3624,10 @@
       <c r="A51" s="43" t="n"/>
       <c r="B51" s="43" t="n"/>
       <c r="C51" s="43" t="n"/>
-      <c r="D51" s="48" t="n"/>
+      <c r="D51" s="44" t="n"/>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>• R1 审批材料提交</t>
+          <t>• UAT #1 正式主持（签字）</t>
         </is>
       </c>
       <c r="F51" s="43" t="n"/>
@@ -3563,19 +3637,19 @@
       <c r="A52" s="43" t="n"/>
       <c r="B52" s="43" t="n"/>
       <c r="C52" s="43" t="n"/>
-      <c r="D52" s="48" t="n"/>
+      <c r="D52" s="44" t="n"/>
       <c r="E52" s="41" t="inlineStr">
         <is>
-          <t>• 48h 值守轮值</t>
+          <t>• 上线后反馈分诊</t>
         </is>
       </c>
       <c r="F52" s="43" t="n"/>
       <c r="G52" s="43" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1" s="18">
-      <c r="A53" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
+      <c r="A53" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
@@ -3588,177 +3662,161 @@
           <t>W7</t>
         </is>
       </c>
-      <c r="D53" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D53" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>• 【02】增量频率与冷数据标准确认</t>
+          <t>• 生产发布执行（就绪包+审批）</t>
         </is>
       </c>
       <c r="F53" s="42" t="inlineStr">
         <is>
-          <t>R2 需求就绪</t>
-        </is>
-      </c>
-      <c r="G53" s="29" t="inlineStr">
-        <is>
-          <t>法务配合</t>
-        </is>
-      </c>
+          <t>★ Go-Live #1</t>
+        </is>
+      </c>
+      <c r="G53" s="29" t="inlineStr"/>
     </row>
     <row r="54" ht="22" customHeight="1" s="18">
       <c r="A54" s="43" t="n"/>
       <c r="B54" s="43" t="n"/>
       <c r="C54" s="43" t="n"/>
-      <c r="D54" s="44" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="41" t="inlineStr">
         <is>
-          <t>• 【03】Legal Hold 触发条件定稿（法务）</t>
+          <t>• CC 50 表生产迁移+对账</t>
         </is>
       </c>
       <c r="F54" s="43" t="n"/>
       <c r="G54" s="43" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1" s="18">
-      <c r="A55" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B55" s="39" t="inlineStr">
+      <c r="A55" s="43" t="n"/>
+      <c r="B55" s="43" t="n"/>
+      <c r="C55" s="43" t="n"/>
+      <c r="D55" s="46" t="n"/>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>• P1 当日清+48h 值守</t>
+        </is>
+      </c>
+      <c r="F55" s="43" t="n"/>
+      <c r="G55" s="43" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1" s="18">
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
+      <c r="C56" s="26" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="D55" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="E55" s="41" t="inlineStr">
-        <is>
-          <t>• 【03】处置引擎（扫描→DROP PARTITION→VACUUM）</t>
-        </is>
-      </c>
-      <c r="F55" s="42" t="inlineStr">
-        <is>
-          <t>处置引擎可跑；加密生效</t>
-        </is>
-      </c>
-      <c r="G55" s="29" t="inlineStr"/>
-    </row>
-    <row r="56" ht="22" customHeight="1" s="18">
-      <c r="A56" s="43" t="n"/>
-      <c r="B56" s="43" t="n"/>
-      <c r="C56" s="43" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="D56" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E56" s="41" t="inlineStr">
         <is>
-          <t>• 【04】加密体系（CMK+字段级+密钥轮转）</t>
-        </is>
-      </c>
-      <c r="F56" s="43" t="n"/>
-      <c r="G56" s="43" t="n"/>
+          <t>• 上线执行记录</t>
+        </is>
+      </c>
+      <c r="F56" s="42" t="inlineStr">
+        <is>
+          <t>★ Release 1 交付</t>
+        </is>
+      </c>
+      <c r="G56" s="29" t="inlineStr">
+        <is>
+          <t>审批受理</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1" s="18">
       <c r="A57" s="43" t="n"/>
       <c r="B57" s="43" t="n"/>
       <c r="C57" s="43" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="D57" s="48" t="n"/>
       <c r="E57" s="41" t="inlineStr">
         <is>
-          <t>• 【02】增量接入（watermark）+ 冷数据自动转冷</t>
+          <t>• R1 审批材料提交</t>
         </is>
       </c>
       <c r="F57" s="43" t="n"/>
       <c r="G57" s="43" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1" s="18">
-      <c r="A58" s="49" t="inlineStr">
+      <c r="A58" s="43" t="n"/>
+      <c r="B58" s="43" t="n"/>
+      <c r="C58" s="43" t="n"/>
+      <c r="D58" s="48" t="n"/>
+      <c r="E58" s="41" t="inlineStr">
+        <is>
+          <t>• 48h 值守轮值</t>
+        </is>
+      </c>
+      <c r="F58" s="43" t="n"/>
+      <c r="G58" s="43" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1" s="18">
+      <c r="A59" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B58" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="D58" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E58" s="41" t="inlineStr">
-        <is>
-          <t>• 功能用例扩充（处置/Hold/增量/脱敏）</t>
-        </is>
-      </c>
-      <c r="F58" s="42" t="inlineStr">
-        <is>
-          <t>用例扩充</t>
-        </is>
-      </c>
-      <c r="G58" s="29" t="inlineStr"/>
-    </row>
-    <row r="59" ht="22" customHeight="1" s="18">
-      <c r="A59" s="43" t="n"/>
-      <c r="B59" s="43" t="n"/>
-      <c r="C59" s="43" t="n"/>
-      <c r="D59" s="48" t="n"/>
+      <c r="B59" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="D59" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E59" s="41" t="inlineStr">
         <is>
-          <t>• R1 上线后回归监控 + 文档推进（手册 60%）</t>
-        </is>
-      </c>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
+          <t>• 【02】增量频率与冷数据标准确认</t>
+        </is>
+      </c>
+      <c r="F59" s="42" t="inlineStr">
+        <is>
+          <t>R2 需求就绪</t>
+        </is>
+      </c>
+      <c r="G59" s="29" t="inlineStr">
+        <is>
+          <t>法务配合</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1" s="18">
-      <c r="A60" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B60" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
+      <c r="A60" s="43" t="n"/>
+      <c r="B60" s="43" t="n"/>
+      <c r="C60" s="43" t="n"/>
+      <c r="D60" s="44" t="n"/>
       <c r="E60" s="41" t="inlineStr">
         <is>
-          <t>• 验收处置全链路（对照合规要求）</t>
-        </is>
-      </c>
-      <c r="F60" s="42" t="inlineStr">
-        <is>
-          <t>处置验收</t>
-        </is>
-      </c>
-      <c r="G60" s="29" t="inlineStr"/>
+          <t>• 【03】Legal Hold 触发条件定稿（法务）</t>
+        </is>
+      </c>
+      <c r="F60" s="43" t="n"/>
+      <c r="G60" s="43" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1" s="18">
       <c r="A61" s="49" t="inlineStr">
@@ -3768,7 +3826,7 @@
       </c>
       <c r="B61" s="39" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
@@ -3783,12 +3841,12 @@
       </c>
       <c r="E61" s="41" t="inlineStr">
         <is>
-          <t>• 【03】Legal Hold（Hold/Release+豁免+留痕）+ 归档模型管理</t>
+          <t>• 【03】处置引擎（扫描→DROP PARTITION→VACUUM）</t>
         </is>
       </c>
       <c r="F61" s="42" t="inlineStr">
         <is>
-          <t>Hold 可用；分层生效</t>
+          <t>处置引擎可跑；加密生效</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr"/>
@@ -3800,7 +3858,7 @@
       <c r="D62" s="46" t="n"/>
       <c r="E62" s="41" t="inlineStr">
         <is>
-          <t>• 【04】境内驻留核查（区域+出口流量）</t>
+          <t>• 【04】加密体系（CMK+字段级+轮转）</t>
         </is>
       </c>
       <c r="F62" s="43" t="n"/>
@@ -3813,70 +3871,90 @@
       <c r="D63" s="46" t="n"/>
       <c r="E63" s="41" t="inlineStr">
         <is>
-          <t>• 【04】ADLS 分层+生命周期+Compaction</t>
+          <t>• 【02】增量接入（watermark）</t>
         </is>
       </c>
       <c r="F63" s="43" t="n"/>
       <c r="G63" s="43" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1" s="18">
-      <c r="A64" s="43" t="n"/>
-      <c r="B64" s="43" t="n"/>
-      <c r="C64" s="43" t="n"/>
-      <c r="D64" s="46" t="n"/>
+      <c r="A64" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B64" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="D64" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E64" s="41" t="inlineStr">
         <is>
-          <t>• 【07】连接器模板库（MySQL+文件源）</t>
-        </is>
-      </c>
-      <c r="F64" s="43" t="n"/>
-      <c r="G64" s="43" t="n"/>
+          <t>• 功能用例扩充（处置/Hold/增量/脱敏）</t>
+        </is>
+      </c>
+      <c r="F64" s="42" t="inlineStr">
+        <is>
+          <t>用例扩充</t>
+        </is>
+      </c>
+      <c r="G64" s="29" t="inlineStr"/>
     </row>
     <row r="65" ht="22" customHeight="1" s="18">
-      <c r="A65" s="49" t="inlineStr">
+      <c r="A65" s="43" t="n"/>
+      <c r="B65" s="43" t="n"/>
+      <c r="C65" s="43" t="n"/>
+      <c r="D65" s="48" t="n"/>
+      <c r="E65" s="41" t="inlineStr">
+        <is>
+          <t>• R1 生产回归监控</t>
+        </is>
+      </c>
+      <c r="F65" s="43" t="n"/>
+      <c r="G65" s="43" t="n"/>
+    </row>
+    <row r="66" ht="22" customHeight="1" s="18">
+      <c r="A66" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B65" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="D65" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E65" s="41" t="inlineStr">
-        <is>
-          <t>• 【03】处置全链路 E2E：1 天保留期→到期→Hold→处置→审计</t>
-        </is>
-      </c>
-      <c r="F65" s="42" t="inlineStr">
-        <is>
-          <t>处置 E2E 通过</t>
-        </is>
-      </c>
-      <c r="G65" s="29" t="inlineStr"/>
-    </row>
-    <row r="66" ht="22" customHeight="1" s="18">
-      <c r="A66" s="43" t="n"/>
-      <c r="B66" s="43" t="n"/>
-      <c r="C66" s="43" t="n"/>
-      <c r="D66" s="48" t="n"/>
+      <c r="B66" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="D66" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E66" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 安全测试②：掩码旁路/越权用例</t>
-        </is>
-      </c>
-      <c r="F66" s="43" t="n"/>
-      <c r="G66" s="43" t="n"/>
+          <t>• 验收处置全链路（对照合规）</t>
+        </is>
+      </c>
+      <c r="F66" s="42" t="inlineStr">
+        <is>
+          <t>处置验收</t>
+        </is>
+      </c>
+      <c r="G66" s="29" t="inlineStr"/>
     </row>
     <row r="67" ht="22" customHeight="1" s="18">
       <c r="A67" s="49" t="inlineStr">
@@ -3886,7 +3964,7 @@
       </c>
       <c r="B67" s="39" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C67" s="26" t="inlineStr">
@@ -3894,19 +3972,19 @@
           <t>W9</t>
         </is>
       </c>
-      <c r="D67" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D67" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E67" s="41" t="inlineStr">
         <is>
-          <t>• 合规报表口径与法务对齐</t>
+          <t>• 【03】Legal Hold+归档模型+处置界面</t>
         </is>
       </c>
       <c r="F67" s="42" t="inlineStr">
         <is>
-          <t>口径确认；范围签字</t>
+          <t>Hold 可用；分层生效</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr"/>
@@ -3915,73 +3993,69 @@
       <c r="A68" s="43" t="n"/>
       <c r="B68" s="43" t="n"/>
       <c r="C68" s="43" t="n"/>
-      <c r="D68" s="44" t="n"/>
+      <c r="D68" s="46" t="n"/>
       <c r="E68" s="41" t="inlineStr">
         <is>
-          <t>• CC 全量迁移范围最终确认（签字）</t>
+          <t>• 【04】驻留核查+ADLS 分层+Compaction</t>
         </is>
       </c>
       <c r="F68" s="43" t="n"/>
       <c r="G68" s="43" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1" s="18">
-      <c r="A69" s="49" t="inlineStr">
+      <c r="A69" s="43" t="n"/>
+      <c r="B69" s="43" t="n"/>
+      <c r="C69" s="43" t="n"/>
+      <c r="D69" s="46" t="n"/>
+      <c r="E69" s="41" t="inlineStr">
+        <is>
+          <t>• 【07】连接器模板库（MySQL+文件源）</t>
+        </is>
+      </c>
+      <c r="F69" s="43" t="n"/>
+      <c r="G69" s="43" t="n"/>
+    </row>
+    <row r="70" ht="22" customHeight="1" s="18">
+      <c r="A70" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B69" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C69" s="26" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="D69" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="E69" s="41" t="inlineStr">
-        <is>
-          <t>• 【08】行级隔离验证（越权全拦）</t>
-        </is>
-      </c>
-      <c r="F69" s="42" t="inlineStr">
-        <is>
-          <t>全量启动；越权拦截</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>CC 数据量实测</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1" s="18">
-      <c r="A70" s="43" t="n"/>
-      <c r="B70" s="43" t="n"/>
-      <c r="C70" s="43" t="n"/>
-      <c r="D70" s="46" t="n"/>
+      <c r="D70" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E70" s="41" t="inlineStr">
         <is>
-          <t>• 【01】CC 全量 1253 表分批迁移启动（600~800 有效表）</t>
-        </is>
-      </c>
-      <c r="F70" s="43" t="n"/>
-      <c r="G70" s="43" t="n"/>
+          <t>• 【03】处置全链路 E2E（1 天保留期→到期→Hold→处置→审计）</t>
+        </is>
+      </c>
+      <c r="F70" s="42" t="inlineStr">
+        <is>
+          <t>处置 E2E 通过</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr"/>
     </row>
     <row r="71" ht="22" customHeight="1" s="18">
       <c r="A71" s="43" t="n"/>
       <c r="B71" s="43" t="n"/>
       <c r="C71" s="43" t="n"/>
-      <c r="D71" s="46" t="n"/>
+      <c r="D71" s="48" t="n"/>
       <c r="E71" s="41" t="inlineStr">
         <is>
-          <t>• 【07】连接器运行监控与审计</t>
+          <t>• 🤖 安全测试②：掩码旁路/越权</t>
         </is>
       </c>
       <c r="F71" s="43" t="n"/>
@@ -3995,27 +4069,27 @@
       </c>
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="D72" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D72" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
         </is>
       </c>
       <c r="E72" s="41" t="inlineStr">
         <is>
-          <t>• 【07】连接器兼容性测试（SQL Server/MySQL 矩阵）</t>
+          <t>• 合规报表口径与法务对齐</t>
         </is>
       </c>
       <c r="F72" s="42" t="inlineStr">
         <is>
-          <t>兼容矩阵</t>
+          <t>口径确认；范围签字</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr"/>
@@ -4024,60 +4098,64 @@
       <c r="A73" s="43" t="n"/>
       <c r="B73" s="43" t="n"/>
       <c r="C73" s="43" t="n"/>
-      <c r="D73" s="48" t="n"/>
+      <c r="D73" s="44" t="n"/>
       <c r="E73" s="41" t="inlineStr">
         <is>
-          <t>• 【06】合规报表口径验证</t>
+          <t>• CC 全量范围最终确认（签字）</t>
         </is>
       </c>
       <c r="F73" s="43" t="n"/>
       <c r="G73" s="43" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1" s="18">
-      <c r="A74" s="43" t="n"/>
-      <c r="B74" s="43" t="n"/>
-      <c r="C74" s="43" t="n"/>
-      <c r="D74" s="48" t="n"/>
+      <c r="A74" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B74" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D74" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E74" s="41" t="inlineStr">
         <is>
-          <t>• 用户手册 70% + 数据字典初稿</t>
-        </is>
-      </c>
-      <c r="F74" s="43" t="n"/>
-      <c r="G74" s="43" t="n"/>
+          <t>• 【01】CC 全量 1253 表分批迁移启动（600~800 有效表）</t>
+        </is>
+      </c>
+      <c r="F74" s="42" t="inlineStr">
+        <is>
+          <t>全量启动</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t>CC 数据量实测</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1" s="18">
-      <c r="A75" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B75" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C75" s="26" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="D75" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
+      <c r="A75" s="43" t="n"/>
+      <c r="B75" s="43" t="n"/>
+      <c r="C75" s="43" t="n"/>
+      <c r="D75" s="46" t="n"/>
       <c r="E75" s="41" t="inlineStr">
         <is>
-          <t>• UAT #2 场景脚本定稿（处置/Hold/脱敏/报表）</t>
-        </is>
-      </c>
-      <c r="F75" s="42" t="inlineStr">
-        <is>
-          <t>UAT #2 脚本</t>
-        </is>
-      </c>
-      <c r="G75" s="29" t="inlineStr"/>
+          <t>• 【06】合规报表开发</t>
+        </is>
+      </c>
+      <c r="F75" s="43" t="n"/>
+      <c r="G75" s="43" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1" s="18">
       <c r="A76" s="49" t="inlineStr">
@@ -4087,7 +4165,7 @@
       </c>
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
@@ -4095,52 +4173,68 @@
           <t>W10</t>
         </is>
       </c>
-      <c r="D76" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
+      <c r="D76" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
         </is>
       </c>
       <c r="E76" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 R2 发布包（增量/处置/加密/分层生产版）+ 回退演练</t>
+          <t>• 【07】连接器兼容性测试</t>
         </is>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
-          <t>R2 发布包就绪</t>
-        </is>
-      </c>
-      <c r="G76" s="29" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
+          <t>兼容矩阵</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr"/>
     </row>
     <row r="77" ht="22" customHeight="1" s="18">
       <c r="A77" s="43" t="n"/>
       <c r="B77" s="43" t="n"/>
       <c r="C77" s="43" t="n"/>
-      <c r="D77" s="46" t="n"/>
+      <c r="D77" s="48" t="n"/>
       <c r="E77" s="41" t="inlineStr">
         <is>
-          <t>• 安全评审材料（技术说明）</t>
+          <t>• 用户手册 70%+数据字典初稿</t>
         </is>
       </c>
       <c r="F77" s="43" t="n"/>
       <c r="G77" s="43" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1" s="18">
-      <c r="A78" s="43" t="n"/>
-      <c r="B78" s="43" t="n"/>
-      <c r="C78" s="43" t="n"/>
-      <c r="D78" s="46" t="n"/>
+      <c r="A78" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B78" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D78" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E78" s="41" t="inlineStr">
         <is>
-          <t>• 【01】全量迁移继续 + 逐批对账 + 生产预跑</t>
-        </is>
-      </c>
-      <c r="F78" s="43" t="n"/>
-      <c r="G78" s="43" t="n"/>
+          <t>• UAT #2 场景脚本初稿</t>
+        </is>
+      </c>
+      <c r="F78" s="42" t="inlineStr">
+        <is>
+          <t>UAT #2 脚本初稿</t>
+        </is>
+      </c>
+      <c r="G78" s="29" t="inlineStr"/>
     </row>
     <row r="79" ht="22" customHeight="1" s="18">
       <c r="A79" s="49" t="inlineStr">
@@ -4150,27 +4244,27 @@
       </c>
       <c r="B79" s="39" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="D79" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D79" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E79" s="41" t="inlineStr">
         <is>
-          <t>• 文档冲刺：用户手册 85% + 运维手册 70% + 架构图更新</t>
+          <t>• 【01】全量迁移继续+逐批对账</t>
         </is>
       </c>
       <c r="F79" s="42" t="inlineStr">
         <is>
-          <t>文档 80%+</t>
+          <t>★ 全量对账 100%</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr"/>
@@ -4179,123 +4273,119 @@
       <c r="A80" s="43" t="n"/>
       <c r="B80" s="43" t="n"/>
       <c r="C80" s="43" t="n"/>
-      <c r="D80" s="48" t="n"/>
+      <c r="D80" s="46" t="n"/>
       <c r="E80" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 审批材料起稿</t>
+          <t>• 【07】连接器运行监控+连接管理界面</t>
         </is>
       </c>
       <c r="F80" s="43" t="n"/>
       <c r="G80" s="43" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1" s="18">
-      <c r="A81" s="49" t="inlineStr">
+      <c r="A81" s="43" t="n"/>
+      <c r="B81" s="43" t="n"/>
+      <c r="C81" s="43" t="n"/>
+      <c r="D81" s="46" t="n"/>
+      <c r="E81" s="41" t="inlineStr">
+        <is>
+          <t>• 【08】行级隔离验证</t>
+        </is>
+      </c>
+      <c r="F81" s="43" t="n"/>
+      <c r="G81" s="43" t="n"/>
+    </row>
+    <row r="82" ht="22" customHeight="1" s="18">
+      <c r="A82" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B81" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C81" s="26" t="inlineStr">
+      <c r="B82" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="D81" s="40" t="inlineStr">
+      <c r="D82" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>• 【06】合规报表口径验证</t>
+        </is>
+      </c>
+      <c r="F82" s="42" t="inlineStr">
+        <is>
+          <t>报表验证过</t>
+        </is>
+      </c>
+      <c r="G82" s="29" t="inlineStr"/>
+    </row>
+    <row r="83" ht="22" customHeight="1" s="18">
+      <c r="A83" s="43" t="n"/>
+      <c r="B83" s="43" t="n"/>
+      <c r="C83" s="43" t="n"/>
+      <c r="D83" s="48" t="n"/>
+      <c r="E83" s="41" t="inlineStr">
+        <is>
+          <t>• 文档 80%（架构图更新+运维手册完善）</t>
+        </is>
+      </c>
+      <c r="F83" s="43" t="n"/>
+      <c r="G83" s="43" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1" s="18">
+      <c r="A84" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B84" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D84" s="40" t="inlineStr">
         <is>
           <t>BA·Mandy</t>
         </is>
       </c>
-      <c r="E81" s="41" t="inlineStr">
-        <is>
-          <t>• UAT #2 预演主持（处置/Hold/脱敏/报表）</t>
-        </is>
-      </c>
-      <c r="F81" s="42" t="inlineStr">
-        <is>
-          <t>预演完成</t>
-        </is>
-      </c>
-      <c r="G81" s="29" t="inlineStr">
+      <c r="E84" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 脚本定稿</t>
+        </is>
+      </c>
+      <c r="F84" s="42" t="inlineStr">
+        <is>
+          <t>UAT #2 脚本</t>
+        </is>
+      </c>
+      <c r="G84" s="29" t="inlineStr">
         <is>
           <t>业务方排期</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="22" customHeight="1" s="18">
-      <c r="A82" s="43" t="n"/>
-      <c r="B82" s="43" t="n"/>
-      <c r="C82" s="43" t="n"/>
-      <c r="D82" s="44" t="n"/>
-      <c r="E82" s="41" t="inlineStr">
-        <is>
-          <t>• 预演反馈裁决</t>
-        </is>
-      </c>
-      <c r="F82" s="43" t="n"/>
-      <c r="G82" s="43" t="n"/>
-    </row>
-    <row r="83" ht="22" customHeight="1" s="18">
-      <c r="A83" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B83" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C83" s="26" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="D83" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="E83" s="41" t="inlineStr">
-        <is>
-          <t>• 全量回归（R1+R2）+ 安全终检（四门禁+渗透）</t>
-        </is>
-      </c>
-      <c r="F83" s="42" t="inlineStr">
-        <is>
-          <t>★ 全量对账 100%</t>
-        </is>
-      </c>
-      <c r="G83" s="29" t="inlineStr">
-        <is>
-          <t>渗透排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1" s="18">
-      <c r="A84" s="43" t="n"/>
-      <c r="B84" s="43" t="n"/>
-      <c r="C84" s="43" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="41" t="inlineStr">
-        <is>
-          <t>• 【01】全量迁移收尾 + 对账报告</t>
-        </is>
-      </c>
-      <c r="F84" s="43" t="n"/>
-      <c r="G84" s="43" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1" s="18">
       <c r="A85" s="43" t="n"/>
       <c r="B85" s="43" t="n"/>
       <c r="C85" s="43" t="n"/>
-      <c r="D85" s="46" t="n"/>
+      <c r="D85" s="44" t="n"/>
       <c r="E85" s="41" t="inlineStr">
         <is>
-          <t>• R2 发布包冻结 + 上线 Checklist v2</t>
+          <t>• 预演协调</t>
         </is>
       </c>
       <c r="F85" s="43" t="n"/>
@@ -4309,27 +4399,27 @@
       </c>
       <c r="B86" s="39" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="D86" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D86" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E86" s="41" t="inlineStr">
         <is>
-          <t>• 文档终审推进（7 套终稿）</t>
+          <t>• 全量回归（R1+R2）+ 功能收口</t>
         </is>
       </c>
       <c r="F86" s="42" t="inlineStr">
         <is>
-          <t>★ R2 就绪检查 100%</t>
+          <t>回归通过；R2 发布包 v1</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr"/>
@@ -4338,10 +4428,10 @@
       <c r="A87" s="43" t="n"/>
       <c r="B87" s="43" t="n"/>
       <c r="C87" s="43" t="n"/>
-      <c r="D87" s="48" t="n"/>
+      <c r="D87" s="46" t="n"/>
       <c r="E87" s="41" t="inlineStr">
         <is>
-          <t>• W11 末就绪检查组织（发布包/预演/文档/回退）</t>
+          <t>• 🤖 R2 发布包（增量/处置/加密/分层生产版）</t>
         </is>
       </c>
       <c r="F87" s="43" t="n"/>
@@ -4355,7 +4445,7 @@
       </c>
       <c r="B88" s="39" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
@@ -4363,98 +4453,118 @@
           <t>W12</t>
         </is>
       </c>
-      <c r="D88" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D88" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
         </is>
       </c>
       <c r="E88" s="41" t="inlineStr">
         <is>
-          <t>• Go/No-Go #2 决策参与</t>
+          <t>• 文档冲刺：7 套进入终稿</t>
         </is>
       </c>
       <c r="F88" s="42" t="inlineStr">
         <is>
-          <t>★ UAT #2 签字</t>
-        </is>
-      </c>
-      <c r="G88" s="29" t="inlineStr">
-        <is>
-          <t>UAT 时间</t>
-        </is>
-      </c>
+          <t>文档 90%</t>
+        </is>
+      </c>
+      <c r="G88" s="29" t="inlineStr"/>
     </row>
     <row r="89" ht="22" customHeight="1" s="18">
       <c r="A89" s="43" t="n"/>
       <c r="B89" s="43" t="n"/>
       <c r="C89" s="43" t="n"/>
-      <c r="D89" s="44" t="n"/>
+      <c r="D89" s="48" t="n"/>
       <c r="E89" s="41" t="inlineStr">
         <is>
-          <t>• UAT #2 正式主持（签字）</t>
+          <t>• 🤖 审批材料起稿</t>
         </is>
       </c>
       <c r="F89" s="43" t="n"/>
       <c r="G89" s="43" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1" s="18">
-      <c r="A90" s="43" t="n"/>
-      <c r="B90" s="43" t="n"/>
-      <c r="C90" s="43" t="n"/>
-      <c r="D90" s="44" t="n"/>
+      <c r="A90" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B90" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C90" s="26" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="D90" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E90" s="41" t="inlineStr">
         <is>
-          <t>• 上线后反馈分诊</t>
-        </is>
-      </c>
-      <c r="F90" s="43" t="n"/>
-      <c r="G90" s="43" t="n"/>
+          <t>• UAT #2 预演主持（处置/Hold/脱敏/报表）</t>
+        </is>
+      </c>
+      <c r="F90" s="42" t="inlineStr">
+        <is>
+          <t>预演完成</t>
+        </is>
+      </c>
+      <c r="G90" s="29" t="inlineStr"/>
     </row>
     <row r="91" ht="22" customHeight="1" s="18">
-      <c r="A91" s="49" t="inlineStr">
+      <c r="A91" s="43" t="n"/>
+      <c r="B91" s="43" t="n"/>
+      <c r="C91" s="43" t="n"/>
+      <c r="D91" s="44" t="n"/>
+      <c r="E91" s="41" t="inlineStr">
+        <is>
+          <t>• 预演反馈裁决</t>
+        </is>
+      </c>
+      <c r="F91" s="43" t="n"/>
+      <c r="G91" s="43" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1" s="18">
+      <c r="A92" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B91" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C91" s="26" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="D91" s="45" t="inlineStr">
+      <c r="B92" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C92" s="26" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="D92" s="45" t="inlineStr">
         <is>
           <t>DEV·Wade</t>
         </is>
       </c>
-      <c r="E91" s="41" t="inlineStr">
-        <is>
-          <t>• R2 生产发布（增量发布不中断 R1）</t>
-        </is>
-      </c>
-      <c r="F91" s="42" t="inlineStr">
-        <is>
-          <t>★ Go-Live #2</t>
-        </is>
-      </c>
-      <c r="G91" s="29" t="inlineStr"/>
-    </row>
-    <row r="92" ht="22" customHeight="1" s="18">
-      <c r="A92" s="43" t="n"/>
-      <c r="B92" s="43" t="n"/>
-      <c r="C92" s="43" t="n"/>
-      <c r="D92" s="46" t="n"/>
       <c r="E92" s="41" t="inlineStr">
         <is>
-          <t>• CC 生产全量迁移收尾+终版对账</t>
-        </is>
-      </c>
-      <c r="F92" s="43" t="n"/>
-      <c r="G92" s="43" t="n"/>
+          <t>• 回退演练+发布包冻结</t>
+        </is>
+      </c>
+      <c r="F92" s="42" t="inlineStr">
+        <is>
+          <t>终检通过；包冻结</t>
+        </is>
+      </c>
+      <c r="G92" s="29" t="inlineStr">
+        <is>
+          <t>渗透排期</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1" s="18">
       <c r="A93" s="43" t="n"/>
@@ -4463,61 +4573,57 @@
       <c r="D93" s="46" t="n"/>
       <c r="E93" s="41" t="inlineStr">
         <is>
-          <t>• P1 当日清 + 48h 值守 + 交付物 tag</t>
+          <t>• 安全终检（四门禁+渗透配合）</t>
         </is>
       </c>
       <c r="F93" s="43" t="n"/>
       <c r="G93" s="43" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1" s="18">
-      <c r="A94" s="49" t="inlineStr">
+      <c r="A94" s="43" t="n"/>
+      <c r="B94" s="43" t="n"/>
+      <c r="C94" s="43" t="n"/>
+      <c r="D94" s="46" t="n"/>
+      <c r="E94" s="41" t="inlineStr">
+        <is>
+          <t>• 迁移预跑+窗口预约</t>
+        </is>
+      </c>
+      <c r="F94" s="43" t="n"/>
+      <c r="G94" s="43" t="n"/>
+    </row>
+    <row r="95" ht="22" customHeight="1" s="18">
+      <c r="A95" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B94" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C94" s="26" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="D94" s="47" t="inlineStr">
+      <c r="B95" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="D95" s="47" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="E94" s="41" t="inlineStr">
-        <is>
-          <t>• 审批材料提交（完整版）</t>
-        </is>
-      </c>
-      <c r="F94" s="42" t="inlineStr">
-        <is>
-          <t>★ Release 2 交付完成</t>
-        </is>
-      </c>
-      <c r="G94" s="29" t="inlineStr">
-        <is>
-          <t>审批受理</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="1" s="18">
-      <c r="A95" s="43" t="n"/>
-      <c r="B95" s="43" t="n"/>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="48" t="n"/>
       <c r="E95" s="41" t="inlineStr">
         <is>
-          <t>• 文档终版归档（7 套）</t>
-        </is>
-      </c>
-      <c r="F95" s="43" t="n"/>
-      <c r="G95" s="43" t="n"/>
+          <t>• W13 末就绪检查组织（发布包/预演/文档/回退）</t>
+        </is>
+      </c>
+      <c r="F95" s="42" t="inlineStr">
+        <is>
+          <t>★ R2 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G95" s="29" t="inlineStr"/>
     </row>
     <row r="96" ht="22" customHeight="1" s="18">
       <c r="A96" s="43" t="n"/>
@@ -4526,11 +4632,196 @@
       <c r="D96" s="48" t="n"/>
       <c r="E96" s="41" t="inlineStr">
         <is>
-          <t>• 上线验证与稳定性报告 → 项目结束</t>
+          <t>• 上线 Checklist v2</t>
         </is>
       </c>
       <c r="F96" s="43" t="n"/>
       <c r="G96" s="43" t="n"/>
+    </row>
+    <row r="97" ht="22" customHeight="1" s="18">
+      <c r="A97" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B97" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D97" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E97" s="41" t="inlineStr">
+        <is>
+          <t>• Go/No-Go #2 决策参与</t>
+        </is>
+      </c>
+      <c r="F97" s="42" t="inlineStr">
+        <is>
+          <t>★ UAT #2 签字</t>
+        </is>
+      </c>
+      <c r="G97" s="29" t="inlineStr">
+        <is>
+          <t>UAT 时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1" s="18">
+      <c r="A98" s="43" t="n"/>
+      <c r="B98" s="43" t="n"/>
+      <c r="C98" s="43" t="n"/>
+      <c r="D98" s="44" t="n"/>
+      <c r="E98" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 正式主持（签字）</t>
+        </is>
+      </c>
+      <c r="F98" s="43" t="n"/>
+      <c r="G98" s="43" t="n"/>
+    </row>
+    <row r="99" ht="22" customHeight="1" s="18">
+      <c r="A99" s="43" t="n"/>
+      <c r="B99" s="43" t="n"/>
+      <c r="C99" s="43" t="n"/>
+      <c r="D99" s="44" t="n"/>
+      <c r="E99" s="41" t="inlineStr">
+        <is>
+          <t>• 上线后反馈分诊</t>
+        </is>
+      </c>
+      <c r="F99" s="43" t="n"/>
+      <c r="G99" s="43" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1" s="18">
+      <c r="A100" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B100" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D100" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E100" s="41" t="inlineStr">
+        <is>
+          <t>• R2 生产发布（增量不中断 R1）</t>
+        </is>
+      </c>
+      <c r="F100" s="42" t="inlineStr">
+        <is>
+          <t>★ Go-Live #2</t>
+        </is>
+      </c>
+      <c r="G100" s="29" t="inlineStr"/>
+    </row>
+    <row r="101" ht="22" customHeight="1" s="18">
+      <c r="A101" s="43" t="n"/>
+      <c r="B101" s="43" t="n"/>
+      <c r="C101" s="43" t="n"/>
+      <c r="D101" s="46" t="n"/>
+      <c r="E101" s="41" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移收尾+终版对账</t>
+        </is>
+      </c>
+      <c r="F101" s="43" t="n"/>
+      <c r="G101" s="43" t="n"/>
+    </row>
+    <row r="102" ht="22" customHeight="1" s="18">
+      <c r="A102" s="43" t="n"/>
+      <c r="B102" s="43" t="n"/>
+      <c r="C102" s="43" t="n"/>
+      <c r="D102" s="46" t="n"/>
+      <c r="E102" s="41" t="inlineStr">
+        <is>
+          <t>• P1 当日清+48h 值守+交付物 tag</t>
+        </is>
+      </c>
+      <c r="F102" s="43" t="n"/>
+      <c r="G102" s="43" t="n"/>
+    </row>
+    <row r="103" ht="22" customHeight="1" s="18">
+      <c r="A103" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B103" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C103" s="26" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D103" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E103" s="41" t="inlineStr">
+        <is>
+          <t>• 审批材料提交（完整版）</t>
+        </is>
+      </c>
+      <c r="F103" s="42" t="inlineStr">
+        <is>
+          <t>★ Release 2 交付完成</t>
+        </is>
+      </c>
+      <c r="G103" s="29" t="inlineStr">
+        <is>
+          <t>审批受理</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1" s="18">
+      <c r="A104" s="43" t="n"/>
+      <c r="B104" s="43" t="n"/>
+      <c r="C104" s="43" t="n"/>
+      <c r="D104" s="48" t="n"/>
+      <c r="E104" s="41" t="inlineStr">
+        <is>
+          <t>• 文档终版归档（7 套）</t>
+        </is>
+      </c>
+      <c r="F104" s="43" t="n"/>
+      <c r="G104" s="43" t="n"/>
+    </row>
+    <row r="105" ht="22" customHeight="1" s="18">
+      <c r="A105" s="43" t="n"/>
+      <c r="B105" s="43" t="n"/>
+      <c r="C105" s="43" t="n"/>
+      <c r="D105" s="48" t="n"/>
+      <c r="E105" s="41" t="inlineStr">
+        <is>
+          <t>• 稳定性报告 → 项目结束</t>
+        </is>
+      </c>
+      <c r="F105" s="43" t="n"/>
+      <c r="G105" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/report/Team1.xlsx
+++ b/report/Team1.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="63">
     <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
@@ -402,8 +402,31 @@
       <color rgb="00ca8a04"/>
       <sz val="9.199999999999999"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0015803d"/>
+      <sz val="9.199999999999999"/>
+    </font>
   </fonts>
-  <fills count="48">
+  <fills count="50">
     <fill>
       <patternFill/>
     </fill>
@@ -677,6 +700,16 @@
         <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -1033,7 +1066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1177,6 +1210,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="47" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="48" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="49" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2113,7 +2158,7 @@
     <col width="15" customWidth="1" style="18" min="1" max="1"/>
     <col width="13" customWidth="1" style="18" min="2" max="2"/>
     <col width="8" customWidth="1" style="18" min="3" max="3"/>
-    <col width="19" customWidth="1" style="18" min="4" max="4"/>
+    <col width="20" customWidth="1" style="18" min="4" max="4"/>
     <col width="66" customWidth="1" style="18" min="5" max="5"/>
     <col width="30" customWidth="1" style="18" min="6" max="6"/>
     <col width="30" customWidth="1" style="18" min="7" max="7"/>
@@ -2123,14 +2168,14 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>B2 湖仓归档平台 · 3 人团队执行计划 V2（14 周 · 双 Release · AI Vibe Coding）</t>
+          <t>B2 湖仓归档平台 · 3 人团队执行计划 V3（20 周 · 双 Release · 功能+非功能全覆盖）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" s="18">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>V2 调整：原 W3~W5 工作过载，拆为「功能开发（W3~W4）+ DevOps与就绪（W5~W6）」两个 Sprint，R1 上线移至 W7；R2 同理多拆一周，上线 W14。R1 = W1~W7 / R2 = W8~W14（各 +1 周，共 14 周）· CC 单系统贯穿</t>
+          <t>范围依据：功能性需求 = task.csv 113 项（Phase1 基础归档 26 / Phase2 能力优化 63 / Phase3 AI 赋能 24）；非功能性需求 = NFR 六类（性能/可用性/安全/合规/可维护/成本）。14 周版仅覆盖 Phase1+部分 Phase2 且无 NFR 独立排期，故扩至 20 周。</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2202,7 @@
       </c>
       <c r="E4" s="22" t="inlineStr">
         <is>
-          <t>核心交付物（按功能域编号）</t>
+          <t>核心交付物（功能域 + Phase + NFR 标注）</t>
         </is>
       </c>
       <c r="F4" s="22" t="inlineStr">
@@ -2176,11 +2221,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="132" customHeight="1" s="18">
+    <row r="5" ht="138" customHeight="1" s="18">
       <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Release 1
-归档检索平台</t>
+Phase1 基础平台</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
@@ -2194,37 +2239,37 @@
           <t>W1~W2</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>需求定稿 + 环境就绪 + CC 连接 + MVP 数据链路</t>
-        </is>
-      </c>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t>【BA】① BRD 定稿（数据流图+保留期矩阵+PII 分级+检索权限矩阵）② CC 垃圾表标准与首批 50 表清单 【DEV】③ 架构定稿+资源申请+验收+UC 初始化 ④ 前后端骨架+CI 骨架 ⑤ SeaTunnel PoC（10 表端到端）+ 1253 表分类 ⑥【01】50 表批量导入+生成器 v1 【QA】⑦ 测试计划（8 域）+ 架构图×2 + 文档模板</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>★ W2：PoC 端到端 + BRD 签字 + 50 表入 RAW</t>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>需求定稿 + 环境就绪 + CC 连接 + MVP 数据链路（Phase1 起步）</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>【BA】① BRD：数据流图+保留期矩阵+PII 分级+检索权限矩阵 ② task.csv Phase1 26 项逐条确认知范围 【DEV】③ 架构定稿+资源申请+验收+UC 初始化 ④ 前后端骨架+CI 骨架 ⑤ SeaTunnel PoC（10 表端到端）+ 1253 表分类 ⑥【01】50 表批量导入+生成器（覆盖 P1 批量导入/迁移规则/任务管理）【QA】⑦ 测试计划+架构图×2+文档模板</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>★ W2：PoC 端到端+BRD 签字+50 表入 RAW</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
-          <t>CC 账号周期；Wade 串行压力</t>
+          <t>CC 账号周期；Phase1 范围蔓延</t>
         </is>
       </c>
       <c r="H5" s="30" t="inlineStr">
         <is>
-          <t>① CC 账号 ② 垃圾表标准 ③ 50 表清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="132" customHeight="1" s="18">
+          <t>① CC 账号 ② Phase1 范围冻结 ③ 50 表清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="138" customHeight="1" s="18">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Release 1
-归档检索平台</t>
+Phase1 基础平台</t>
         </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
@@ -2238,37 +2283,37 @@
           <t>W3~W4</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>检索/权限/审计 功能开发（纯功能，不做上线准备）</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>【DEV】【05】① 配置化检索页 ② 预览（SAS）③ 导出【08】④ RBAC 五角色 CRUD+鉴权 ⑤ UC GRANT+掩码函数（权限三态）⑥ SERVE 物化 【06】⑦ 审计埋点【07】⑧ 连接器模板 v1【安全】⑨ 依赖扫描+SAST 门禁 【BA】⑩ PII 字段标记+预览范围 ⑪ R1 功能验收 【QA】⑫ 功能/安全测试 ⑬ 文档 50%</t>
-        </is>
-      </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>★ W4：R1 功能全部 Done（登录→检索→预览→导出+权限三态）</t>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>Phase1 检索/权限/审计 功能开发（纯功能）</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>【DEV】【05】① 配置化检索页 ② 预览（SAS）③ 导出【08】④ RBAC+掩码（权限三态）⑤ SSO 【06】⑥ 审计埋点+用户操作审计追踪【07】⑦ 连接器模板 v1（P1 剩余：迁移完整性校验补全） 【BA】⑧ PII 标记+预览范围 ⑨ Phase1 验收 【QA】⑩ 功能/安全测试 ⑪ 文档 50%</t>
+        </is>
+      </c>
+      <c r="F6" s="42" t="inlineStr">
+        <is>
+          <t>★ W4：Phase1 26 项功能全部 Done（登录→检索→预览→导出）</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
         <is>
-          <t>功能密度仍高但不再混上线准备；掩码/三态是硬骨头</t>
+          <t>功能密度高；掩码/三态难啃</t>
         </is>
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>① PII 标记（W3）② 性能标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="132" customHeight="1" s="18">
+          <t>① PII 标记 ② 性能标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="138" customHeight="1" s="18">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Release 1
-归档检索平台</t>
+Phase1 基础平台</t>
         </is>
       </c>
       <c r="B7" s="50" t="inlineStr">
@@ -2279,243 +2324,243 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>W5~W6</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>DevOps + R1 上线就绪（独立 Sprint，不再挤占功能期）</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>【DEV·DevOps】① CD 流水线完善（Helm 多环境 Dev/Staging/Prod + Environments 审批流）② 四道安全门禁全量上线（gitleaks/Trivy）③ 生产发布包（一键发布就绪）④ 回退预案与演练 ⑤ 监控告警就绪（App Insights+Dashboard）⑥ CC 迁移预跑+Runbook 【BA】⑦ UAT #1 脚本+预演主持 【QA】⑧ R1 文档冲刺（用户手册/运维手册 70%）⑨ 上线 Checklist ⑩ W6 末就绪检查</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>★ W6 末：R1 就绪检查 100%（DevOps 就绪/预演/回退/预跑全绿）</t>
+          <t>W5~W7</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>DevOps + NFR 第一批 + R1 上线（W7 Go-Live #1）</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>【DEV·DevOps】① CD 多环境+Environments 审批 ② 四道安全门禁全开 ③ 发布包+回退演练 ④ 监控告警 【NFR-安全】⑤ 代码安全四门禁生产化（高中危清零）【NFR-性能】⑥ 首屏 P95&lt;5s 基准测试（100 万行） 【NFR-可用性】⑦ 备份策略（SQL DB PITR/ADLS 版本）【BA】⑧ UAT #1（Phase1 场景）【QA】⑨ R1 审批材料 ⑩ W6 就绪检查 → W7 上线</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>★ W7：Go-Live #1 —— Phase1 全部上线（基础归档与查询可用）</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>DevOps 环境问题（AKS 权限/ACR 网络）；预演排期</t>
+          <t>DevOps 环境问题；NFR 首次验证返工</t>
         </is>
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>① 生产环境权限 ② 预演排期 ③ 迁移窗口</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="132" customHeight="1" s="18">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Release 1
-归档检索平台</t>
-        </is>
-      </c>
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>Sprint 3
-DevOps+R1就绪</t>
+          <t>① 生产权限 ② 预演排期 ③ Go 窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="138" customHeight="1" s="18">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Release 2
+Phase2/3 完整版</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Sprint 4
+Phase2 治理</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>R1 上线周：发布 → UAT → Go-Live #1（仅执行）</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>【DEV】① 生产发布（就绪包+审批）② CC 50 表生产迁移+对账 ③ P1 当日清 【BA】④ UAT #1 正式主持（签字）⑤ Go/No-Go 【QA】⑥ 上线记录+R1 审批材料提交 ⑦ 48h 值守三角色轮值</t>
-        </is>
-      </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>★ W7：Go-Live #1 —— CC 可查、有权限、有审计（Release 1 交付）</t>
+          <t>W8~W10</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>Phase2 治理主体：元数据/冷数据/归档生命周期（63 项之前半）</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>【DEV】【02】① 统一元数据模型+来源绑定 ② 冷数据识别与周期接入 ③ 标签体系 【03】④ 标准归档模型+转换校验 ⑤ 到期处置引擎+Legal Hold ⑥ 处置/Hold 界面 【BA】⑦ Hold 条件定稿（法务）【QA】⑧ 处置 E2E+合规初验</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>★ W10：处置全链路（到期→Hold→处置→审计）通过</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>依赖 W6 就绪检查通过</t>
+          <t>Phase2 63 项范围大；处置不可逆</t>
         </is>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
-          <t>① Go 窗口 ② UAT 签字人</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="132" customHeight="1" s="18">
+          <t>① Hold 审批人 ② 保留期底线 ③ 冷数据标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="138" customHeight="1" s="18">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Release 2
-治理合规完整版</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>Sprint 4
-治理+安全</t>
+Phase2/3 完整版</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 5
+Phase2 安全+连接</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>W8~W9</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>治理 + 生命周期 + 安全管控（R2 功能主体一）</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>【DEV】【02】① 增量接入+冷数据转冷 ② 元数据标准界面【03】③ 处置引擎+Legal Hold+归档模型 ④ 处置/Hold 界面 【04】⑤ 加密+脱敏+驻留核查 ⑥ ADLS 分层+Compaction【07】⑦ 连接器模板库 【BA】⑧ Hold 条件定稿（法务）【QA】⑨ 处置 E2E+安全测试 ⑩ 文档 60%</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>★ W9：处置全链路+脱敏三态+驻留核查通过</t>
+          <t>W11~W13</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Phase2 安全+连接器+合规报表（63 项之后半）+ CC 全量</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>【DEV】【04】① 境内驻留管理 ② 加密+密钥管理+字段级脱敏 ③ 备份与灾备 ④ 冷热分层 【07】⑤ 连接器模板库+运行监控+集成标准【06】⑥ 合规报表（等保/个保法对照） 【01】⑦ CC 全量 1253 表分批迁移+对账【08】⑧ 行级隔离 【BA】⑨ 全量范围签字 ⑩ 报表口径【QA】⑪ 兼容矩阵 ⑫ 文档 70%</t>
+        </is>
+      </c>
+      <c r="F9" s="42" t="inlineStr">
+        <is>
+          <t>★ W12：脱敏三态+驻留核查；★ W13：CC 全量对账 100%</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>处置不可逆；加密需人工复核</t>
+          <t>全量迁移时长；加密人工验证</t>
         </is>
       </c>
       <c r="H9" s="30" t="inlineStr">
         <is>
-          <t>① Hold 审批人 ② 保留期底线 ③ 实时指标</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="132" customHeight="1" s="18">
+          <t>① 数据量实测 ② 迁移窗口 ③ 报表口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="138" customHeight="1" s="18">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Release 2
-治理合规完整版</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>Sprint 5
-全量+合规+R2就绪</t>
+Phase2/3 完整版</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Sprint 6
+AI 赋能</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>W10~W13</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>CC 全量 + 合规报表 + 连接器完善 + R2 就绪（多一周，不再挤）</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>【DEV】【01】① CC 全量 1253 表分批迁移+逐批对账【06】② 合规报表【07】③ 连接器运行监控+连接管理界面【08】④ 行级隔离验证 【就绪 W12~13】⑤ 全量回归（R1+R2）⑥ R2 发布包+回退演练 ⑦ 安全终检（四门禁+渗透）⑧ 迁移预跑+窗口预约 【BA】⑨ 全量范围签字 ⑩ 报表口径对齐 ⑪ UAT #2 脚本+预演 【QA】⑫ 文档冲刺（7 套终稿）+审批材料 ⑬ 兼容矩阵 ⑭ W13 末就绪检查</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>★ W11：全量对账 100%；★ W13 末：R2 就绪检查 100%</t>
+          <t>W14~W16</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Phase3 AI 智能化赋能（24 项）</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>【DEV】① 智能内容解析（PDF/Word/图片文本提取+结构化字段识别）② 核心业务信息提取（产品/批次/金额） ③ AI 自动分类与语义标签 ④ 智能检索增强（自然语言→SQL 初版）⑤ 解析结果人工校验界面 【BA】⑥ AI 准确率验收标准定稿（如字段提取 ≥90%）⑦ 人工校验流程设计 【QA】⑧ AI 输出质量抽测方案（抽样集+准确率报告）⑨ Phase3 UAT 脚本</t>
+        </is>
+      </c>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>★ W16：AI 解析/分类演示可接受（准确率达标）</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>全量迁移时长；文档冲刺与就绪并行</t>
+          <t>AI 准确率不达标（最大不确定区）；解析成本</t>
         </is>
       </c>
       <c r="H10" s="30" t="inlineStr">
         <is>
-          <t>① 数据量实测 ② 迁移窗口 ③ 报表口径签字</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="132" customHeight="1" s="18">
+          <t>① AI 验收标准 ② 抽样集准备 ③ 是否降级范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="138" customHeight="1" s="18">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Release 2
-治理合规完整版</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>Sprint 5
-全量+合规+R2就绪</t>
+Phase2/3 完整版</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>Sprint 7
+NFR+全量+就绪</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>R2 上线周 + 收尾：Go-Live #2 → 项目结束</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>【DEV】① R2 生产发布（增量不中断 R1）② CC 生产全量迁移收尾+终版对账 ③ P1 当日清 【BA】④ UAT #2 正式主持（签字）⑤ Go/No-Go 【QA】⑥ 审批材料提交 ⑦ 文档终版归档（7 套）⑧ 稳定性报告 → 项目结束</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>★ W14：Go-Live #2（完整版）+ 交付物归档 → 项目结束</t>
+          <t>W17~W20</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>NFR 达标冲刺 + R2 就绪 + 上线 + 收尾</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>【NFR-性能】① 20GB 级性能基准+调优（首屏/导出/联邦查询）【NFR-可用性】② 灾备演练（SQL 故障转移/ADLS 恢复）【NFR-安全】③ 渗透测试+整改 ④ 全量安全回归【NFR-合规】⑤ 等保/个保法对照举证材料 【NFR-可维护】⑥ 7 套文档终稿（架构/详设×3/接口/字典/用户/运维）⑦ 培训视频 【DEV】⑧ 全量回归（R1+R2）⑨ R2 发布包+回退 ⑩ W18 预演+就绪检查【BA】⑪ UAT #2（全场景）【上线】W19 Go-Live #2（全量版）→ W20 稳定确认+归档+项目结束</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>★ W18：NFR 全部达标+就绪检查；★ W19：Go-Live #2；★ W20：项目结束</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>上线+文档+收尾并行；迁移收尾跨窗口</t>
+          <t>NFR 达标与文档冲刺并行压力；渗透整改返工</t>
         </is>
       </c>
       <c r="H11" s="30" t="inlineStr">
         <is>
-          <t>① Go 窗口 ② UAT 签字人 ③ 文档确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" s="18">
+          <t>① NFR 验收签字人 ② 渗透窗口 ③ Go #2 窗口 ④ 文档确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="18">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>V2 变更：原「W3~W5 检索增强+就绪」一个 Sprint 拆为两个 —— S2 功能开发（W3~W4，纯功能）+ S3 DevOps与就绪（W5~W6），R1 上线 W7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1" s="18">
+          <t>20 周构成：R1 = W1~W7（Phase1 基础归档与查询 26 项 → Go-Live #1）；R2 = W8~W20（Phase2 63 项 + Phase3 AI 24 项 + NFR 六类达标 → Go-Live #2 + 项目结束）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="18">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>R2 同理：原「W10~W11 全量+就绪」扩为 W10~W13（多一周），R2 上线 W14。总工期 12 → 14 周（+2 周）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1" s="18">
+          <t>与 14 周版差异：① 补全 Phase2 后半（安全管控 9 项/连接器 9 项/检索增强 11 项）② 新增 Phase3 AI 赋能 24 项（W14~16 独立 Sprint）③ NFR 从"散在任务里"变为独立排期（W5~7 第一批 / W17~18 达标冲刺）④ 文档与培训给足 2.5 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" s="18">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>人天口径：仍按 Team1 表（BA 20 + DEV 100 + QA 30 = 150 人天）；+2 周主要为 DevOps/就绪/缓冲的节奏舒展，不增功能范围</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" s="18">
+          <t>人天口径：BA 20 + DEV 100 + QA 30 = 150 人天不变；20 周按 3 人 ≈ 300 人日在岗，余量为 AI 提效吸收（×2 假设）——若 W7/W13 里程碑发现提效不足，优先砍 Phase3 范围（AI 项可降级为 V2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" s="18">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>团队与风险不变：Mandy·BA（50%）/ Wade·DEV（全开发，🤖 AI 提效）/ QA；无独立架构评审——W1/W5/W12 三个节点请平台团队外部 sanity check</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" s="18">
+          <t>NFR 清单（六类）：性能（首屏 P95&lt;5s/导出 1 万行&lt;10s）· 可用性（99.5%/灾备演练）· 安全（四门禁+渗透+脱敏三态）· 合规（等保/个保法举证）· 可维护（7 套文档+培训）· 成本（存储分层生效）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="18">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>上线只占 W7 / W14 最后一周；W8~W13 期间 R1 已在生产运行，R2 增量发布不中断服务</t>
+          <t>上线只占 W7 / W19 最后一周；W8~W18 期间 R1 已在生产运行，Phase2/3 增量发布不中断服务</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="18" min="1" max="1"/>
@@ -2548,20 +2593,20 @@
     <col width="13" customWidth="1" style="18" min="4" max="4"/>
     <col width="64" customWidth="1" style="18" min="5" max="5"/>
     <col width="26" customWidth="1" style="18" min="6" max="6"/>
-    <col width="20" customWidth="1" style="18" min="7" max="7"/>
+    <col width="18" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="inlineStr">
         <is>
-          <t>周计划明细 · 3 人 × 14 周（W3~W4 纯功能 / W5~W6 DevOps就绪 / W7 上线 · R2 同理 / W14 上线收尾）</t>
+          <t>周计划明细 · 3 人 × 20 周（Phase1 → Phase2 → Phase3 AI → NFR 达标 · 上线 W7 / W19）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>🤖 = AI 提效标注 · BA·Mandy / DEV·Wade / QA · 外部依赖为不可压缩时间</t>
+          <t>🤖 = AI 提效标注 · 功能域【01】~【08】+ Phase 标注 + NFR 标注 · BA·Mandy / DEV·Wade / QA</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2670,12 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>• 【8 域需求访谈】业务方×2 + 合规法务×1（保留期/PII/Legal Hold）</t>
+          <t>• 【8 域需求访谈】+ task.csv Phase1 26 项逐条确认（范围冻结）</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>BRD 初稿；剔除规则</t>
+          <t>BRD 初稿；Phase1 范围冻结</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -2646,7 +2691,7 @@
       <c r="D6" s="44" t="n"/>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 BRD 起稿：数据流图+归档范围矩阵+PII 分级+检索权限矩阵</t>
+          <t>• 🤖 BRD：数据流图+保留期矩阵+PII 分级+检索权限矩阵</t>
         </is>
       </c>
       <c r="F6" s="43" t="n"/>
@@ -2659,7 +2704,7 @@
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>• CC 垃圾表剔除标准与业务方对齐</t>
+          <t>• CC 垃圾表剔除标准</t>
         </is>
       </c>
       <c r="F7" s="43" t="n"/>
@@ -2688,7 +2733,7 @@
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>• 架构文档定稿 + 资源申请单（区域=境内）+ CC 账号/白名单申请（D1）</t>
+          <t>• 架构定稿+资源申请单（区域=境内）+ CC 账号申请（D1）</t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
@@ -2709,57 +2754,57 @@
       <c r="D9" s="46" t="n"/>
       <c r="E9" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 CC 1253 表扫描分类脚本</t>
+          <t>• 🤖 CC 1253 表扫描分类 + 前后端骨架 + CI 骨架</t>
         </is>
       </c>
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1" s="18">
-      <c r="A10" s="43" t="n"/>
-      <c r="B10" s="43" t="n"/>
-      <c r="C10" s="43" t="n"/>
-      <c r="D10" s="46" t="n"/>
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 前后端骨架 + CI 骨架（build+单测+推镜像）</t>
-        </is>
-      </c>
-      <c r="F10" s="43" t="n"/>
-      <c r="G10" s="43" t="n"/>
+          <t>• 🤖 测试计划（8 域+Phase 映射）</t>
+        </is>
+      </c>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>测试计划</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1" s="18">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
+      <c r="A11" s="43" t="n"/>
+      <c r="B11" s="43" t="n"/>
+      <c r="C11" s="43" t="n"/>
+      <c r="D11" s="48" t="n"/>
       <c r="E11" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 测试计划初稿（8 域）</t>
-        </is>
-      </c>
-      <c r="F11" s="42" t="inlineStr">
-        <is>
-          <t>测试计划；架构图×2</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="inlineStr"/>
+          <t>• 架构图×2 初稿</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="n"/>
+      <c r="G11" s="43" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1" s="18">
       <c r="A12" s="43" t="n"/>
@@ -2768,111 +2813,111 @@
       <c r="D12" s="48" t="n"/>
       <c r="E12" s="41" t="inlineStr">
         <is>
-          <t>• 架构图初稿：上下文+容器图</t>
+          <t>• 文档模板 4 套</t>
         </is>
       </c>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1" s="18">
-      <c r="A13" s="43" t="n"/>
-      <c r="B13" s="43" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="48" t="n"/>
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E13" s="41" t="inlineStr">
         <is>
-          <t>• 文档模板 4 套</t>
-        </is>
-      </c>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="43" t="n"/>
+          <t>• BRD 评审→签字</t>
+        </is>
+      </c>
+      <c r="F13" s="42" t="inlineStr">
+        <is>
+          <t>BRD 签字</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>业务方到场</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1" s="18">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="43" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>• CC 首批 50 表清单确认</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="43" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="18">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D14" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E14" s="41" t="inlineStr">
-        <is>
-          <t>• BRD 评审→定稿签字</t>
-        </is>
-      </c>
-      <c r="F14" s="42" t="inlineStr">
-        <is>
-          <t>BRD 签字；50 表清单</t>
-        </is>
-      </c>
-      <c r="G14" s="29" t="inlineStr">
-        <is>
-          <t>业务方到场</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" s="18">
-      <c r="A15" s="43" t="n"/>
-      <c r="B15" s="43" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="44" t="n"/>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E15" s="41" t="inlineStr">
         <is>
-          <t>• CC 首批 50 张热表清单确认</t>
-        </is>
-      </c>
-      <c r="F15" s="43" t="n"/>
-      <c r="G15" s="43" t="n"/>
+          <t>• 资源验收+UC 初始化</t>
+        </is>
+      </c>
+      <c r="F15" s="42" t="inlineStr">
+        <is>
+          <t>★ PoC 端到端；50 表入 RAW</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t>资源交付</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="18">
-      <c r="A16" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A16" s="43" t="n"/>
+      <c r="B16" s="43" t="n"/>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="41" t="inlineStr">
         <is>
-          <t>• 平台资源验收 + UC 初始化（arch_cc+GRANT+SP）</t>
-        </is>
-      </c>
-      <c r="F16" s="42" t="inlineStr">
-        <is>
-          <t>★ PoC 端到端；50 表入 RAW</t>
-        </is>
-      </c>
-      <c r="G16" s="29" t="inlineStr">
-        <is>
-          <t>资源交付</t>
-        </is>
-      </c>
+          <t>• 🤖 SeaTunnel PoC 10 表端到端</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="43" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1" s="18">
       <c r="A17" s="43" t="n"/>
@@ -2881,149 +2926,149 @@
       <c r="D17" s="46" t="n"/>
       <c r="E17" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 SeaTunnel PoC：抽样 10 表端到端</t>
+          <t>• 【01/P1】50 表批量导入+生成器（含迁移规则配置/任务调度监控）</t>
         </is>
       </c>
       <c r="F17" s="43" t="n"/>
       <c r="G17" s="43" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1" s="18">
-      <c r="A18" s="43" t="n"/>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E18" s="41" t="inlineStr">
         <is>
-          <t>• 【01】50 表批量导入 + 配置生成器 v1</t>
-        </is>
-      </c>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
+          <t>• 架构图×4</t>
+        </is>
+      </c>
+      <c r="F18" s="42" t="inlineStr">
+        <is>
+          <t>架构图×4 初稿</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1" s="18">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="43" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="48" t="n"/>
+      <c r="E19" s="41" t="inlineStr">
+        <is>
+          <t>• 【01】对账测试设计（P1 完整性校验用例）</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="43" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="18">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D19" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="inlineStr">
-        <is>
-          <t>• 架构图完善：组件+部署图</t>
-        </is>
-      </c>
-      <c r="F19" s="42" t="inlineStr">
-        <is>
-          <t>架构图×4 初稿</t>
-        </is>
-      </c>
-      <c r="G19" s="29" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="18">
-      <c r="A20" s="43" t="n"/>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="48" t="n"/>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E20" s="41" t="inlineStr">
         <is>
-          <t>• 【01】对账测试设计</t>
-        </is>
-      </c>
-      <c r="F20" s="43" t="n"/>
-      <c r="G20" s="43" t="n"/>
+          <t>• 【05】检索字段级确认（PII 标记）</t>
+        </is>
+      </c>
+      <c r="F20" s="42" t="inlineStr">
+        <is>
+          <t>PII 标记清单</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1" s="18">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="43" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="41" t="inlineStr">
+        <is>
+          <t>• 预览格式范围确认</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="43" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="18">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="D21" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E21" s="41" t="inlineStr">
-        <is>
-          <t>• 【05】检索场景字段级确认（PII 列标记）</t>
-        </is>
-      </c>
-      <c r="F21" s="42" t="inlineStr">
-        <is>
-          <t>PII 标记清单</t>
-        </is>
-      </c>
-      <c r="G21" s="29" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1" s="18">
-      <c r="A22" s="43" t="n"/>
-      <c r="B22" s="43" t="n"/>
-      <c r="C22" s="43" t="n"/>
-      <c r="D22" s="44" t="n"/>
+      <c r="D22" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E22" s="41" t="inlineStr">
         <is>
-          <t>• 预览格式范围确认</t>
-        </is>
-      </c>
-      <c r="F22" s="43" t="n"/>
-      <c r="G22" s="43" t="n"/>
+          <t>• 🤖【08】RBAC CRUD+OIDC/JWT 鉴权+前端权限渲染</t>
+        </is>
+      </c>
+      <c r="F22" s="42" t="inlineStr">
+        <is>
+          <t>RBAC+检索页提测</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1" s="18">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="D23" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A23" s="43" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="41" t="inlineStr">
         <is>
-          <t>• 🤖【08】RBAC CRUD + OIDC/JWT 鉴权 + 前端权限渲染</t>
-        </is>
-      </c>
-      <c r="F23" s="42" t="inlineStr">
-        <is>
-          <t>RBAC+检索页提测</t>
-        </is>
-      </c>
-      <c r="G23" s="29" t="inlineStr"/>
+          <t>• 🤖【05】配置化检索页+一对多联动（订单头→行）</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="43" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1" s="18">
       <c r="A24" s="43" t="n"/>
@@ -3032,153 +3077,149 @@
       <c r="D24" s="46" t="n"/>
       <c r="E24" s="41" t="inlineStr">
         <is>
-          <t>• 🤖【05】配置化检索页（动态筛选/表格/分页）</t>
+          <t>• 【06/P1】用户操作审计追踪埋点</t>
         </is>
       </c>
       <c r="F24" s="43" t="n"/>
       <c r="G24" s="43" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1" s="18">
-      <c r="A25" s="43" t="n"/>
-      <c r="B25" s="43" t="n"/>
-      <c r="C25" s="43" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="D25" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E25" s="41" t="inlineStr">
         <is>
-          <t>• 【06】审计埋点 v1</t>
-        </is>
-      </c>
-      <c r="F25" s="43" t="n"/>
-      <c r="G25" s="43" t="n"/>
+          <t>• 单测框架+覆盖率&gt;70%</t>
+        </is>
+      </c>
+      <c r="F25" s="42" t="inlineStr">
+        <is>
+          <t>CI 门禁生效</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1" s="18">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="43" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 API 集成测试</t>
+        </is>
+      </c>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="43" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="18">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="D26" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="inlineStr">
-        <is>
-          <t>• 单测框架+覆盖率门禁 &gt;70%</t>
-        </is>
-      </c>
-      <c r="F26" s="42" t="inlineStr">
-        <is>
-          <t>CI 门禁生效</t>
-        </is>
-      </c>
-      <c r="G26" s="29" t="inlineStr">
-        <is>
-          <t>DEV API 稳定</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" s="18">
-      <c r="A27" s="43" t="n"/>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="48" t="n"/>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E27" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 API 集成测试 10 场景</t>
-        </is>
-      </c>
-      <c r="F27" s="43" t="n"/>
-      <c r="G27" s="43" t="n"/>
+          <t>• Phase1 26 项逐项验收（对照 task.csv）</t>
+        </is>
+      </c>
+      <c r="F27" s="42" t="inlineStr">
+        <is>
+          <t>Phase1 验收记录</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1" s="18">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="43" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #1 脚本初稿</t>
+        </is>
+      </c>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" s="18">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="D28" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="inlineStr">
-        <is>
-          <t>• R1 功能验收（检索/预览/导出/权限三态）</t>
-        </is>
-      </c>
-      <c r="F28" s="42" t="inlineStr">
-        <is>
-          <t>R1 功能验收记录</t>
-        </is>
-      </c>
-      <c r="G28" s="29" t="inlineStr"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" s="18">
-      <c r="A29" s="43" t="n"/>
-      <c r="B29" s="43" t="n"/>
-      <c r="C29" s="43" t="n"/>
-      <c r="D29" s="44" t="n"/>
+      <c r="D29" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E29" s="41" t="inlineStr">
         <is>
-          <t>• UAT #1 场景脚本初稿</t>
-        </is>
-      </c>
-      <c r="F29" s="43" t="n"/>
-      <c r="G29" s="43" t="n"/>
+          <t>• 【08】UC GRANT+掩码函数+权限三态</t>
+        </is>
+      </c>
+      <c r="F29" s="42" t="inlineStr">
+        <is>
+          <t>★ Phase1 功能全部 Done</t>
+        </is>
+      </c>
+      <c r="G29" s="29" t="inlineStr"/>
     </row>
     <row r="30" ht="22" customHeight="1" s="18">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="D30" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A30" s="43" t="n"/>
+      <c r="B30" s="43" t="n"/>
+      <c r="C30" s="43" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="41" t="inlineStr">
         <is>
-          <t>• 【08】UC GRANT+掩码函数+权限三态联调</t>
-        </is>
-      </c>
-      <c r="F30" s="42" t="inlineStr">
-        <is>
-          <t>★ R1 功能全部 Done</t>
-        </is>
-      </c>
-      <c r="G30" s="29" t="inlineStr"/>
+          <t>• 【05】SERVE 物化+预览+导出</t>
+        </is>
+      </c>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="43" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1" s="18">
       <c r="A31" s="43" t="n"/>
@@ -3187,57 +3228,57 @@
       <c r="D31" s="46" t="n"/>
       <c r="E31" s="41" t="inlineStr">
         <is>
-          <t>• 【05】SERVE 物化+预览（SAS）+导出</t>
+          <t>• 【01/P1】迁移完整性校验补全（基准记录+迁移后比对）</t>
         </is>
       </c>
       <c r="F31" s="43" t="n"/>
       <c r="G31" s="43" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1" s="18">
-      <c r="A32" s="43" t="n"/>
-      <c r="B32" s="43" t="n"/>
-      <c r="C32" s="43" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="D32" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E32" s="41" t="inlineStr">
         <is>
-          <t>• 安全门禁①②上线 + High 清零</t>
-        </is>
-      </c>
-      <c r="F32" s="43" t="n"/>
-      <c r="G32" s="43" t="n"/>
+          <t>• 功能测试+Bug 跟踪</t>
+        </is>
+      </c>
+      <c r="F32" s="42" t="inlineStr">
+        <is>
+          <t>测试报告</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="inlineStr"/>
     </row>
     <row r="33" ht="22" customHeight="1" s="18">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="D33" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
+      <c r="A33" s="43" t="n"/>
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="48" t="n"/>
       <c r="E33" s="41" t="inlineStr">
         <is>
-          <t>• 功能测试执行+Bug 跟踪</t>
-        </is>
-      </c>
-      <c r="F33" s="42" t="inlineStr">
-        <is>
-          <t>测试报告</t>
-        </is>
-      </c>
-      <c r="G33" s="29" t="inlineStr"/>
+          <t>• 🤖 安全测试①</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="43" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1" s="18">
       <c r="A34" s="43" t="n"/>
@@ -3246,111 +3287,111 @@
       <c r="D34" s="48" t="n"/>
       <c r="E34" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 安全测试①：注入/XSS/越权</t>
+          <t>• 性能基准准备</t>
         </is>
       </c>
       <c r="F34" s="43" t="n"/>
       <c r="G34" s="43" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1" s="18">
-      <c r="A35" s="43" t="n"/>
-      <c r="B35" s="43" t="n"/>
-      <c r="C35" s="43" t="n"/>
-      <c r="D35" s="48" t="n"/>
+      <c r="A35" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E35" s="41" t="inlineStr">
         <is>
-          <t>• 性能测试准备</t>
-        </is>
-      </c>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
+          <t>• UAT #1 脚本定稿</t>
+        </is>
+      </c>
+      <c r="F35" s="42" t="inlineStr">
+        <is>
+          <t>UAT #1 脚本</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>业务方排期</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="18">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="A36" s="43" t="n"/>
+      <c r="B36" s="43" t="n"/>
+      <c r="C36" s="43" t="n"/>
+      <c r="D36" s="44" t="n"/>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>• 预演协调</t>
+        </is>
+      </c>
+      <c r="F36" s="43" t="n"/>
+      <c r="G36" s="43" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" s="18">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="D36" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E36" s="41" t="inlineStr">
-        <is>
-          <t>• UAT #1 脚本定稿</t>
-        </is>
-      </c>
-      <c r="F36" s="42" t="inlineStr">
-        <is>
-          <t>UAT #1 脚本</t>
-        </is>
-      </c>
-      <c r="G36" s="29" t="inlineStr">
-        <is>
-          <t>业务方排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1" s="18">
-      <c r="A37" s="43" t="n"/>
-      <c r="B37" s="43" t="n"/>
-      <c r="C37" s="43" t="n"/>
-      <c r="D37" s="44" t="n"/>
+      <c r="D37" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E37" s="41" t="inlineStr">
         <is>
-          <t>• 预演协调（业务方排期）</t>
-        </is>
-      </c>
-      <c r="F37" s="43" t="n"/>
-      <c r="G37" s="43" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1" s="18">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="D38" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+          <t>• 【DevOps】CD 多环境+Environments 审批流</t>
+        </is>
+      </c>
+      <c r="F37" s="42" t="inlineStr">
+        <is>
+          <t>CD 就绪；四道门禁</t>
+        </is>
+      </c>
+      <c r="G37" s="29" t="inlineStr">
+        <is>
+          <t>生产环境权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="18">
+      <c r="A38" s="43" t="n"/>
+      <c r="B38" s="43" t="n"/>
+      <c r="C38" s="43" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="41" t="inlineStr">
         <is>
-          <t>• 【DevOps】CD 流水线完善：Helm 多环境（Dev/Staging/Prod）+ Environments 审批流</t>
-        </is>
-      </c>
-      <c r="F38" s="42" t="inlineStr">
-        <is>
-          <t>CD 就绪；发布包 v1</t>
-        </is>
-      </c>
-      <c r="G38" s="29" t="inlineStr">
-        <is>
-          <t>生产环境权限</t>
-        </is>
-      </c>
+          <t>• 【DevOps】门禁③④上线（四道全开）</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="n"/>
+      <c r="G38" s="43" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1" s="18">
       <c r="A39" s="43" t="n"/>
@@ -3359,153 +3400,153 @@
       <c r="D39" s="46" t="n"/>
       <c r="E39" s="41" t="inlineStr">
         <is>
-          <t>• 【DevOps】安全门禁③④上线（gitleaks+Trivy，四道全开）</t>
+          <t>• 【NFR-安全】安全门禁生产化+High 清零复扫</t>
         </is>
       </c>
       <c r="F39" s="43" t="n"/>
       <c r="G39" s="43" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1" s="18">
-      <c r="A40" s="43" t="n"/>
-      <c r="B40" s="43" t="n"/>
-      <c r="C40" s="43" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="D40" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E40" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 生产发布包（Helm 生产 values+UC 生产脚本）</t>
-        </is>
-      </c>
-      <c r="F40" s="43" t="n"/>
-      <c r="G40" s="43" t="n"/>
+          <t>• 【NFR-性能】性能基准用例（100 万行 P95）</t>
+        </is>
+      </c>
+      <c r="F40" s="42" t="inlineStr">
+        <is>
+          <t>性能用例就绪</t>
+        </is>
+      </c>
+      <c r="G40" s="29" t="inlineStr"/>
     </row>
     <row r="41" ht="22" customHeight="1" s="18">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="A41" s="43" t="n"/>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="43" t="n"/>
+      <c r="D41" s="48" t="n"/>
+      <c r="E41" s="41" t="inlineStr">
+        <is>
+          <t>• R1 文档冲刺（用户手册 60%）</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="n"/>
+      <c r="G41" s="43" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1" s="18">
+      <c r="A42" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="D41" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E41" s="41" t="inlineStr">
-        <is>
-          <t>• R1 文档冲刺：用户手册 60%</t>
-        </is>
-      </c>
-      <c r="F41" s="42" t="inlineStr">
-        <is>
-          <t>文档 60%</t>
-        </is>
-      </c>
-      <c r="G41" s="29" t="inlineStr"/>
-    </row>
-    <row r="42" ht="22" customHeight="1" s="18">
-      <c r="A42" s="43" t="n"/>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="48" t="n"/>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="D42" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E42" s="41" t="inlineStr">
         <is>
-          <t>• 运维手册初稿（部署/监控部分）</t>
-        </is>
-      </c>
-      <c r="F42" s="43" t="n"/>
-      <c r="G42" s="43" t="n"/>
+          <t>• UAT #1 预演主持</t>
+        </is>
+      </c>
+      <c r="F42" s="42" t="inlineStr">
+        <is>
+          <t>预演完成</t>
+        </is>
+      </c>
+      <c r="G42" s="29" t="inlineStr"/>
     </row>
     <row r="43" ht="22" customHeight="1" s="18">
-      <c r="A43" s="38" t="inlineStr">
+      <c r="A43" s="43" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="44" t="n"/>
+      <c r="E43" s="41" t="inlineStr">
+        <is>
+          <t>• 预演反馈裁决</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1" s="18">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B43" s="39" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="D43" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E43" s="41" t="inlineStr">
-        <is>
-          <t>• UAT #1 预演主持（Staging：检索/权限/审计）</t>
-        </is>
-      </c>
-      <c r="F43" s="42" t="inlineStr">
-        <is>
-          <t>预演完成</t>
-        </is>
-      </c>
-      <c r="G43" s="29" t="inlineStr"/>
-    </row>
-    <row r="44" ht="22" customHeight="1" s="18">
-      <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="44" t="n"/>
+      <c r="D44" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
       <c r="E44" s="41" t="inlineStr">
         <is>
-          <t>• 预演反馈裁决</t>
-        </is>
-      </c>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
+          <t>• 🤖 生产发布包+回退演练</t>
+        </is>
+      </c>
+      <c r="F44" s="42" t="inlineStr">
+        <is>
+          <t>NFR 第一批达标；预跑完成</t>
+        </is>
+      </c>
+      <c r="G44" s="29" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="22" customHeight="1" s="18">
-      <c r="A45" s="38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="D45" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A45" s="43" t="n"/>
+      <c r="B45" s="43" t="n"/>
+      <c r="C45" s="43" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="41" t="inlineStr">
         <is>
-          <t>• 回退预案演练（发布回滚+UC 配置回滚）</t>
-        </is>
-      </c>
-      <c r="F45" s="42" t="inlineStr">
-        <is>
-          <t>回退演练过；预跑完成</t>
-        </is>
-      </c>
-      <c r="G45" s="29" t="inlineStr">
-        <is>
-          <t>生产窗口审批</t>
-        </is>
-      </c>
+          <t>• 【NFR-性能】首屏 P95&lt;5s 调优复测</t>
+        </is>
+      </c>
+      <c r="F45" s="43" t="n"/>
+      <c r="G45" s="43" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1" s="18">
       <c r="A46" s="43" t="n"/>
@@ -3514,7 +3555,7 @@
       <c r="D46" s="46" t="n"/>
       <c r="E46" s="41" t="inlineStr">
         <is>
-          <t>• 监控告警就绪（App Insights+Dashboard）</t>
+          <t>• 【NFR-可用性】备份策略落地（SQL PITR/ADLS 版本）+监控告警</t>
         </is>
       </c>
       <c r="F46" s="43" t="n"/>
@@ -3527,7 +3568,7 @@
       <c r="D47" s="46" t="n"/>
       <c r="E47" s="41" t="inlineStr">
         <is>
-          <t>• CC 迁移预跑（50 表→Staging）+ Runbook</t>
+          <t>• CC 迁移预跑+Runbook</t>
         </is>
       </c>
       <c r="F47" s="43" t="n"/>
@@ -3564,11 +3605,7 @@
           <t>★ R1 就绪检查 100%</t>
         </is>
       </c>
-      <c r="G48" s="29" t="inlineStr">
-        <is>
-          <t>各角色材料</t>
-        </is>
-      </c>
+      <c r="G48" s="29" t="inlineStr"/>
     </row>
     <row r="49" ht="22" customHeight="1" s="18">
       <c r="A49" s="43" t="n"/>
@@ -3577,7 +3614,7 @@
       <c r="D49" s="48" t="n"/>
       <c r="E49" s="41" t="inlineStr">
         <is>
-          <t>• W6 末就绪检查组织（CD/发布包/预演/回退/预跑）</t>
+          <t>• W6 末就绪检查（CD/发布包/预演/NFR 首批）</t>
         </is>
       </c>
       <c r="F49" s="43" t="n"/>
@@ -3606,7 +3643,7 @@
       </c>
       <c r="E50" s="41" t="inlineStr">
         <is>
-          <t>• Go/No-Go #1 决策参与</t>
+          <t>• Go/No-Go #1</t>
         </is>
       </c>
       <c r="F50" s="42" t="inlineStr">
@@ -3616,7 +3653,7 @@
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>UAT 业务方时间</t>
+          <t>UAT 时间</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3664,7 @@
       <c r="D51" s="44" t="n"/>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>• UAT #1 正式主持（签字）</t>
+          <t>• UAT #1 正式主持（Phase1 全场景签字）</t>
         </is>
       </c>
       <c r="F51" s="43" t="n"/>
@@ -3669,7 +3706,7 @@
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>• 生产发布执行（就绪包+审批）</t>
+          <t>• 生产发布（就绪包+审批）</t>
         </is>
       </c>
       <c r="F53" s="42" t="inlineStr">
@@ -3728,7 +3765,7 @@
       </c>
       <c r="E56" s="41" t="inlineStr">
         <is>
-          <t>• 上线执行记录</t>
+          <t>• 上线记录</t>
         </is>
       </c>
       <c r="F56" s="42" t="inlineStr">
@@ -3791,12 +3828,12 @@
       </c>
       <c r="E59" s="41" t="inlineStr">
         <is>
-          <t>• 【02】增量频率与冷数据标准确认</t>
+          <t>• 【02】统一元数据标准确认</t>
         </is>
       </c>
       <c r="F59" s="42" t="inlineStr">
         <is>
-          <t>R2 需求就绪</t>
+          <t>Phase2 需求就绪</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
@@ -3812,7 +3849,7 @@
       <c r="D60" s="44" t="n"/>
       <c r="E60" s="41" t="inlineStr">
         <is>
-          <t>• 【03】Legal Hold 触发条件定稿（法务）</t>
+          <t>• 【03】Legal Hold 条件定稿（法务）</t>
         </is>
       </c>
       <c r="F60" s="43" t="n"/>
@@ -3841,12 +3878,12 @@
       </c>
       <c r="E61" s="41" t="inlineStr">
         <is>
-          <t>• 【03】处置引擎（扫描→DROP PARTITION→VACUUM）</t>
+          <t>• 【02/P2】统一元数据模型+来源系统绑定</t>
         </is>
       </c>
       <c r="F61" s="42" t="inlineStr">
         <is>
-          <t>处置引擎可跑；加密生效</t>
+          <t>元数据模型；归档模型</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr"/>
@@ -3858,7 +3895,7 @@
       <c r="D62" s="46" t="n"/>
       <c r="E62" s="41" t="inlineStr">
         <is>
-          <t>• 【04】加密体系（CMK+字段级+轮转）</t>
+          <t>• 【03/P2】标准归档模型+转换校验</t>
         </is>
       </c>
       <c r="F62" s="43" t="n"/>
@@ -3900,7 +3937,7 @@
       </c>
       <c r="E64" s="41" t="inlineStr">
         <is>
-          <t>• 功能用例扩充（处置/Hold/增量/脱敏）</t>
+          <t>• Phase2 用例扩充</t>
         </is>
       </c>
       <c r="F64" s="42" t="inlineStr">
@@ -3946,17 +3983,17 @@
       </c>
       <c r="E66" s="41" t="inlineStr">
         <is>
-          <t>• 验收处置全链路（对照合规）</t>
+          <t>• 【02】冷数据识别标准确认（频率/时间阈值）</t>
         </is>
       </c>
       <c r="F66" s="42" t="inlineStr">
         <is>
-          <t>处置验收</t>
+          <t>冷数据标准</t>
         </is>
       </c>
       <c r="G66" s="29" t="inlineStr"/>
     </row>
-    <row r="67" ht="22" customHeight="1" s="18">
+    <row r="67" ht="30" customHeight="1" s="18">
       <c r="A67" s="49" t="inlineStr">
         <is>
           <t>R2</t>
@@ -3979,12 +4016,12 @@
       </c>
       <c r="E67" s="41" t="inlineStr">
         <is>
-          <t>• 【03】Legal Hold+归档模型+处置界面</t>
+          <t>• 【03】处置引擎（DROP PARTITION+VACUUM）+Legal Hold+归档模型界面</t>
         </is>
       </c>
       <c r="F67" s="42" t="inlineStr">
         <is>
-          <t>Hold 可用；分层生效</t>
+          <t>处置引擎+Hold 可用</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr"/>
@@ -3996,70 +4033,90 @@
       <c r="D68" s="46" t="n"/>
       <c r="E68" s="41" t="inlineStr">
         <is>
-          <t>• 【04】驻留核查+ADLS 分层+Compaction</t>
+          <t>• 【02/P2】冷数据识别标记+周期性接入任务</t>
         </is>
       </c>
       <c r="F68" s="43" t="n"/>
       <c r="G68" s="43" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1" s="18">
-      <c r="A69" s="43" t="n"/>
-      <c r="B69" s="43" t="n"/>
-      <c r="C69" s="43" t="n"/>
-      <c r="D69" s="46" t="n"/>
+      <c r="A69" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B69" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="D69" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E69" s="41" t="inlineStr">
         <is>
-          <t>• 【07】连接器模板库（MySQL+文件源）</t>
-        </is>
-      </c>
-      <c r="F69" s="43" t="n"/>
-      <c r="G69" s="43" t="n"/>
+          <t>• 【03】处置 E2E：1 天保留期→到期→Hold→处置→审计</t>
+        </is>
+      </c>
+      <c r="F69" s="42" t="inlineStr">
+        <is>
+          <t>处置 E2E 通过</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr"/>
     </row>
     <row r="70" ht="22" customHeight="1" s="18">
-      <c r="A70" s="49" t="inlineStr">
+      <c r="A70" s="43" t="n"/>
+      <c r="B70" s="43" t="n"/>
+      <c r="C70" s="43" t="n"/>
+      <c r="D70" s="48" t="n"/>
+      <c r="E70" s="41" t="inlineStr">
+        <is>
+          <t>• 数据一致性对账验证</t>
+        </is>
+      </c>
+      <c r="F70" s="43" t="n"/>
+      <c r="G70" s="43" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1" s="18">
+      <c r="A71" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B70" s="39" t="inlineStr">
+      <c r="B71" s="39" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="D70" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="inlineStr">
-        <is>
-          <t>• 【03】处置全链路 E2E（1 天保留期→到期→Hold→处置→审计）</t>
-        </is>
-      </c>
-      <c r="F70" s="42" t="inlineStr">
-        <is>
-          <t>处置 E2E 通过</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr"/>
-    </row>
-    <row r="71" ht="22" customHeight="1" s="18">
-      <c r="A71" s="43" t="n"/>
-      <c r="B71" s="43" t="n"/>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="48" t="n"/>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D71" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E71" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 安全测试②：掩码旁路/越权</t>
-        </is>
-      </c>
-      <c r="F71" s="43" t="n"/>
-      <c r="G71" s="43" t="n"/>
+          <t>• 处置链路合规验收</t>
+        </is>
+      </c>
+      <c r="F71" s="42" t="inlineStr">
+        <is>
+          <t>S4 验收</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr"/>
     </row>
     <row r="72" ht="22" customHeight="1" s="18">
       <c r="A72" s="49" t="inlineStr">
@@ -4069,7 +4126,7 @@
       </c>
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
@@ -4077,19 +4134,19 @@
           <t>W10</t>
         </is>
       </c>
-      <c r="D72" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D72" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E72" s="41" t="inlineStr">
         <is>
-          <t>• 合规报表口径与法务对齐</t>
+          <t>• 【02/P2】数据标签体系（多层级+停用）</t>
         </is>
       </c>
       <c r="F72" s="42" t="inlineStr">
         <is>
-          <t>口径确认；范围签字</t>
+          <t>★ Phase2 前半 Done</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr"/>
@@ -4098,10 +4155,10 @@
       <c r="A73" s="43" t="n"/>
       <c r="B73" s="43" t="n"/>
       <c r="C73" s="43" t="n"/>
-      <c r="D73" s="44" t="n"/>
+      <c r="D73" s="46" t="n"/>
       <c r="E73" s="41" t="inlineStr">
         <is>
-          <t>• CC 全量范围最终确认（签字）</t>
+          <t>• W8~W10 功能收口+回归</t>
         </is>
       </c>
       <c r="F73" s="43" t="n"/>
@@ -4115,7 +4172,7 @@
       </c>
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
@@ -4123,35 +4180,31 @@
           <t>W10</t>
         </is>
       </c>
-      <c r="D74" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
+      <c r="D74" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
         </is>
       </c>
       <c r="E74" s="41" t="inlineStr">
         <is>
-          <t>• 【01】CC 全量 1253 表分批迁移启动（600~800 有效表）</t>
+          <t>• Phase2 前半回归+文档 60%</t>
         </is>
       </c>
       <c r="F74" s="42" t="inlineStr">
         <is>
-          <t>全量启动</t>
-        </is>
-      </c>
-      <c r="G74" s="29" t="inlineStr">
-        <is>
-          <t>CC 数据量实测</t>
-        </is>
-      </c>
+          <t>回归通过</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr"/>
     </row>
     <row r="75" ht="22" customHeight="1" s="18">
       <c r="A75" s="43" t="n"/>
       <c r="B75" s="43" t="n"/>
       <c r="C75" s="43" t="n"/>
-      <c r="D75" s="46" t="n"/>
+      <c r="D75" s="48" t="n"/>
       <c r="E75" s="41" t="inlineStr">
         <is>
-          <t>• 【06】合规报表开发</t>
+          <t>• Sprint Review 支撑</t>
         </is>
       </c>
       <c r="F75" s="43" t="n"/>
@@ -4170,22 +4223,22 @@
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="D76" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D76" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
         </is>
       </c>
       <c r="E76" s="41" t="inlineStr">
         <is>
-          <t>• 【07】连接器兼容性测试</t>
+          <t>• 【04】境内驻留要求确认</t>
         </is>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
-          <t>兼容矩阵</t>
+          <t>驻留要求</t>
         </is>
       </c>
       <c r="G76" s="29" t="inlineStr"/>
@@ -4194,10 +4247,10 @@
       <c r="A77" s="43" t="n"/>
       <c r="B77" s="43" t="n"/>
       <c r="C77" s="43" t="n"/>
-      <c r="D77" s="48" t="n"/>
+      <c r="D77" s="44" t="n"/>
       <c r="E77" s="41" t="inlineStr">
         <is>
-          <t>• 用户手册 70%+数据字典初稿</t>
+          <t>• 合规报表口径启动对齐</t>
         </is>
       </c>
       <c r="F77" s="43" t="n"/>
@@ -4219,55 +4272,35 @@
           <t>W11</t>
         </is>
       </c>
-      <c r="D78" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D78" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E78" s="41" t="inlineStr">
         <is>
-          <t>• UAT #2 场景脚本初稿</t>
+          <t>• 【04/P2】境内数据驻留管理（区域锁定+核查）</t>
         </is>
       </c>
       <c r="F78" s="42" t="inlineStr">
         <is>
-          <t>UAT #2 脚本初稿</t>
+          <t>驻留+脱敏生效</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr"/>
     </row>
     <row r="79" ht="22" customHeight="1" s="18">
-      <c r="A79" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B79" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C79" s="26" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="D79" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A79" s="43" t="n"/>
+      <c r="B79" s="43" t="n"/>
+      <c r="C79" s="43" t="n"/>
+      <c r="D79" s="46" t="n"/>
       <c r="E79" s="41" t="inlineStr">
         <is>
-          <t>• 【01】全量迁移继续+逐批对账</t>
-        </is>
-      </c>
-      <c r="F79" s="42" t="inlineStr">
-        <is>
-          <t>★ 全量对账 100%</t>
-        </is>
-      </c>
-      <c r="G79" s="29" t="inlineStr"/>
+          <t>• 【04】加密+密钥管理+字段级脱敏（COLUMN MASK）</t>
+        </is>
+      </c>
+      <c r="F79" s="43" t="n"/>
+      <c r="G79" s="43" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1" s="18">
       <c r="A80" s="43" t="n"/>
@@ -4276,70 +4309,90 @@
       <c r="D80" s="46" t="n"/>
       <c r="E80" s="41" t="inlineStr">
         <is>
-          <t>• 【07】连接器运行监控+连接管理界面</t>
+          <t>• 【07/P2】连接器模板库（MySQL+文件源）</t>
         </is>
       </c>
       <c r="F80" s="43" t="n"/>
       <c r="G80" s="43" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1" s="18">
-      <c r="A81" s="43" t="n"/>
-      <c r="B81" s="43" t="n"/>
-      <c r="C81" s="43" t="n"/>
-      <c r="D81" s="46" t="n"/>
+      <c r="A81" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D81" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E81" s="41" t="inlineStr">
         <is>
-          <t>• 【08】行级隔离验证</t>
-        </is>
-      </c>
-      <c r="F81" s="43" t="n"/>
-      <c r="G81" s="43" t="n"/>
+          <t>• 🤖 安全测试②：掩码旁路/越权</t>
+        </is>
+      </c>
+      <c r="F81" s="42" t="inlineStr">
+        <is>
+          <t>安全测试②</t>
+        </is>
+      </c>
+      <c r="G81" s="29" t="inlineStr"/>
     </row>
     <row r="82" ht="22" customHeight="1" s="18">
-      <c r="A82" s="49" t="inlineStr">
+      <c r="A82" s="43" t="n"/>
+      <c r="B82" s="43" t="n"/>
+      <c r="C82" s="43" t="n"/>
+      <c r="D82" s="48" t="n"/>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>• 驻留核查用例</t>
+        </is>
+      </c>
+      <c r="F82" s="43" t="n"/>
+      <c r="G82" s="43" t="n"/>
+    </row>
+    <row r="83" ht="22" customHeight="1" s="18">
+      <c r="A83" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B82" s="39" t="inlineStr">
+      <c r="B83" s="39" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="D82" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E82" s="41" t="inlineStr">
-        <is>
-          <t>• 【06】合规报表口径验证</t>
-        </is>
-      </c>
-      <c r="F82" s="42" t="inlineStr">
-        <is>
-          <t>报表验证过</t>
-        </is>
-      </c>
-      <c r="G82" s="29" t="inlineStr"/>
-    </row>
-    <row r="83" ht="22" customHeight="1" s="18">
-      <c r="A83" s="43" t="n"/>
-      <c r="B83" s="43" t="n"/>
-      <c r="C83" s="43" t="n"/>
-      <c r="D83" s="48" t="n"/>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D83" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E83" s="41" t="inlineStr">
         <is>
-          <t>• 文档 80%（架构图更新+运维手册完善）</t>
-        </is>
-      </c>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
+          <t>• 【06】合规报表口径与法务对齐</t>
+        </is>
+      </c>
+      <c r="F83" s="42" t="inlineStr">
+        <is>
+          <t>报表口径</t>
+        </is>
+      </c>
+      <c r="G83" s="29" t="inlineStr"/>
     </row>
     <row r="84" ht="22" customHeight="1" s="18">
       <c r="A84" s="49" t="inlineStr">
@@ -4357,131 +4410,127 @@
           <t>W12</t>
         </is>
       </c>
-      <c r="D84" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D84" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E84" s="41" t="inlineStr">
         <is>
-          <t>• UAT #2 脚本定稿</t>
+          <t>• 【04/P2】备份与灾难恢复策略</t>
         </is>
       </c>
       <c r="F84" s="42" t="inlineStr">
         <is>
-          <t>UAT #2 脚本</t>
-        </is>
-      </c>
-      <c r="G84" s="29" t="inlineStr">
-        <is>
-          <t>业务方排期</t>
-        </is>
-      </c>
+          <t>灾备就绪；越权拦截</t>
+        </is>
+      </c>
+      <c r="G84" s="29" t="inlineStr"/>
     </row>
     <row r="85" ht="22" customHeight="1" s="18">
       <c r="A85" s="43" t="n"/>
       <c r="B85" s="43" t="n"/>
       <c r="C85" s="43" t="n"/>
-      <c r="D85" s="44" t="n"/>
+      <c r="D85" s="46" t="n"/>
       <c r="E85" s="41" t="inlineStr">
         <is>
-          <t>• 预演协调</t>
+          <t>• 【07/P2】集成标准与接口管理+连接器运行监控</t>
         </is>
       </c>
       <c r="F85" s="43" t="n"/>
       <c r="G85" s="43" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1" s="18">
-      <c r="A86" s="49" t="inlineStr">
+      <c r="A86" s="43" t="n"/>
+      <c r="B86" s="43" t="n"/>
+      <c r="C86" s="43" t="n"/>
+      <c r="D86" s="46" t="n"/>
+      <c r="E86" s="41" t="inlineStr">
+        <is>
+          <t>• 【08】行级隔离验证</t>
+        </is>
+      </c>
+      <c r="F86" s="43" t="n"/>
+      <c r="G86" s="43" t="n"/>
+    </row>
+    <row r="87" ht="22" customHeight="1" s="18">
+      <c r="A87" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B86" s="39" t="inlineStr">
+      <c r="B87" s="39" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C86" s="26" t="inlineStr">
+      <c r="C87" s="26" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="D86" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="E86" s="41" t="inlineStr">
-        <is>
-          <t>• 全量回归（R1+R2）+ 功能收口</t>
-        </is>
-      </c>
-      <c r="F86" s="42" t="inlineStr">
-        <is>
-          <t>回归通过；R2 发布包 v1</t>
-        </is>
-      </c>
-      <c r="G86" s="29" t="inlineStr"/>
-    </row>
-    <row r="87" ht="22" customHeight="1" s="18">
-      <c r="A87" s="43" t="n"/>
-      <c r="B87" s="43" t="n"/>
-      <c r="C87" s="43" t="n"/>
-      <c r="D87" s="46" t="n"/>
+      <c r="D87" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="E87" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 R2 发布包（增量/处置/加密/分层生产版）</t>
-        </is>
-      </c>
-      <c r="F87" s="43" t="n"/>
-      <c r="G87" s="43" t="n"/>
+          <t>• 连接器兼容矩阵（SQL Server/MySQL）</t>
+        </is>
+      </c>
+      <c r="F87" s="42" t="inlineStr">
+        <is>
+          <t>兼容矩阵</t>
+        </is>
+      </c>
+      <c r="G87" s="29" t="inlineStr"/>
     </row>
     <row r="88" ht="22" customHeight="1" s="18">
-      <c r="A88" s="49" t="inlineStr">
+      <c r="A88" s="43" t="n"/>
+      <c r="B88" s="43" t="n"/>
+      <c r="C88" s="43" t="n"/>
+      <c r="D88" s="48" t="n"/>
+      <c r="E88" s="41" t="inlineStr">
+        <is>
+          <t>• 文档 70%</t>
+        </is>
+      </c>
+      <c r="F88" s="43" t="n"/>
+      <c r="G88" s="43" t="n"/>
+    </row>
+    <row r="89" ht="22" customHeight="1" s="18">
+      <c r="A89" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B88" s="39" t="inlineStr">
+      <c r="B89" s="39" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C88" s="26" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="D88" s="47" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E88" s="41" t="inlineStr">
-        <is>
-          <t>• 文档冲刺：7 套进入终稿</t>
-        </is>
-      </c>
-      <c r="F88" s="42" t="inlineStr">
-        <is>
-          <t>文档 90%</t>
-        </is>
-      </c>
-      <c r="G88" s="29" t="inlineStr"/>
-    </row>
-    <row r="89" ht="22" customHeight="1" s="18">
-      <c r="A89" s="43" t="n"/>
-      <c r="B89" s="43" t="n"/>
-      <c r="C89" s="43" t="n"/>
-      <c r="D89" s="48" t="n"/>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="D89" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E89" s="41" t="inlineStr">
         <is>
-          <t>• 🤖 审批材料起稿</t>
-        </is>
-      </c>
-      <c r="F89" s="43" t="n"/>
-      <c r="G89" s="43" t="n"/>
+          <t>• CC 全量范围最终确认（600~800 表签字）</t>
+        </is>
+      </c>
+      <c r="F89" s="42" t="inlineStr">
+        <is>
+          <t>全量范围签字</t>
+        </is>
+      </c>
+      <c r="G89" s="29" t="inlineStr"/>
     </row>
     <row r="90" ht="22" customHeight="1" s="18">
       <c r="A90" s="49" t="inlineStr">
@@ -4499,31 +4548,35 @@
           <t>W13</t>
         </is>
       </c>
-      <c r="D90" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="D90" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
         </is>
       </c>
       <c r="E90" s="41" t="inlineStr">
         <is>
-          <t>• UAT #2 预演主持（处置/Hold/脱敏/报表）</t>
+          <t>• 【01】CC 全量 1253 表分批迁移+逐批对账</t>
         </is>
       </c>
       <c r="F90" s="42" t="inlineStr">
         <is>
-          <t>预演完成</t>
-        </is>
-      </c>
-      <c r="G90" s="29" t="inlineStr"/>
+          <t>★ 全量对账 100%</t>
+        </is>
+      </c>
+      <c r="G90" s="29" t="inlineStr">
+        <is>
+          <t>CC 数据量实测</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1" s="18">
       <c r="A91" s="43" t="n"/>
       <c r="B91" s="43" t="n"/>
       <c r="C91" s="43" t="n"/>
-      <c r="D91" s="44" t="n"/>
+      <c r="D91" s="46" t="n"/>
       <c r="E91" s="41" t="inlineStr">
         <is>
-          <t>• 预演反馈裁决</t>
+          <t>• 【06】合规报表开发（等保/个保法对照）</t>
         </is>
       </c>
       <c r="F91" s="43" t="n"/>
@@ -4545,157 +4598,169 @@
           <t>W13</t>
         </is>
       </c>
-      <c r="D92" s="45" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
+      <c r="D92" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
         </is>
       </c>
       <c r="E92" s="41" t="inlineStr">
         <is>
-          <t>• 回退演练+发布包冻结</t>
+          <t>• 【06】报表口径验证（可举证性）</t>
         </is>
       </c>
       <c r="F92" s="42" t="inlineStr">
         <is>
-          <t>终检通过；包冻结</t>
-        </is>
-      </c>
-      <c r="G92" s="29" t="inlineStr">
-        <is>
-          <t>渗透排期</t>
-        </is>
-      </c>
+          <t>报表验证过</t>
+        </is>
+      </c>
+      <c r="G92" s="29" t="inlineStr"/>
     </row>
     <row r="93" ht="22" customHeight="1" s="18">
       <c r="A93" s="43" t="n"/>
       <c r="B93" s="43" t="n"/>
       <c r="C93" s="43" t="n"/>
-      <c r="D93" s="46" t="n"/>
+      <c r="D93" s="48" t="n"/>
       <c r="E93" s="41" t="inlineStr">
         <is>
-          <t>• 安全终检（四门禁+渗透配合）</t>
+          <t>• 数据字典初稿</t>
         </is>
       </c>
       <c r="F93" s="43" t="n"/>
       <c r="G93" s="43" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1" s="18">
-      <c r="A94" s="43" t="n"/>
-      <c r="B94" s="43" t="n"/>
-      <c r="C94" s="43" t="n"/>
-      <c r="D94" s="46" t="n"/>
+      <c r="A94" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B94" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D94" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
       <c r="E94" s="41" t="inlineStr">
         <is>
-          <t>• 迁移预跑+窗口预约</t>
-        </is>
-      </c>
-      <c r="F94" s="43" t="n"/>
-      <c r="G94" s="43" t="n"/>
+          <t>• 【P3】AI 准确率验收标准定稿（字段提取≥90% 等）</t>
+        </is>
+      </c>
+      <c r="F94" s="42" t="inlineStr">
+        <is>
+          <t>AI 验收标准</t>
+        </is>
+      </c>
+      <c r="G94" s="29" t="inlineStr"/>
     </row>
     <row r="95" ht="22" customHeight="1" s="18">
-      <c r="A95" s="49" t="inlineStr">
+      <c r="A95" s="43" t="n"/>
+      <c r="B95" s="43" t="n"/>
+      <c r="C95" s="43" t="n"/>
+      <c r="D95" s="44" t="n"/>
+      <c r="E95" s="41" t="inlineStr">
+        <is>
+          <t>• 人工校验流程设计</t>
+        </is>
+      </c>
+      <c r="F95" s="43" t="n"/>
+      <c r="G95" s="43" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1" s="18">
+      <c r="A96" s="49" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B95" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C95" s="26" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="D95" s="47" t="inlineStr">
+      <c r="B96" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C96" s="26" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D96" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E96" s="41" t="inlineStr">
+        <is>
+          <t>• 【P3】智能内容解析：PDF/Word/图片文本提取</t>
+        </is>
+      </c>
+      <c r="F96" s="42" t="inlineStr">
+        <is>
+          <t>解析管道可跑</t>
+        </is>
+      </c>
+      <c r="G96" s="29" t="inlineStr"/>
+    </row>
+    <row r="97" ht="22" customHeight="1" s="18">
+      <c r="A97" s="43" t="n"/>
+      <c r="B97" s="43" t="n"/>
+      <c r="C97" s="43" t="n"/>
+      <c r="D97" s="46" t="n"/>
+      <c r="E97" s="41" t="inlineStr">
+        <is>
+          <t>• 【P3】结构化数据自动解析（字段含义/关系识别）</t>
+        </is>
+      </c>
+      <c r="F97" s="43" t="n"/>
+      <c r="G97" s="43" t="n"/>
+    </row>
+    <row r="98" ht="22" customHeight="1" s="18">
+      <c r="A98" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B98" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C98" s="26" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D98" s="47" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="E95" s="41" t="inlineStr">
-        <is>
-          <t>• W13 末就绪检查组织（发布包/预演/文档/回退）</t>
-        </is>
-      </c>
-      <c r="F95" s="42" t="inlineStr">
-        <is>
-          <t>★ R2 就绪检查 100%</t>
-        </is>
-      </c>
-      <c r="G95" s="29" t="inlineStr"/>
-    </row>
-    <row r="96" ht="22" customHeight="1" s="18">
-      <c r="A96" s="43" t="n"/>
-      <c r="B96" s="43" t="n"/>
-      <c r="C96" s="43" t="n"/>
-      <c r="D96" s="48" t="n"/>
-      <c r="E96" s="41" t="inlineStr">
-        <is>
-          <t>• 上线 Checklist v2</t>
-        </is>
-      </c>
-      <c r="F96" s="43" t="n"/>
-      <c r="G96" s="43" t="n"/>
-    </row>
-    <row r="97" ht="22" customHeight="1" s="18">
-      <c r="A97" s="49" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B97" s="39" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C97" s="26" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="D97" s="40" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="E97" s="41" t="inlineStr">
-        <is>
-          <t>• Go/No-Go #2 决策参与</t>
-        </is>
-      </c>
-      <c r="F97" s="42" t="inlineStr">
-        <is>
-          <t>★ UAT #2 签字</t>
-        </is>
-      </c>
-      <c r="G97" s="29" t="inlineStr">
-        <is>
-          <t>UAT 时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="22" customHeight="1" s="18">
-      <c r="A98" s="43" t="n"/>
-      <c r="B98" s="43" t="n"/>
-      <c r="C98" s="43" t="n"/>
-      <c r="D98" s="44" t="n"/>
       <c r="E98" s="41" t="inlineStr">
         <is>
-          <t>• UAT #2 正式主持（签字）</t>
-        </is>
-      </c>
-      <c r="F98" s="43" t="n"/>
-      <c r="G98" s="43" t="n"/>
+          <t>• AI 抽样集准备（金标准数据）</t>
+        </is>
+      </c>
+      <c r="F98" s="42" t="inlineStr">
+        <is>
+          <t>抽样集就绪</t>
+        </is>
+      </c>
+      <c r="G98" s="29" t="inlineStr"/>
     </row>
     <row r="99" ht="22" customHeight="1" s="18">
       <c r="A99" s="43" t="n"/>
       <c r="B99" s="43" t="n"/>
       <c r="C99" s="43" t="n"/>
-      <c r="D99" s="44" t="n"/>
+      <c r="D99" s="48" t="n"/>
       <c r="E99" s="41" t="inlineStr">
         <is>
-          <t>• 上线后反馈分诊</t>
+          <t>• 质量抽测方案</t>
         </is>
       </c>
       <c r="F99" s="43" t="n"/>
@@ -4709,43 +4774,63 @@
       </c>
       <c r="B100" s="39" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="C100" s="26" t="inlineStr">
         <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="D100" s="45" t="inlineStr">
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="D100" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E100" s="41" t="inlineStr">
+        <is>
+          <t>• 解析结果抽检（业务视角）</t>
+        </is>
+      </c>
+      <c r="F100" s="42" t="inlineStr">
+        <is>
+          <t>抽检反馈</t>
+        </is>
+      </c>
+      <c r="G100" s="29" t="inlineStr"/>
+    </row>
+    <row r="101" ht="22" customHeight="1" s="18">
+      <c r="A101" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B101" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C101" s="26" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="D101" s="45" t="inlineStr">
         <is>
           <t>DEV·Wade</t>
         </is>
       </c>
-      <c r="E100" s="41" t="inlineStr">
-        <is>
-          <t>• R2 生产发布（增量不中断 R1）</t>
-        </is>
-      </c>
-      <c r="F100" s="42" t="inlineStr">
-        <is>
-          <t>★ Go-Live #2</t>
-        </is>
-      </c>
-      <c r="G100" s="29" t="inlineStr"/>
-    </row>
-    <row r="101" ht="22" customHeight="1" s="18">
-      <c r="A101" s="43" t="n"/>
-      <c r="B101" s="43" t="n"/>
-      <c r="C101" s="43" t="n"/>
-      <c r="D101" s="46" t="n"/>
       <c r="E101" s="41" t="inlineStr">
         <is>
-          <t>• CC 生产全量迁移收尾+终版对账</t>
-        </is>
-      </c>
-      <c r="F101" s="43" t="n"/>
-      <c r="G101" s="43" t="n"/>
+          <t>• 【P3】核心业务信息提取（产品/批次/日期/金额）</t>
+        </is>
+      </c>
+      <c r="F101" s="42" t="inlineStr">
+        <is>
+          <t>信息提取达标</t>
+        </is>
+      </c>
+      <c r="G101" s="29" t="inlineStr"/>
     </row>
     <row r="102" ht="22" customHeight="1" s="18">
       <c r="A102" s="43" t="n"/>
@@ -4754,7 +4839,7 @@
       <c r="D102" s="46" t="n"/>
       <c r="E102" s="41" t="inlineStr">
         <is>
-          <t>• P1 当日清+48h 值守+交付物 tag</t>
+          <t>• 【P3】解析结果人工校验界面</t>
         </is>
       </c>
       <c r="F102" s="43" t="n"/>
@@ -4768,12 +4853,12 @@
       </c>
       <c r="B103" s="39" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="C103" s="26" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="D103" s="47" t="inlineStr">
@@ -4783,45 +4868,704 @@
       </c>
       <c r="E103" s="41" t="inlineStr">
         <is>
+          <t>• AI 准确率首轮报告</t>
+        </is>
+      </c>
+      <c r="F103" s="42" t="inlineStr">
+        <is>
+          <t>首轮准确率</t>
+        </is>
+      </c>
+      <c r="G103" s="29" t="inlineStr"/>
+    </row>
+    <row r="104" ht="22" customHeight="1" s="18">
+      <c r="A104" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B104" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C104" s="26" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="D104" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E104" s="41" t="inlineStr">
+        <is>
+          <t>• AI 验收（对照标准）——不达标则启动降级方案（范围裁剪）</t>
+        </is>
+      </c>
+      <c r="F104" s="42" t="inlineStr">
+        <is>
+          <t>AI 验收结论</t>
+        </is>
+      </c>
+      <c r="G104" s="29" t="inlineStr"/>
+    </row>
+    <row r="105" ht="22" customHeight="1" s="18">
+      <c r="A105" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B105" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C105" s="26" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="D105" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E105" s="41" t="inlineStr">
+        <is>
+          <t>• 【P3】AI 自动分类+语义标签</t>
+        </is>
+      </c>
+      <c r="F105" s="42" t="inlineStr">
+        <is>
+          <t>★ AI 演示可接受</t>
+        </is>
+      </c>
+      <c r="G105" s="29" t="inlineStr"/>
+    </row>
+    <row r="106" ht="22" customHeight="1" s="18">
+      <c r="A106" s="43" t="n"/>
+      <c r="B106" s="43" t="n"/>
+      <c r="C106" s="43" t="n"/>
+      <c r="D106" s="46" t="n"/>
+      <c r="E106" s="41" t="inlineStr">
+        <is>
+          <t>• 【P3/05】智能检索增强（自然语言→SQL 初版）</t>
+        </is>
+      </c>
+      <c r="F106" s="43" t="n"/>
+      <c r="G106" s="43" t="n"/>
+    </row>
+    <row r="107" ht="22" customHeight="1" s="18">
+      <c r="A107" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B107" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C107" s="26" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="D107" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E107" s="41" t="inlineStr">
+        <is>
+          <t>• Phase3 UAT 脚本+AI 质量报告</t>
+        </is>
+      </c>
+      <c r="F107" s="42" t="inlineStr">
+        <is>
+          <t>AI 质量报告</t>
+        </is>
+      </c>
+      <c r="G107" s="29" t="inlineStr"/>
+    </row>
+    <row r="108" ht="22" customHeight="1" s="18">
+      <c r="A108" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B108" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C108" s="26" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="D108" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E108" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 脚本定稿（全场景：Phase1+2+3+NFR）</t>
+        </is>
+      </c>
+      <c r="F108" s="42" t="inlineStr">
+        <is>
+          <t>UAT #2 脚本</t>
+        </is>
+      </c>
+      <c r="G108" s="29" t="inlineStr"/>
+    </row>
+    <row r="109" ht="22" customHeight="1" s="18">
+      <c r="A109" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B109" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C109" s="26" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="D109" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E109" s="41" t="inlineStr">
+        <is>
+          <t>• 【NFR-性能】20GB 级基准+调优（首屏/导出/联邦）</t>
+        </is>
+      </c>
+      <c r="F109" s="42" t="inlineStr">
+        <is>
+          <t>性能达标</t>
+        </is>
+      </c>
+      <c r="G109" s="29" t="inlineStr"/>
+    </row>
+    <row r="110" ht="22" customHeight="1" s="18">
+      <c r="A110" s="43" t="n"/>
+      <c r="B110" s="43" t="n"/>
+      <c r="C110" s="43" t="n"/>
+      <c r="D110" s="46" t="n"/>
+      <c r="E110" s="41" t="inlineStr">
+        <is>
+          <t>• 全量回归（R1+R2 全功能）</t>
+        </is>
+      </c>
+      <c r="F110" s="43" t="n"/>
+      <c r="G110" s="43" t="n"/>
+    </row>
+    <row r="111" ht="22" customHeight="1" s="18">
+      <c r="A111" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B111" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C111" s="26" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="D111" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E111" s="41" t="inlineStr">
+        <is>
+          <t>• 【NFR-可用性】灾备演练（SQL 故障转移/ADLS 恢复）</t>
+        </is>
+      </c>
+      <c r="F111" s="42" t="inlineStr">
+        <is>
+          <t>灾备演练过</t>
+        </is>
+      </c>
+      <c r="G111" s="29" t="inlineStr"/>
+    </row>
+    <row r="112" ht="22" customHeight="1" s="18">
+      <c r="A112" s="43" t="n"/>
+      <c r="B112" s="43" t="n"/>
+      <c r="C112" s="43" t="n"/>
+      <c r="D112" s="48" t="n"/>
+      <c r="E112" s="41" t="inlineStr">
+        <is>
+          <t>• 文档冲刺：7 套进入终稿</t>
+        </is>
+      </c>
+      <c r="F112" s="43" t="n"/>
+      <c r="G112" s="43" t="n"/>
+    </row>
+    <row r="113" ht="22" customHeight="1" s="18">
+      <c r="A113" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B113" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C113" s="26" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E113" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 预演主持</t>
+        </is>
+      </c>
+      <c r="F113" s="42" t="inlineStr">
+        <is>
+          <t>预演完成</t>
+        </is>
+      </c>
+      <c r="G113" s="29" t="inlineStr">
+        <is>
+          <t>业务方排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1" s="18">
+      <c r="A114" s="43" t="n"/>
+      <c r="B114" s="43" t="n"/>
+      <c r="C114" s="43" t="n"/>
+      <c r="D114" s="44" t="n"/>
+      <c r="E114" s="41" t="inlineStr">
+        <is>
+          <t>• 预演反馈裁决</t>
+        </is>
+      </c>
+      <c r="F114" s="43" t="n"/>
+      <c r="G114" s="43" t="n"/>
+    </row>
+    <row r="115" ht="22" customHeight="1" s="18">
+      <c r="A115" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B115" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C115" s="26" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="D115" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E115" s="41" t="inlineStr">
+        <is>
+          <t>• 🤖 R2 发布包+回退演练+冻结</t>
+        </is>
+      </c>
+      <c r="F115" s="42" t="inlineStr">
+        <is>
+          <t>发布包冻结；渗透整改</t>
+        </is>
+      </c>
+      <c r="G115" s="29" t="inlineStr">
+        <is>
+          <t>渗透排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1" s="18">
+      <c r="A116" s="43" t="n"/>
+      <c r="B116" s="43" t="n"/>
+      <c r="C116" s="43" t="n"/>
+      <c r="D116" s="46" t="n"/>
+      <c r="E116" s="41" t="inlineStr">
+        <is>
+          <t>• 【NFR-安全】渗透测试配合+整改</t>
+        </is>
+      </c>
+      <c r="F116" s="43" t="n"/>
+      <c r="G116" s="43" t="n"/>
+    </row>
+    <row r="117" ht="22" customHeight="1" s="18">
+      <c r="A117" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B117" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C117" s="26" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="D117" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E117" s="41" t="inlineStr">
+        <is>
+          <t>• 【NFR-合规】等保/个保法举证材料整理</t>
+        </is>
+      </c>
+      <c r="F117" s="42" t="inlineStr">
+        <is>
+          <t>★ R2 就绪检查 100%</t>
+        </is>
+      </c>
+      <c r="G117" s="29" t="inlineStr"/>
+    </row>
+    <row r="118" ht="22" customHeight="1" s="18">
+      <c r="A118" s="43" t="n"/>
+      <c r="B118" s="43" t="n"/>
+      <c r="C118" s="43" t="n"/>
+      <c r="D118" s="48" t="n"/>
+      <c r="E118" s="41" t="inlineStr">
+        <is>
+          <t>• W18 末就绪检查（NFR 全达标+发布包+文档）</t>
+        </is>
+      </c>
+      <c r="F118" s="43" t="n"/>
+      <c r="G118" s="43" t="n"/>
+    </row>
+    <row r="119" ht="22" customHeight="1" s="18">
+      <c r="A119" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B119" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C119" s="26" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E119" s="41" t="inlineStr">
+        <is>
+          <t>• Go/No-Go #2</t>
+        </is>
+      </c>
+      <c r="F119" s="42" t="inlineStr">
+        <is>
+          <t>★ UAT #2 签字</t>
+        </is>
+      </c>
+      <c r="G119" s="29" t="inlineStr">
+        <is>
+          <t>UAT 时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1" s="18">
+      <c r="A120" s="43" t="n"/>
+      <c r="B120" s="43" t="n"/>
+      <c r="C120" s="43" t="n"/>
+      <c r="D120" s="44" t="n"/>
+      <c r="E120" s="41" t="inlineStr">
+        <is>
+          <t>• UAT #2 正式主持（签字）</t>
+        </is>
+      </c>
+      <c r="F120" s="43" t="n"/>
+      <c r="G120" s="43" t="n"/>
+    </row>
+    <row r="121" ht="22" customHeight="1" s="18">
+      <c r="A121" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B121" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C121" s="26" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="D121" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E121" s="41" t="inlineStr">
+        <is>
+          <t>• R2 生产发布（Phase2+3+NFR，增量不中断 R1）</t>
+        </is>
+      </c>
+      <c r="F121" s="42" t="inlineStr">
+        <is>
+          <t>★ Go-Live #2</t>
+        </is>
+      </c>
+      <c r="G121" s="29" t="inlineStr"/>
+    </row>
+    <row r="122" ht="22" customHeight="1" s="18">
+      <c r="A122" s="43" t="n"/>
+      <c r="B122" s="43" t="n"/>
+      <c r="C122" s="43" t="n"/>
+      <c r="D122" s="46" t="n"/>
+      <c r="E122" s="41" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移收尾</t>
+        </is>
+      </c>
+      <c r="F122" s="43" t="n"/>
+      <c r="G122" s="43" t="n"/>
+    </row>
+    <row r="123" ht="22" customHeight="1" s="18">
+      <c r="A123" s="43" t="n"/>
+      <c r="B123" s="43" t="n"/>
+      <c r="C123" s="43" t="n"/>
+      <c r="D123" s="46" t="n"/>
+      <c r="E123" s="41" t="inlineStr">
+        <is>
+          <t>• P1 当日清+48h 值守</t>
+        </is>
+      </c>
+      <c r="F123" s="43" t="n"/>
+      <c r="G123" s="43" t="n"/>
+    </row>
+    <row r="124" ht="22" customHeight="1" s="18">
+      <c r="A124" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B124" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C124" s="26" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="D124" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E124" s="41" t="inlineStr">
+        <is>
           <t>• 审批材料提交（完整版）</t>
         </is>
       </c>
-      <c r="F103" s="42" t="inlineStr">
-        <is>
-          <t>★ Release 2 交付完成</t>
-        </is>
-      </c>
-      <c r="G103" s="29" t="inlineStr">
+      <c r="F124" s="42" t="inlineStr">
         <is>
           <t>审批受理</t>
         </is>
       </c>
-    </row>
-    <row r="104" ht="22" customHeight="1" s="18">
-      <c r="A104" s="43" t="n"/>
-      <c r="B104" s="43" t="n"/>
-      <c r="C104" s="43" t="n"/>
-      <c r="D104" s="48" t="n"/>
-      <c r="E104" s="41" t="inlineStr">
-        <is>
-          <t>• 文档终版归档（7 套）</t>
-        </is>
-      </c>
-      <c r="F104" s="43" t="n"/>
-      <c r="G104" s="43" t="n"/>
-    </row>
-    <row r="105" ht="22" customHeight="1" s="18">
-      <c r="A105" s="43" t="n"/>
-      <c r="B105" s="43" t="n"/>
-      <c r="C105" s="43" t="n"/>
-      <c r="D105" s="48" t="n"/>
-      <c r="E105" s="41" t="inlineStr">
+      <c r="G124" s="29" t="inlineStr"/>
+    </row>
+    <row r="125" ht="22" customHeight="1" s="18">
+      <c r="A125" s="43" t="n"/>
+      <c r="B125" s="43" t="n"/>
+      <c r="C125" s="43" t="n"/>
+      <c r="D125" s="48" t="n"/>
+      <c r="E125" s="41" t="inlineStr">
+        <is>
+          <t>• 上线记录</t>
+        </is>
+      </c>
+      <c r="F125" s="43" t="n"/>
+      <c r="G125" s="43" t="n"/>
+    </row>
+    <row r="126" ht="22" customHeight="1" s="18">
+      <c r="A126" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B126" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C126" s="26" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="D126" s="40" t="inlineStr">
+        <is>
+          <t>BA·Mandy</t>
+        </is>
+      </c>
+      <c r="E126" s="41" t="inlineStr">
+        <is>
+          <t>• 上线一周稳定性观察</t>
+        </is>
+      </c>
+      <c r="F126" s="42" t="inlineStr">
+        <is>
+          <t>稳定性确认</t>
+        </is>
+      </c>
+      <c r="G126" s="29" t="inlineStr"/>
+    </row>
+    <row r="127" ht="22" customHeight="1" s="18">
+      <c r="A127" s="43" t="n"/>
+      <c r="B127" s="43" t="n"/>
+      <c r="C127" s="43" t="n"/>
+      <c r="D127" s="44" t="n"/>
+      <c r="E127" s="41" t="inlineStr">
+        <is>
+          <t>• 遗留清单确认</t>
+        </is>
+      </c>
+      <c r="F127" s="43" t="n"/>
+      <c r="G127" s="43" t="n"/>
+    </row>
+    <row r="128" ht="22" customHeight="1" s="18">
+      <c r="A128" s="43" t="n"/>
+      <c r="B128" s="43" t="n"/>
+      <c r="C128" s="43" t="n"/>
+      <c r="D128" s="44" t="n"/>
+      <c r="E128" s="41" t="inlineStr">
+        <is>
+          <t>• 项目结束确认</t>
+        </is>
+      </c>
+      <c r="F128" s="43" t="n"/>
+      <c r="G128" s="43" t="n"/>
+    </row>
+    <row r="129" ht="22" customHeight="1" s="18">
+      <c r="A129" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B129" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C129" s="26" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="D129" s="45" t="inlineStr">
+        <is>
+          <t>DEV·Wade</t>
+        </is>
+      </c>
+      <c r="E129" s="41" t="inlineStr">
+        <is>
+          <t>• 遗留清零+技术债清理</t>
+        </is>
+      </c>
+      <c r="F129" s="42" t="inlineStr">
+        <is>
+          <t>交付物归档</t>
+        </is>
+      </c>
+      <c r="G129" s="29" t="inlineStr"/>
+    </row>
+    <row r="130" ht="22" customHeight="1" s="18">
+      <c r="A130" s="43" t="n"/>
+      <c r="B130" s="43" t="n"/>
+      <c r="C130" s="43" t="n"/>
+      <c r="D130" s="46" t="n"/>
+      <c r="E130" s="41" t="inlineStr">
+        <is>
+          <t>• 交付物归档（代码/脚本/ADR+tag）</t>
+        </is>
+      </c>
+      <c r="F130" s="43" t="n"/>
+      <c r="G130" s="43" t="n"/>
+    </row>
+    <row r="131" ht="22" customHeight="1" s="18">
+      <c r="A131" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B131" s="39" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C131" s="26" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="D131" s="47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E131" s="41" t="inlineStr">
+        <is>
+          <t>• 7 套文档终版归档+培训视频</t>
+        </is>
+      </c>
+      <c r="F131" s="42" t="inlineStr">
+        <is>
+          <t>★ 项目结束</t>
+        </is>
+      </c>
+      <c r="G131" s="29" t="inlineStr"/>
+    </row>
+    <row r="132" ht="22" customHeight="1" s="18">
+      <c r="A132" s="43" t="n"/>
+      <c r="B132" s="43" t="n"/>
+      <c r="C132" s="43" t="n"/>
+      <c r="D132" s="48" t="n"/>
+      <c r="E132" s="41" t="inlineStr">
         <is>
           <t>• 稳定性报告 → 项目结束</t>
         </is>
       </c>
-      <c r="F105" s="43" t="n"/>
-      <c r="G105" s="43" t="n"/>
+      <c r="F132" s="43" t="n"/>
+      <c r="G132" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
